--- a/工事担任者問題20260523.xlsx
+++ b/工事担任者問題20260523.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>GE-PON,OLT,ONU,TDMA,LLID,DBA</t>
+          <t>GE-PON|GE-PON OLT ONU,OLT|OLT GE-PON 光加入者線終端装置,ONU|ONU GE-PON 光網終端装置,TDMA|TDMA GE-PON 上り信号 衝突回避,LLID|LLID GE-PON 論理リンクID</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>IP-PBX,VoIPゲートウェイ,SIP,IPセントレックス</t>
+          <t>IP-PBX|IP-PBX VoIPゲートウェイ アナログ電話,VoIPゲートウェイ|VoIPゲートウェイ IP-PBX アナログ変換,IPセントレックス|IPセントレックス クラウドPBX SIP</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>PoE,IEEE802.3at,PSE,PD</t>
+          <t>IEEE802.3at|IEEE802.3at PoE PSE PD 給電規格,PSE|PSE PoE 給電機器 IEEE802.3at</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>レイヤ3スイッチ,RIP,OSPF,ルーティングプロトコル</t>
+          <t>レイヤ3スイッチ|レイヤ3スイッチ ルーティング RIP OSPF,RIP|RIP OSPF ルーティングプロトコル,OSPF|OSPF RIP ルーティングプロトコル</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SPD,バリスタ,過渡電圧抑制ダイオード,サージ防護</t>
+          <t>SPD|SPD サージ防護デバイス バリスタ,バリスタ|バリスタ SPD 非線形素子 サージ防護</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10GBASE-LR,64B/66B,8B/10B,4B/5B</t>
+          <t>10GBASE-LR|10GBASE-LR 64B/66B 符号化方式,64B/66B|64B/66B 10GBASE-LR 符号化</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SS方式,PDS方式,PON,光ファイバ</t>
+          <t>SS方式|SS方式 シングルスター 光ファイバ 1対1接続,PDS方式|PDS方式 PON 光受動素子 分岐</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>HFC,FTTH,光ノード,同軸ケーブル</t>
+          <t>HFC|HFC Hybrid Fiber Coaxial 光ノード 同軸ケーブル,FTTH|FTTH 光ファイバ 全区間</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>IPv6,IPv4,MTU,パケット分割,DF</t>
+          <t>IPv6|IPv6 パケット分割 送信元ノード,IPv4|IPv4 DF TTL パケット分割 中継</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,プリアンブル,FCS</t>
+          <t>EoMPLS|EoMPLS LER MPLS イーサネット転送,LER|LER EoMPLS ラベルエッジルータ,MPLS|MPLS LER LSR ラベルスイッチング</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>バッファオーバフロー,スタック,DoS攻撃</t>
+          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 スタック 任意コード実行</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>PAP,CHAP,チャレンジ・レスポンス,シングルサインオン</t>
+          <t>CHAP|CHAP チャレンジ・レスポンス 認証,PAP|PAP 平文認証 パスワード</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>TLS,HTTPS,SMTP,スニッフィング,暗号化</t>
+          <t>TLS|TLS HTTPS 暗号化 スニッフィング対策,スニッフィング|スニッフィング 盗聴 TLS 暗号化対策</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>syslog,UDP,SNMP,ログ管理</t>
+          <t>syslog|syslog UDP ログ管理 リモート転送</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>JIS Q 27001,ISMS,情報セキュリティ</t>
+          <t>JIS Q 27001|JIS Q 27001 ISMS 情報セキュリティ管理</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>挿入法,カットバック法,OTDR,挿入損失</t>
+          <t>挿入法|挿入法 光ファイバ損失 挿入損失測定,カットバック法|カットバック法 光ファイバ損失 破壊試験,OTDR|OTDR 光ファイバ 後方散乱光 損失測定</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>POF,アクリル樹脂,フッ素樹脂,プラスチック光ファイバ</t>
+          <t>POF|POF プラスチック光ファイバ アクリル フッ素樹脂</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>OTDR法,後方散乱光,光ファイバ損失試験,JIS C 6823</t>
+          <t>OTDR法|OTDR法 後方散乱光 光ファイバ損失試験 JIS C 6823,JIS C 6823|JIS C 6823 光ファイバ損失試験 OTDR</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,UTPケーブル,心線配色</t>
+          <t>T568B|T568B RJ-45 心線配色 UTPケーブル配線規格</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスE,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 水平配線 チャネル最大長 クラスE</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>反射減衰量,挿入損失,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 反射減衰量 挿入損失 測定規定</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>OTDR,ダイナミックレンジ,後方散乱光,パルスパワー</t>
+          <t>OTDR|OTDR ダイナミックレンジ 後方散乱光 パルスパワー,ダイナミックレンジ|OTDRダイナミックレンジ 測定範囲 後方散乱光</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>全二重,半二重,CSMA/CD,衝突</t>
+          <t>CSMA/CD|CSMA/CD 全二重 半二重 衝突 イーサネット,全二重通信|全二重通信 CSMA/CD 衝突なし イーサネット</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>施工計画書,現場代理人,監督員,工事管理</t>
+          <t>施工計画書|施工計画書 受注者 監督員 工事管理</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム クリティカルパス PERT 工程管理,クリティカルパス|クリティカルパス トータルフロート アローダイアグラム,トータルフロート|トータルフロート クリティカルパス フリーフロート</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>基礎的電気通信役務,電気通信事業法</t>
+          <t>基礎的電気通信役務|基礎的電気通信役務 電気通信事業法 適切公平安定</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>管理規程,電気通信事業法</t>
+          <t>管理規程|管理規程 電気通信事業法 確実かつ安定的</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>技術基準適合認定,登録認定機関,表示</t>
+          <t>技術基準適合認定|技術基準適合認定 登録認定機関 表示 端末機器</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>端末設備,技術基準,電気通信事業法</t>
+          <t>端末設備|端末設備 技術基準 電気通信事業法 接続検査</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>重要通信,緊急通信,電気通信事業法</t>
+          <t>重要通信|重要通信 緊急通信 電気通信事業法 優先</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>工事担任者,資格者証,端末設備等</t>
+          <t>工事担任者|工事担任者 資格者証 端末設備 知識技術向上</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>資格者証,再交付,書換え交付</t>
+          <t>資格者証|資格者証 再交付 書換え交付 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>技術基準適合認定,認定番号,表示方法</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 先頭文字 端末機器</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>有線電気通信法,総務大臣,立入検査</t>
+          <t>有線電気通信法|有線電気通信法 総務大臣 立入検査 報告</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>有線電気通信設備,技術基準,有線電気通信法</t>
+          <t>有線電気通信設備令|有線電気通信設備令 技術基準 保安</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>アナログ電話用設備,専用通信回線設備,端末設備等規則</t>
+          <t>アナログ電話用設備|アナログ電話用設備 端末設備等規則 アナログ信号,専用通信回線設備|専用通信回線設備 端末設備等規則 特定利用者</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>分界点,端末設備,接続方式</t>
+          <t>分界点|分界点 端末設備 事業用電気通信設備 切り離し</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>直流回路,アナログ電話用設備,交換設備</t>
+          <t>直流回路|直流回路 アナログ電話用設備 交換設備 動作制御</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>評価雑音電力,実効的雑音電力,端末設備等規則</t>
+          <t>評価雑音電力|評価雑音電力 実効的雑音電力 人間聴覚 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,端末設備</t>
+          <t>識別符号|識別符号 無線設備 通信路設定 照合</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,ダイヤル番号,ミニマムポーズ</t>
+          <t>押しボタンダイヤル信号|押しボタンダイヤル信号 ダイヤル番号 16種類 ミニマムポーズ</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>絶縁抵抗,配線設備,有線電気通信設備令</t>
+          <t>絶縁抵抗|絶縁抵抗 配線設備 直流200V 1MΩ 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>自動再発信,発信要求信号,アナログ電話端末</t>
+          <t>自動再発信|自動再発信 アナログ電話端末 2回以内 3分間</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>初期識別符号,アクセス制御,端末設備等規則</t>
+          <t>初期識別符号|初期識別符号 変更を促す機能 アクセス制御 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>漏話減衰量,専用通信回線設備等端末,端末設備等規則</t>
+          <t>漏話減衰量|漏話減衰量 専用通信回線設備等端末 1500Hz 70dB</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>架空電線,電柱,安全係数,有線電気通信設備令</t>
+          <t>有線電気通信設備令|有線電気通信設備令 架空電線 電柱 安全係数</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>電線,有線電気通信法,強電流電線</t>
+          <t>有線電気通信法|有線電気通信法 電線 強電流電線 定義</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>屋内電線,強電流電線,離隔距離,有線電気通信設備令</t>
+          <t>有線電気通信設備令|有線電気通信設備令 屋内電線 強電流電線 離隔距離</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 アクセス制御機能 制限を免れる</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>電子署名法,電磁的記録,認証業務</t>
+          <t>電子署名法|電子署名法 電磁的記録 真正成立 推定</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>10G-EPON,IEEE802.3av,XG-PON,XGS-PON,FEC,64B/66B</t>
+          <t>10G-EPON|10G-EPON IEEE802.3av FEC 64B/66B,XGS-PON|XGS-PON ITU-T G.9807 10Gbps対称,FEC|FEC 前方誤り訂正 10G-EPON</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>SIPサーバ,レジストラ,プロキシサーバ,リダイレクトサーバ,UAC</t>
+          <t>SIPサーバ|SIPサーバ レジストラ プロキシ リダイレクト UAC,レジストラ|レジストラ SIPサーバ 登録要求 REGISTER,UAC|UAC SIPクライアント 発信側</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>PoE,IEEE802.3at,Type1,Class0,PSE</t>
+          <t>IEEE802.3at|IEEE802.3at PoE Type1 Class0 350mA</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>ZigBee,Bluetooth,無線PAN,IEEE802.15.4</t>
+          <t>ZigBee|ZigBee IEEE802.15.4 センサネットワーク 250kbps 65535台</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>フェライトコア,コモンモードチョークコイル,EMC,ノイズ対策</t>
+          <t>コモンモードチョークコイル|コモンモードチョークコイル EMC ノイズ対策,フェライトコア|フェライトコア 高周波ノイズ インダクタンス EMC</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>NRZI,AMI,2値符号,3値符号,MLT-3</t>
+          <t>NRZI|NRZI 2値符号 AMI MLT-3 比較,AMI|AMI 3値符号 NRZIとの違い</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>FTTB,VDSL,PDS方式,PON</t>
+          <t>FTTB|FTTB VDSL 集合住宅 光ファイバ 既設電話線,VDSL|VDSL FTTB 既設電話線 高速伝送</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>IPv6,マルチキャスト,リンクローカル,ユニークローカル</t>
+          <t>IPv6マルチキャスト|IPv6 マルチキャストアドレス ff 先頭8ビット</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>PLC,パケット損失,ジッタ,VoIP,ARQ</t>
+          <t>PLC|PLC Packet Loss Concealment パケット損失補間 VoIP</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>IP-VPN,広域イーサネット,MPLS,レイヤ2,レイヤ3</t>
+          <t>IP-VPN|IP-VPN MPLS レイヤ3 広域イーサネット比較,広域イーサネット|広域イーサネット レイヤ2 IP-VPN比較</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>TCPスキャン,SYN,ポートスキャン,ステルススキャン</t>
+          <t>TCPスキャン|TCP SYNスキャン ポートスキャン ステルス</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>RSA暗号,素因数分解,ブロック暗号,ストリーム暗号</t>
+          <t>RSA暗号|RSA暗号 素因数分解 公開鍵暗号,ブロック暗号|ブロック暗号 ストリーム暗号 違い 暗号方式</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>パケットフィルタリング,ファイアウォール,IPアドレス,ポート番号</t>
+          <t>パケットフィルタリング|パケットフィルタリング ファイアウォール IPアドレス ポート番号</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>ペネトレーションテスト,脆弱性診断,セキュリティ評価</t>
+          <t>ペネトレーションテスト|ペネトレーションテスト 侵入テスト 脆弱性診断</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>情報セキュリティ方針,JIS Q 27001,ISMS</t>
+          <t>JIS Q 27001|JIS Q 27001 ISMS 情報セキュリティ方針</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>光導通試験,励振用光ファイバ,SI形,GI形,PINホトダイオード</t>
+          <t>光導通試験|光導通試験 励振用光ファイバ SI形 GI形,PINホトダイオード|PINホトダイオード 光検出器 受感面</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>フリーアクセスフロア,OAフロア,不陸調整</t>
+          <t>フリーアクセスフロア|フリーアクセスフロア OAフロア 不陸調整</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>PoE,オルタナティブA,オルタナティブB,給電ピン</t>
+          <t>PoEオルタナティブA|PoE オルタナティブA ピン1 2 3 6 データ信号線,PoEオルタナティブB|PoE オルタナティブB ピン4 5 7 8 予備ペア</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>プライベートIPアドレス,クラスA,クラスB,クラスC</t>
+          <t>プライベートIPアドレス|プライベートIPアドレス クラスA B C 範囲</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>クロスコネクト,クラスE,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 クロスコネクト クラスE 水平ケーブル最大長</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>MPOコネクタ,多心光コネクタ,プッシュプル,データセンタ</t>
+          <t>MPOコネクタ|MPOコネクタ 多心光コネクタ 12心 24心 プッシュプル</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>挿入損失法,カットバック法,OTDR,非破壊測定</t>
+          <t>挿入損失法|挿入損失法 カットバック法 OTDR 非破壊測定 比較</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>STP,IEEE802.1D,スパニングツリー,ループ防止</t>
+          <t>STP|STP IEEE802.1D スパニングツリー ループ防止,IEEE802.1D|IEEE802.1D STP スパニングツリープロトコル</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>ヒストグラム,パレート図,管理図,QC7つ道具</t>
+          <t>ヒストグラム|ヒストグラム パレート図 管理図 QC7つ道具 違い,パレート図|パレート図 累積度数 QC7つ道具</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>クリティカルパス,トータルフロート,アローダイアグラム</t>
+          <t>クリティカルパス|クリティカルパス トータルフロート ゼロ アローダイアグラム</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>業務改善命令,電気通信事業法,重要通信</t>
+          <t>業務改善命令|業務改善命令 電気通信事業法 対象 要件</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>重要通信,緊急通信,選挙管理機関,天災</t>
+          <t>重要通信|重要通信 緊急通信 選挙管理機関 天災 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>業務改善命令,重要通信,電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 重要通信 適切に配慮 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>管理規程,確実かつ安定的,電気通信事業法</t>
+          <t>管理規程|管理規程 確実かつ安定的 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,電波,電気通信事業法</t>
+          <t>端末設備接続拒否|端末設備 接続請求 拒否 電波 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>工事担任者,第二級アナログ通信,基本インタフェース,資格区分</t>
+          <t>第二級アナログ通信|第二級アナログ通信 工事担任者 回線数1以下 資格区分</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>専用設備,工事担任者,資格者証,技術基準</t>
+          <t>専用設備接続|専用設備 工事担任者 不要 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,IP電話用設備,認定番号</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 先頭文字 IP電話用設備 E</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>本邦外,有線電気通信設備,総務大臣,有線電気通信法</t>
+          <t>有線電気通信法|有線電気通信法 本邦外 総務大臣 許可</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保</t>
+          <t>有線電気通信法非常事態|有線電気通信法 非常事態 通信確保 命令</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>総合デジタル通信用設備,専用通信回線設備,アナログ電話用設備,端末設備等規則</t>
+          <t>総合デジタル通信用設備|総合デジタル通信用設備 64kbps 符号音声影像 統合,専用通信回線設備|専用通信回線設備 特定利用者 専用 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>接地抵抗,絶縁耐力,端末設備等規則</t>
+          <t>接地抵抗100オーム|接地抵抗 100オーム以下 端末設備 金属筐体,絶縁耐力試験|絶縁耐力試験 使用電圧 10分間 端末設備</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,通信路</t>
+          <t>識別符号|識別符号 無線設備 通信路設定 照合</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>端末設備,事業用電気通信設備,識別機能,無線設備</t>
+          <t>端末設備識別機能|端末設備 事業用電気通信設備 漏えい 識別禁止,無線設備筐体|端末設備 無線設備 一の筐体 容易に開けられない</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>制御チャネル,移動電話用設備,移動電話端末</t>
+          <t>制御チャネル|制御チャネル 移動電話用設備 制御信号 通信路</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>絶縁抵抗,配線設備,有線電気通信設備令</t>
+          <t>絶縁抵抗1MΩ|絶縁抵抗 直流200V 1MΩ 配線設備 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,ダイヤル番号,ミニマムポーズ</t>
+          <t>ダイヤル番号16種類|押しボタンダイヤル ダイヤル番号 16種類 0-9 記号</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,電気的条件,光学的条件,直流電圧</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 直流電圧 電気的条件 光学的条件</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>IPを使用する専用通信回線設備等端末,アクセス制御</t>
+          <t>IPを使用する専用通信回線設備等端末|IPを使用する専用通信回線設備等端末 アクセス制御</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>IP電話端末,発信,応答,通信終了</t>
+          <t>IP電話端末発着信|IP電話端末 発信 応答 通信終了 メッセージ送出</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>絶対レベル,有効電力,デシベル,端末設備等規則</t>
+          <t>絶対レベル|絶対レベル 有効電力 1mW デシベル 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>架空電線,強電流電線,足場金具,有線電気通信設備令</t>
+          <t>架空電線足場金具|架空電線 足場金具 地表1.8m 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>架空電線,鉄道横断,軌条面,有線電気通信設備令</t>
+          <t>架空電線鉄道横断|架空電線 鉄道軌道横断 軌条面6m 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,アクセス管理者,アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 アクセス管理者 アクセス制御機能</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>電子署名法,認証業務,電磁的記録</t>
+          <t>電子署名法|電子署名法 認証業務 電磁的記録</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>GE-PON,OLT,P2MPディスカバリ,マルチポイントMACコントロール</t>
+          <t>GE-PON|GE-PON OLT P2MPディスカバリ マルチポイントMAC,P2MPディスカバリ|P2MPディスカバリ GE-PON ONU自動発見</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>IP-PBX,ハードウェアタイプ,ソフトウェアタイプ,IPセントレックス</t>
+          <t>IP-PBX|IP-PBX ハードウェアタイプ ソフトウェアタイプ 比較,IPセントレックス|IPセントレックス クラウドPBX 通信事業者</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>MIMO,OFDM,空間分割多重,無線LAN</t>
+          <t>MIMO|MIMO 空間分割多重 複数アンテナ 無線LAN高速化,OFDM|OFDM MIMO 無線LAN 直交周波数分割多重</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>LPWA,LoRaWAN,SIGFOX,IoT,省電力通信</t>
+          <t>LPWA|LPWA Low Power Wide Area IoT 省電力 広域通信,LoRaWAN|LoRaWAN LPWA IoT 省電力無線</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>EMC,電磁エミッション,電磁障害,イミュニティ,JIS C 60050</t>
+          <t>電磁エミッション|電磁エミッション EMC 電磁障害 イミュニティ JIS C 60050</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>SS方式,シングルスター,PDS方式,PON,光ファイバ</t>
+          <t>SS方式|SS方式 シングルスター 光ファイバ 1対1 PDS方式比較</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>1000BASE-T,8B1Q4,4D-PAM5,符号化,UTP</t>
+          <t>8B1Q4|8B1Q4 1000BASE-T 4D-PAM5 符号化方式</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>MACアドレス,NIC,FCS,MACフレーム</t>
+          <t>MACアドレス|MACアドレス NIC 48ビット 固有アドレス,FCS|FCS フレームチェックシーケンス 誤り検出</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>トンネリング,デュアルスタック,IPv4,IPv6,カプセル化</t>
+          <t>トンネリング|トンネリング IPv6 IPv4 カプセル化 移行技術,デュアルスタック|デュアルスタック IPv4 IPv6 両方実装</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,L2ヘッダ,プリアンブル</t>
+          <t>EoMPLS|EoMPLS LER MPLS プリアンブル FCS 除去,LER|LER EoMPLS ラベルエッジルータ,MPLS|MPLS LER LSR ラベルスイッチング</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>スマーフ攻撃,DoS,ICMP,ブロードキャスト,IPスプーフィング</t>
+          <t>スマーフ攻撃|スマーフ攻撃 DoS ICMP ブロードキャスト IPスプーフィング</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>認証局,CA,デジタル証明書,公開鍵,秘密鍵</t>
+          <t>認証局|認証局 CA デジタル証明書 公開鍵 秘密鍵 署名</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>バッファオーバフロー,スタック,脆弱性</t>
+          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 スタック 入力サイズ 脆弱性</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>デフォルトアカウント,アカウント管理,セキュリティ</t>
+          <t>デフォルトアカウント|デフォルトアカウント 初期設定 無効化 セキュリティ対策</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>リスクマネジメント,残留リスク,リスク低減,ISMS</t>
+          <t>残留リスク|残留リスク リスクマネジメント 許容 ISMS</t>
         </is>
       </c>
     </row>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>挿入法,カットバック法,挿入損失,光コネクタ,JIS C 6823</t>
+          <t>挿入法|挿入法 光コネクタ 挿入損失測定 JIS C 6823,カットバック法|カットバック法 破壊試験 光ファイバ損失</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>JIS C 0303,図記号,複合アウトレット,情報用アウトレット</t>
+          <t>JIS C 0303|JIS C 0303 電気設備図記号 複合アウトレット</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>OTDR法,後方散乱光,光ファイバ損失,JIS C 6823</t>
+          <t>OTDR法|OTDR法 後方散乱光 光ファイバ損失 JIS C 6823,JIS C 6823|JIS C 6823 光ファイバ損失試験方法</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,UTPケーブル,心線配色</t>
+          <t>T568B|T568B RJ-45 心線配色 UTPケーブル</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスE,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 インタコネクト クラスE 水平ケーブル最大長</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>OTDR,ダミー光ファイバ,測定不能領域,後方散乱光</t>
+          <t>OTDR|OTDR ダミー光ファイバ 測定不能領域 後方散乱光</t>
         </is>
       </c>
     </row>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>FASコネクタ,単心光コネクタ,ドロップ光ファイバ,架空クロージャ</t>
+          <t>FASコネクタ|FASコネクタ 単心光コネクタ ドロップ光ファイバ 架空クロージャ</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>細径インドア光ケーブル,低摩擦,集合住宅,光配線</t>
+          <t>細径インドア光ケーブル|細径インドア光ケーブル 低摩擦 集合住宅 押し込み工法</t>
         </is>
       </c>
     </row>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>工程管理,出来形管理,施工管理,品質管理</t>
+          <t>工程管理|工程管理 出来形管理 施工管理 違い,出来形管理|出来形管理 工程管理 寸法数量 施工管理</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム クリティカルパス トータルフロート PERT</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>資格者証,工事担任者,罰金,養成課程,電気通信事業法</t>
+          <t>資格者証交付要件|資格者証 罰金以上 5年 養成課程 工事担任者法</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>自営電気通信設備,接続拒否,技術基準,電気通信事業法</t>
+          <t>自営電気通信設備接続拒否|自営電気通信設備 保持 経営困難 接続拒否 総務大臣</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>管理規程,基礎的電気通信役務,届出,電気通信事業法</t>
+          <t>管理規程届出|管理規程 事業開始前 届出 許可ではない 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>技術基準適合認定,表示,電気通信事業法</t>
+          <t>技術基準適合認定取消|技術基準適合認定 不適合 表示なしとみなす 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>重要通信,緊急通信,公共の利益,電気通信事業法</t>
+          <t>重要通信人命安全|重要通信 人命安全 火災 疫病 交通事故 緊急通信</t>
         </is>
       </c>
     </row>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>工事担任者,第一級デジタル通信,第一級アナログ通信,資格区分</t>
+          <t>第一級デジタル通信|第一級デジタル通信 デジタル伝送路設備 総合デジタル除く,第一級アナログ通信|第一級アナログ通信 アナログ伝送路設備 総合デジタル</t>
         </is>
       </c>
     </row>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>資格者証,再交付,返納,写真</t>
+          <t>資格者証再交付|資格者証 再交付 汚破損 返納 10日以内</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,移動電話用設備,総合デジタル通信用設備,認定番号</t>
+          <t>技術基準適合認定番号先頭文字|技術基準適合認定番号 先頭文字 移動電話A 総合デジタルC IP電話E</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>有線電気通信法,総務大臣,報告,立入検査</t>
+          <t>有線電気通信法立入検査|有線電気通信法 総務大臣 報告 立入検査</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>有線電気通信設備,設置の場所,変更届,2週間前</t>
+          <t>有線電気通信設備変更届|有線電気通信設備 設置の場所 変更届 2週間前</t>
         </is>
       </c>
     </row>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>IP電話端末,IP電話用設備,絶対レベル,有効電力,端末設備等規則</t>
+          <t>IP電話端末|IP電話端末 IP電話用設備のみ 接続 端末設備等規則,絶対レベル|絶対レベル 有効電力 1mW デシベル</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>通話機能,音響衝撃,鳴音,端末設備等規則</t>
+          <t>音響衝撃防止|通話機能 音響衝撃 過大 防止機能 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13919,7 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>配線設備,絶縁抵抗,直流200V,1MΩ</t>
+          <t>配線設備絶縁抵抗|配線設備 絶縁抵抗 直流200V 1MΩ以上</t>
         </is>
       </c>
     </row>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,呼出符号,空き周波数</t>
+          <t>識別符号空き周波数|識別符号 無線設備 空き周波数判定 通信路設定</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>絶縁抵抗,使用電圧,300V,0.4MΩ,0.2MΩ</t>
+          <t>絶縁抵抗値|絶縁抵抗 使用電圧300V以下0.2MΩ 300V超0.4MΩ</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>移動電話端末,発信要求信号,漏話減衰量,1500Hz</t>
+          <t>移動電話端末発信|移動電話端末 発信要求信号 漏話減衰量 1500Hz</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,信号送出時間,ミニマムポーズ,50ms</t>
+          <t>信号送出時間50ms|押しボタンダイヤル 信号送出時間50ms ミニマムポーズ30ms</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>分界点,接地抵抗,100オーム,端末設備</t>
+          <t>分界点接地抵抗|分界点 接地抵抗100オーム 端末設備</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>IP電話端末,通信終了メッセージ,2分以内,応答確認</t>
+          <t>IP電話端末通信終了|IP電話端末 応答確認 2分以内 通信終了メッセージ</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>総合デジタル通信用設備,自動再発信,チャネル切断</t>
+          <t>自動再発信総合デジタル|総合デジタル通信用設備 自動再発信 チャネル切断</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>架空電線,建造物,離隔距離,30センチメートル,有線電気通信設備令</t>
+          <t>架空電線建造物離隔|架空電線 建造物 離隔距離 30センチメートル以下禁止</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>強電流電線,重畳,分離,有線電気通信設備令</t>
+          <t>強電流電線重畳分離|強電流電線 重畳 分離 開閉 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>横断歩道橋,架空電線,3メートル,有線電気通信設備令</t>
+          <t>架空電線横断歩道橋|架空電線 横断歩道橋 路面3m以上 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,アクセス管理者,アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 アクセス制御機能 制限を免れる</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>電子署名法,特定認証業務,電磁的記録,電子署名</t>
+          <t>特定認証業務|特定認証業務 電子署名法 主務省令 本人のみ</t>
         </is>
       </c>
     </row>
@@ -15180,7 +15180,7 @@
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>10G-EPON,IEEE802.3av,XGS-PON,FEC,64B/66B</t>
+          <t>10G-EPON|10G-EPON IEEE802.3av XGS-PON FEC 64B/66B</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>カットアンドスルー,ストアアンドフォワード,イーサネットスイッチ</t>
+          <t>カットアンドスルー|カットアンドスルー ストアアンドフォワード スイッチ転送方式 比較</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>IEEE802.3bt,Type4,Class8,PoE,90W</t>
+          <t>IEEE802.3bt|IEEE802.3bt Type4 Class8 90W PoE 4対給電</t>
         </is>
       </c>
     </row>
@@ -15469,7 +15469,7 @@
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>IEEE802.11n,ブロックACK,MIMO,フレーム集約</t>
+          <t>ブロックACK|IEEE802.11n ブロックACK フレーム集約 スループット向上</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>SPD,バリスタ,過渡電圧抑制ダイオード,サージ防護</t>
+          <t>SPD|SPD サージ防護デバイス バリスタ 非線形素子</t>
         </is>
       </c>
     </row>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>NRZI,AMI,MLT-3,PAM-5,2値符号</t>
+          <t>NRZI|NRZI 2値符号 AMI MLT-3 PAM-5 比較</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>SS方式,HFC,PDS方式,PON,光ファイバ</t>
+          <t>SS方式|SS方式 HFC PDS方式 光ファイバ 1対1接続</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>IaaS,PaaS,SaaS,クラウドサービス</t>
+          <t>IaaS|IaaS PaaS SaaS クラウドサービス 比較</t>
         </is>
       </c>
     </row>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>ジッタバッファ,揺らぎ吸収,VoIP,音声品質</t>
+          <t>ジッタバッファ|ジッタバッファ 揺らぎ吸収 VoIP 音声品質 パケット到着遅延</t>
         </is>
       </c>
     </row>
@@ -16047,7 +16047,7 @@
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,ラベルスイッチング,ルーティング</t>
+          <t>EoMPLS|EoMPLS LER MPLS ラベルスイッチング ルーティング比較,LER|LER EoMPLS ラベルエッジルータ,LSR|LSR MPLS ラベルスイッチングルータ</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>SEOポイズニング,不正Webサイト,検索エンジン</t>
+          <t>SEOポイズニング|SEOポイズニング 不正Webサイト 検索エンジン悪用</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>チャレンジ・レスポンス,CHAP,ハイブリッド方式,認証</t>
+          <t>チャレンジ・レスポンス|チャレンジ・レスポンス CHAP 認証方式</t>
         </is>
       </c>
     </row>
@@ -16336,7 +16336,7 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>MACアドレスフィルタリング,ANY接続拒否,無線LAN,SSID</t>
+          <t>MACアドレスフィルタリング|MACアドレスフィルタリング ANY接続拒否 無線LAN SSID</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>IPsec,トランスポートモード,トンネルモード,VPN</t>
+          <t>IPsec|IPsec トランスポートモード トンネルモード VPN リモートアクセス</t>
         </is>
       </c>
     </row>
@@ -16529,7 +16529,7 @@
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>アンチパスバック,入退室管理,セキュリティ</t>
+          <t>アンチパスバック|アンチパスバック 入退室管理 再入室防止</t>
         </is>
       </c>
     </row>
@@ -16624,7 +16624,7 @@
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>光導通試験,SI形,GI形,励振,PINホトダイオード</t>
+          <t>光導通試験励振|光導通試験 励振用光ファイバ SI形 GI形 コア径</t>
         </is>
       </c>
     </row>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>POF,フッ素樹脂,アクリル樹脂,プラスチック光ファイバ</t>
+          <t>POF|POF プラスチック光ファイバ フッ素樹脂 アクリル樹脂 比較</t>
         </is>
       </c>
     </row>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>1000BASE-T,UTP,8心,カテゴリ5e,全二重</t>
+          <t>1000BASE-T|1000BASE-T UTP 8心全対 カテゴリ5e,1000BASE-TX|1000BASE-TX カテゴリ6 4心 1000BASE-T比較</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>反射減衰量,挿入損失,UTPケーブル,JIS X 5150</t>
+          <t>反射減衰量測定|反射減衰量 挿入損失 UTPケーブル 測定方法</t>
         </is>
       </c>
     </row>
@@ -17021,7 +17021,7 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>クロスコネクト,クラスE,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 クロスコネクト クラスE 水平ケーブル最大長</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>FASコネクタ,ターミネーションコネクタ,SC型,光キャビネット</t>
+          <t>FASコネクタ|FASコネクタ ターミネーションコネクタ SC型 光キャビネット</t>
         </is>
       </c>
     </row>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>反射減衰量,挿入損失,クラスC,JIS X 5150</t>
+          <t>JIS X 5150反射減衰量|JIS X 5150 反射減衰量 クラスC D E 適用</t>
         </is>
       </c>
     </row>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>融着接続,気泡,光ファイバカッタ,端面切断</t>
+          <t>融着接続気泡|融着接続 気泡 光ファイバカッタ 端面切断 やり直し</t>
         </is>
       </c>
     </row>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>設計図書,不整合,発注者,受注者,施工管理</t>
+          <t>設計図書不整合|設計図書 不整合 発注者 受注者 確認指示</t>
         </is>
       </c>
     </row>
@@ -17504,7 +17504,7 @@
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,フリーフロート,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム クリティカルパス フリーフロート PERT</t>
         </is>
       </c>
     </row>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>重要通信,相互接続,電気通信事業法</t>
+          <t>重要通信相互接続|重要通信 相互接続 電気通信事業者 連携</t>
         </is>
       </c>
     </row>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>重要通信,緊急通信,天災,選挙管理機関</t>
+          <t>重要通信緊急通信|重要通信 緊急通信 天災 選挙管理機関 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -17785,7 +17785,7 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>業務改善命令,重要通信,適切に配慮,電気通信事業法</t>
+          <t>業務改善命令重要通信|業務改善命令 重要通信 適切に配慮 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>管理規程,確実かつ安定的,電気通信事業法</t>
+          <t>管理規程確実安定|管理規程 確実かつ安定的 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,電波,電気通信事業法</t>
+          <t>端末設備接続拒否|端末設備 接続請求 電波 著しく不適当 拒否</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>工事担任者,第一級デジタル通信,総合デジタル通信用設備,資格区分</t>
+          <t>第一級デジタル通信|第一級デジタル通信 総合デジタル除く デジタル伝送路</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>資格者証,書換え交付,再交付,住所変更</t>
+          <t>資格者証書換え交付|資格者証 書換え交付 住所変更 再交付との違い</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,デジタルデータ伝送用設備,認定番号</t>
+          <t>技術基準適合認定番号D|技術基準適合認定番号 デジタルデータ伝送用設備 D</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>有線電気通信法,設置及び使用,秩序,公共の福祉</t>
+          <t>有線電気通信法目的|有線電気通信法 設置及び使用 秩序 公共の福祉</t>
         </is>
       </c>
     </row>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保,命令</t>
+          <t>有線電気通信法非常事態|有線電気通信法 非常事態 通信確保 命令</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,通話チャネル,制御チャネル,端末設備等規則</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 通話チャネル 制御チャネル 定義</t>
         </is>
       </c>
     </row>
@@ -18663,7 +18663,7 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>分界点,鳴音,事業用電気通信設備,端末設備等規則</t>
+          <t>分界点鳴音|分界点 鳴音 事業用電気通信設備 告示条件</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>事業用電気通信設備,識別機能,漏えい,端末設備等規則</t>
+          <t>事業用電気通信設備識別禁止|端末設備 事業用電気通信設備 漏えい 識別禁止</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>評価雑音電力,実効的雑音電力,マイナス64dB,端末設備等規則</t>
+          <t>評価雑音電力値|評価雑音電力 実効的雑音電力 マイナス64dB マイナス58dB</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>配線設備,強電流電線,有線電気通信設備令,告示</t>
+          <t>配線設備強電流電線|配線設備 強電流電線 有線電気通信設備令 告示</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,ダイヤル番号,16種類,ミニマムポーズ</t>
+          <t>ダイヤル番号16種類|押しボタンダイヤル ダイヤル番号 16種類 ミニマムポーズ</t>
         </is>
       </c>
     </row>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>IP移動電話端末,128秒,通信終了メッセージ,応答確認</t>
+          <t>IP移動電話端末128秒|IP移動電話端末 128秒 通信終了メッセージ 応答確認</t>
         </is>
       </c>
     </row>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,漏話減衰量,1500Hz,70dB</t>
+          <t>漏話減衰量1500Hz|専用通信回線設備等端末 漏話減衰量 1500Hz 70dB</t>
         </is>
       </c>
     </row>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,直流電圧,電気的条件,光学的条件</t>
+          <t>専用通信回線設備等端末直流|専用通信回線設備等端末 直流電圧 電気的条件 光学的条件</t>
         </is>
       </c>
     </row>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>初期識別符号,変更を促す機能,アクセス制御,端末設備等規則</t>
+          <t>初期識別符号変更|初期識別符号 変更を促す機能 アクセス制御 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>音声周波,高周波,離隔距離,有線電気通信法</t>
+          <t>音声周波高周波定義|音声周波 200Hz超3500Hz以下 高周波 3500Hz超 有線電気通信法</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>足場金具,1.8メートル,架空電線,有線電気通信設備令</t>
+          <t>足場金具1.8m|足場金具 地表1.8メートル未満禁止 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>架空電線,支持物,強電流電線,1メートル,有線電気通信設備令</t>
+          <t>架空電線支持物離隔|架空電線 支持物 強電流電線 1メートル以上 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>アクセス管理者,動作を管理する者,不正アクセス禁止法</t>
+          <t>アクセス管理者動作管理|アクセス管理者 動作を管理する者 不正アクセス禁止法</t>
         </is>
       </c>
     </row>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>電子署名法,流通及び情報処理,公共の福祉</t>
+          <t>電子署名法流通|電子署名法 流通及び情報処理 公共の福祉</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20019,7 @@
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>GE-PON,OLT,TDMA,P2MPディスカバリ,DBA</t>
+          <t>GE-PON|GE-PON OLT TDMA P2MPディスカバリ DBA,DBA|DBA動的帯域割当 GE-PON 上り帯域制御</t>
         </is>
       </c>
     </row>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>クラウド型PBX,SIP,アプリケーション層,IP電話</t>
+          <t>クラウド型PBX|クラウド型PBX SIP IPセントレックス 比較,SIPアプリケーション層|SIP アプリケーション層 インターネット層 違い</t>
         </is>
       </c>
     </row>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>PoE,IEEE802.3at,Type1,Class0,350mA</t>
+          <t>IEEE802.3at Type1|IEEE802.3at Type1 Class0 350mA PoE</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>IEEE802.11n,IEEE802.11ax,Wi-Fi 6,2.4GHz,5GHz</t>
+          <t>IEEE802.11n|IEEE802.11n 2.4GHz 5GHz 両対応 IEEE802.11ax,IEEE802.11ax|IEEE802.11ax Wi-Fi6 2.4GHz 5GHz 6GHz</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>コモンモードノイズ,ノーマルモードノイズ,誘導雑音,EMC</t>
+          <t>コモンモードノイズ|コモンモードノイズ ノーマルモードノイズ 誘導雑音 違い</t>
         </is>
       </c>
     </row>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>10GBASE-LR,64B/66B,8B/10B,8B1Q4,符号化</t>
+          <t>10GBASE-LR|10GBASE-LR 64B/66B 符号化方式,64B/66B|64B/66B 10GBASE-LR スクランブル 符号化</t>
         </is>
       </c>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>FM一括変換方式,CATV,光強度変調,3GHz</t>
+          <t>FM一括変換方式|FM一括変換方式 CATV 3GHz 光強度変調 映像伝送</t>
         </is>
       </c>
     </row>
@@ -20687,7 +20687,7 @@
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>10GBASE-SR,850nm,マルチモード光ファイバ,10GBASE-LR</t>
+          <t>10GBASE-SR|10GBASE-SR 850nm マルチモード 10GBASE-LR比較</t>
         </is>
       </c>
     </row>
@@ -20787,7 +20787,7 @@
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>ICMPv6,IPv6,パケット分割,PMTUD</t>
+          <t>ICMPv6|ICMPv6 IPv6 必須 PMTUD パケット分割</t>
         </is>
       </c>
     </row>
@@ -20880,7 +20880,7 @@
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,L2ヘッダ,プリアンブル</t>
+          <t>EoMPLS|EoMPLS LER MPLS L2ヘッダ プリアンブル FCS,MPLS|MPLS LER LSR ラベルスイッチング</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>バックドア,フィッシング,ボット,スキミング,マルウェア</t>
+          <t>バックドア|バックドア マルウェア 再侵入 隠れた経路,フィッシング|フィッシング 偽サイト ID パスワード詐取 スキミング比較</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>IPsec,トンネルモード,トランスポートモード,VPN,PPP</t>
+          <t>IPsec|IPsec トンネルモード トランスポートモード VPN</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>パケットフィルタリング,ポートスキャン,ファイアウォール</t>
+          <t>パケットフィルタリング|パケットフィルタリング ポートスキャン対策 ファイアウォール</t>
         </is>
       </c>
     </row>
@@ -21272,7 +21272,7 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>IPS,IDS,不正アクセス検知,自動遮断</t>
+          <t>IPS|IPS IDS 不正アクセス検知 自動遮断 違い</t>
         </is>
       </c>
     </row>
@@ -21372,7 +21372,7 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>アンチパスバック,ゾーニング,入退室管理,セキュリティ</t>
+          <t>アンチパスバック|アンチパスバック 入退室管理 再入室防止,ゾーニング|ゾーニング セキュリティ区画 ハウジングとの違い</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>融着接続,スクリーニング試験,引張試験,光ファイバ</t>
+          <t>融着接続スクリーニング|融着接続 スクリーニング試験 引張試験 曲げ試験ではない</t>
         </is>
       </c>
     </row>
@@ -21573,7 +21573,7 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>1000BASE-TX,1000BASE-T,カテゴリ6,カテゴリ5e,UTP</t>
+          <t>1000BASE-TX|1000BASE-TX カテゴリ6 1000BASE-T比較,1000BASE-T|1000BASE-T カテゴリ5e 8心全対</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>交差接続,クロスコネクト,光配線盤,ジャンパコード</t>
+          <t>交差接続|交差接続 クロスコネクト 光配線盤 ジャンパコード</t>
         </is>
       </c>
     </row>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,心線配色,UTPケーブル</t>
+          <t>T568B|T568B RJ-45 ピン2番 橙色 心線配色</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスE,水平ケーブル,81.5m,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 インタコネクト クラスE 81.5m 15m</t>
         </is>
       </c>
     </row>
@@ -21954,7 +21954,7 @@
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>光キャビネット,光ローゼット,ドロップ光ファイバ,インドア光ファイバ</t>
+          <t>光キャビネット|光キャビネット 光ローゼット ドロップ光ファイバ インドア光ファイバ 違い</t>
         </is>
       </c>
     </row>
@@ -22046,7 +22046,7 @@
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>STP,IEEE802.1D,スパニングツリー,ループ防止</t>
+          <t>STP|STP IEEE802.1D スパニングツリー ループ防止</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>OTDR,ダイナミックレンジ,後方散乱光,パルスパワー</t>
+          <t>OTDRダイナミックレンジ|OTDR ダイナミックレンジ 後方散乱光 パルスパワー 増加</t>
         </is>
       </c>
     </row>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>施工計画書,現場代理人,監督員,受注者,発注者</t>
+          <t>施工計画書|施工計画書 受注者作成 発注者監督員 工事管理</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,PERT</t>
+          <t>クリティカルパス|クリティカルパス トータルフロート アローダイアグラム PERT</t>
         </is>
       </c>
     </row>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>資格者証,工事担任者,罰金,5年,養成課程</t>
+          <t>資格者証交付要件|資格者証 罰金以上 5年 養成課程 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>管理規程,事業開始前,届出,技術基準,電気通信事業法</t>
+          <t>管理規程事業開始前|管理規程 事業開始前 届出 許可ではない 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22628,7 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>自営電気通信設備,保持,経営上困難,接続拒否,総務大臣</t>
+          <t>自営電気通信設備保持|自営電気通信設備 保持 経営困難 接続拒否 総務大臣認定</t>
         </is>
       </c>
     </row>
@@ -22718,7 +22718,7 @@
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>技術基準適合認定,表示,総務大臣,公示</t>
+          <t>技術基準適合認定公示|技術基準適合認定 表示なしとみなす 総務大臣</t>
         </is>
       </c>
     </row>
@@ -22811,7 +22811,7 @@
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>重要通信,公共の利益,緊急通信,人命の安全</t>
+          <t>重要通信人命|重要通信 公共の利益 人命安全 火災 疫病</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>工事担任者,第一級アナログ通信,アナログ伝送路設備,総合デジタル通信用設備</t>
+          <t>第一級アナログ通信|第一級アナログ通信 アナログ伝送路設備 総合デジタル通信用設備</t>
         </is>
       </c>
     </row>
@@ -23010,7 +23010,7 @@
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>資格者証,再交付,失った,技術の向上,端末設備等</t>
+          <t>資格者証再交付失った|資格者証 再交付 失った 写真1枚 資格者証添付不要</t>
         </is>
       </c>
     </row>
@@ -23110,7 +23110,7 @@
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,IP電話用設備,E,認定番号</t>
+          <t>技術基準適合認定番号E|技術基準適合認定番号 IP電話用設備 E</t>
         </is>
       </c>
     </row>
@@ -23202,7 +23202,7 @@
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>有線電気通信法,設置及び使用,秩序,公共の福祉</t>
+          <t>有線電気通信法目的|有線電気通信法 設置及び使用 秩序 公共の福祉</t>
         </is>
       </c>
     </row>
@@ -23294,7 +23294,7 @@
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保,使用させ,接続</t>
+          <t>有線電気通信法非常事態|有線電気通信法 非常事態 他の者に使用させ 接続</t>
         </is>
       </c>
     </row>
@@ -23399,7 +23399,7 @@
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,デジタルデータ伝送用設備,端末設備等規則</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 デジタルデータ伝送用設備 接続</t>
         </is>
       </c>
     </row>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>直流回路,アナログ電話用設備,交換設備,端末設備等規則</t>
+          <t>直流回路|直流回路 アナログ電話用設備 交換設備 動作制御</t>
         </is>
       </c>
     </row>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>分界点,事業用電気通信設備,端末設備,接続方式</t>
+          <t>分界点事業用|分界点 事業用電気通信設備 端末設備 接続方式</t>
         </is>
       </c>
     </row>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>絶縁抵抗,使用電圧,300V,0.2MΩ,端末設備等規則</t>
+          <t>絶縁抵抗300V以下|絶縁抵抗 300V以下 0.2MΩ 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -23786,7 +23786,7 @@
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>配線設備,絶縁抵抗,直流200V,1MΩ,告示</t>
+          <t>配線設備絶縁抵抗200V|配線設備 絶縁抵抗 直流200V 1MΩ 告示</t>
         </is>
       </c>
     </row>
@@ -23891,7 +23891,7 @@
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>ミニマムポーズ,押しボタンダイヤル,高群周波数,信号周波数偏差</t>
+          <t>ミニマムポーズ最小値|ミニマムポーズ 最小値 押しボタンダイヤル 高群周波数</t>
         </is>
       </c>
     </row>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>アナログ電話端末,緊急通報,警察機関,海上保安,消防機関</t>
+          <t>アナログ電話端末緊急通報|アナログ電話端末 緊急通報 警察 海上保安 消防</t>
         </is>
       </c>
     </row>
@@ -24088,7 +24088,7 @@
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>IP電話端末,自動再発信,3分間,2回以内</t>
+          <t>IP電話端末自動再発信|IP電話端末 自動再発信 3分間 2回以内</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>移動電話端末,漏話減衰量,1500Hz,70dB</t>
+          <t>移動電話端末漏話|移動電話端末 漏話減衰量 1500Hz 70dB</t>
         </is>
       </c>
     </row>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,ソフトウェア更新,アクセス制御,電力停止</t>
+          <t>専用通信回線設備等端末ソフト|専用通信回線設備等端末 ソフトウェア更新 アクセス制御 電力停止</t>
         </is>
       </c>
     </row>
@@ -24363,7 +24363,7 @@
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>有線電気通信設備,絶縁機能,避雷機能,保安機能</t>
+          <t>有線電気通信設備保安|有線電気通信設備 絶縁機能 避雷機能 保安機能</t>
         </is>
       </c>
     </row>
@@ -24468,7 +24468,7 @@
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>電線,強電流電線,重畳,有線電気通信法</t>
+          <t>電線定義|電線 強電流電線 重畳 除く 有線電気通信法</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>屋内電線,高圧,強電流ケーブル,離隔距離,隔壁</t>
+          <t>屋内電線強電流ケーブル|屋内電線 強電流ケーブル 離隔距離 隔壁 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>アクセス管理者,アクセス制御機能,有効性,高度化,不正アクセス禁止法</t>
+          <t>アクセス制御機能有効性|アクセス管理者 アクセス制御機能 有効性検証 高度化 不正アクセス禁止法</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>電子署名法,真正に成立,推定,電磁的記録</t>
+          <t>電子署名真正成立|電子署名法 本人による署名 真正に成立 推定</t>
         </is>
       </c>
     </row>
@@ -24829,7 +24829,7 @@
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>10G-EPON,GE-PON,デュアルレートバースト受信器,OLT</t>
+          <t>デュアルレートバースト受信器|デュアルレートバースト受信器 10G-EPON GE-PON 混在</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>IPセントレックス,IP-PBX,ハードウェアタイプ,ソフトウェアタイプ</t>
+          <t>IPセントレックス|IPセントレックス IP-PBX ハードウェアタイプ ソフトウェアタイプ</t>
         </is>
       </c>
     </row>
@@ -25022,7 +25022,7 @@
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>IEEE802.11ax,Wi-Fi 6,6GHz,ISMバンド,気象レーダ</t>
+          <t>IEEE802.11ax 6GHz|IEEE802.11ax Wi-Fi6 6GHz ISMバンド 気象レーダ</t>
         </is>
       </c>
     </row>
@@ -25115,7 +25115,7 @@
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>IEEE802.3bt,Type4,Class8,90W,PoE</t>
+          <t>IEEE802.3bt Type4|IEEE802.3bt Type4 Class8 90W 4対給電</t>
         </is>
       </c>
     </row>
@@ -25208,7 +25208,7 @@
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>誘導雷サージ,電磁誘導,静電誘導,過電圧,雷保護</t>
+          <t>誘導雷サージ|誘導雷サージ 電磁誘導 静電誘導 過電圧 雷保護</t>
         </is>
       </c>
     </row>
@@ -25301,7 +25301,7 @@
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>4D-PAM5,1000BASE-T,PAM,5値,符号化</t>
+          <t>4D-PAM5|4D-PAM5 1000BASE-T 5値 4次元 符号化</t>
         </is>
       </c>
     </row>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>CWDM,DWDM,波長多重,20nm,アクセス系</t>
+          <t>CWDM|CWDM DWDM 波長多重 隣接波長間隔20nm アクセス系</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="W260" t="inlineStr">
         <is>
-          <t>SDN,NFV,データプレーン,コントロールプレーン</t>
+          <t>SDN|SDN NFV データプレーン コントロールプレーン 分離</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>トンネリング,デュアルスタック,IPv4,IPv6,カプセル化</t>
+          <t>トンネリング|トンネリング デュアルスタック IPv4 IPv6 移行技術</t>
         </is>
       </c>
     </row>
@@ -25685,7 +25685,7 @@
       </c>
       <c r="W262" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,LSR,MPLS,ラベルスイッチング</t>
+          <t>EoMPLS|EoMPLS LER LSR MPLS ラベルスイッチング ルーティング比較</t>
         </is>
       </c>
     </row>
@@ -25778,7 +25778,7 @@
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>OP25B,SPF,DKIM,迷惑メール対策,25番ポート</t>
+          <t>OP25B|OP25B 迷惑メール対策 25番ポート SPF DKIM</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="W264" t="inlineStr">
         <is>
-          <t>デジタル署名,公開鍵暗号,送信否認防止,メッセージ認証</t>
+          <t>デジタル署名送信否認|デジタル署名 公開鍵暗号 送信否認防止 共通鍵との違い</t>
         </is>
       </c>
     </row>
@@ -25978,7 +25978,7 @@
       </c>
       <c r="W265" t="inlineStr">
         <is>
-          <t>チェックサム,ウイルス,改変検出,メールサーバ</t>
+          <t>チェックサム|チェックサム ウイルス 改変検出 名前特定不可</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26069,7 @@
       </c>
       <c r="W266" t="inlineStr">
         <is>
-          <t>サニタイジング,XSS,クロスサイトスクリプティング,HTMLタグ</t>
+          <t>サニタイジング|サニタイジング XSS HTMLタグ JavaScript 無効化</t>
         </is>
       </c>
     </row>
@@ -26162,7 +26162,7 @@
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>ベースラインアプローチ,詳細リスク分析,リスク分析手法,ISMS</t>
+          <t>ベースラインアプローチ|ベースラインアプローチ 詳細リスク分析 ISMS リスク分析手法比較</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="W268" t="inlineStr">
         <is>
-          <t>光導通試験,SI形,GI形,励振,コア径</t>
+          <t>光導通試験|光導通試験 励振用光ファイバ SI形 GI形 コア径,PINホトダイオード|PINホトダイオード 光検出器 受感面 大きくする</t>
         </is>
       </c>
     </row>
@@ -26355,7 +26355,7 @@
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>PoE,オルタナティブA,オルタナティブB,ピン4・5・7・8</t>
+          <t>PoEオルタナティブB|PoE オルタナティブB ピン4 5 7 8 予備ペア</t>
         </is>
       </c>
     </row>
@@ -26448,7 +26448,7 @@
       </c>
       <c r="W270" t="inlineStr">
         <is>
-          <t>光ファイバケーブル,けん引速度,20メートル,OITDA</t>
+          <t>光ファイバけん引速度|光ファイバケーブル けん引速度 20メートル以下 OITDA</t>
         </is>
       </c>
     </row>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="W271" t="inlineStr">
         <is>
-          <t>プライベートIPアドレス,クラスB,172.16,IPv4</t>
+          <t>プライベートIPアドレス|プライベートIPアドレス クラスB 172.16 範囲</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="W272" t="inlineStr">
         <is>
-          <t>クロスコネクト,クラスF,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 クロスコネクト クラスF 水平ケーブル最大長</t>
         </is>
       </c>
     </row>
@@ -26732,7 +26732,7 @@
       </c>
       <c r="W273" t="inlineStr">
         <is>
-          <t>CSMA/CD,全二重,半二重,オートネゴシエーション,衝突</t>
+          <t>CSMA/CD全二重|CSMA/CD 全二重 半二重 衝突 オートネゴシエーション,全二重通信|全二重通信 CSMA/CD 衝突なし 送受信独立チャネル</t>
         </is>
       </c>
     </row>
@@ -26825,7 +26825,7 @@
       </c>
       <c r="W274" t="inlineStr">
         <is>
-          <t>MPOコネクタ,多心光コネクタ,プッシュプル,12心,24心</t>
+          <t>MPOコネクタ|MPOコネクタ 多心光コネクタ 12心 24心 プッシュプル</t>
         </is>
       </c>
     </row>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>細径インドア光ケーブル,低摩擦,集合住宅,押し込み工法</t>
+          <t>細径インドア光ケーブル|細径インドア光ケーブル 低摩擦 集合住宅 押し込み工法</t>
         </is>
       </c>
     </row>
@@ -27024,7 +27024,7 @@
       </c>
       <c r="W276" t="inlineStr">
         <is>
-          <t>KY活動,危険予知,ほう・れん・そう,安全管理</t>
+          <t>KY活動|KY活動 危険予知 ほう・れん・そう 安全管理 違い</t>
         </is>
       </c>
     </row>
@@ -27125,7 +27125,7 @@
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム クリティカルパス トータルフロート PERT</t>
         </is>
       </c>
     </row>
@@ -27226,7 +27226,7 @@
       </c>
       <c r="W278" t="inlineStr">
         <is>
-          <t>技術基準,責任の分界,設置の場所,電気通信事業法</t>
+          <t>技術基準責任分界|技術基準 責任の分界 設置の場所 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="W279" t="inlineStr">
         <is>
-          <t>業務改善命令,修理,支障,電気通信事業法</t>
+          <t>業務改善命令修理|業務改善命令 修理 支障 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -27407,7 +27407,7 @@
       </c>
       <c r="W280" t="inlineStr">
         <is>
-          <t>技術基準,修理,改造,使用制限,総務大臣</t>
+          <t>技術基準修理改造|技術基準 修理 改造 使用制限 総務大臣</t>
         </is>
       </c>
     </row>
@@ -27500,7 +27500,7 @@
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,電波,電気通信事業法</t>
+          <t>端末設備接続拒否電波|端末設備 接続請求 電波 著しく不適当</t>
         </is>
       </c>
     </row>
@@ -27595,7 +27595,7 @@
       </c>
       <c r="W282" t="inlineStr">
         <is>
-          <t>重要通信,気象,水象,生活基盤,緊急通信</t>
+          <t>重要通信生活基盤|重要通信 気象 水象 生活基盤 緊急通信</t>
         </is>
       </c>
     </row>
@@ -27685,7 +27685,7 @@
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>工事担任者,第二級デジタル通信,1Gbps,第一級アナログ,資格区分</t>
+          <t>第二級デジタル通信|第二級デジタル通信 1Gbps以下 インターネット接続</t>
         </is>
       </c>
     </row>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="W284" t="inlineStr">
         <is>
-          <t>資格者証,書換え交付,返納,10日以内</t>
+          <t>資格者証書換え交付|資格者証 書換え交付 住所変更 返納10日以内</t>
         </is>
       </c>
     </row>
@@ -27889,7 +27889,7 @@
       </c>
       <c r="W285" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,総合デジタル通信用設備,C,認定番号</t>
+          <t>技術基準適合認定番号C|技術基準適合認定番号 総合デジタル通信用設備 C</t>
         </is>
       </c>
     </row>
@@ -27994,7 +27994,7 @@
       </c>
       <c r="W286" t="inlineStr">
         <is>
-          <t>有線電気通信法,設置及び使用,秩序,公共の福祉</t>
+          <t>有線電気通信法|有線電気通信法 設置及び使用 秩序 公共の福祉</t>
         </is>
       </c>
     </row>
@@ -28086,7 +28086,7 @@
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>有線電気通信設備,本邦外,総務大臣,許可</t>
+          <t>有線電気通信設備本邦外|有線電気通信設備 本邦外 総務大臣 許可</t>
         </is>
       </c>
     </row>
@@ -28192,7 +28192,7 @@
       </c>
       <c r="W288" t="inlineStr">
         <is>
-          <t>IP電話端末,IP電話用設備,デジタルデータ伝送用設備,端末設備等規則</t>
+          <t>IP電話端末接続|IP電話端末 IP電話用設備のみ デジタルデータ伝送用設備ではない</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>端末設備,事業用電気通信設備,識別機能,鳴音</t>
+          <t>端末設備識別鳴音|端末設備 事業用電気通信設備 漏えい 識別禁止 鳴音</t>
         </is>
       </c>
     </row>
@@ -28392,7 +28392,7 @@
       </c>
       <c r="W290" t="inlineStr">
         <is>
-          <t>接地抵抗,100オーム,絶縁耐力,端末設備等規則</t>
+          <t>接地抵抗100オーム|接地抵抗 100オーム以下 端末設備 金属筐体</t>
         </is>
       </c>
     </row>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>評価雑音電力,マイナス64dB,マイナス58dB,端末設備等規則</t>
+          <t>評価雑音電力マイナス58dB|評価雑音電力 マイナス64dB マイナス58dB 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -28591,7 +28591,7 @@
       </c>
       <c r="W292" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,交換設備,端末設備等規則</t>
+          <t>識別符号無線設備|識別符号 無線設備 交換設備ではない 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -28690,7 +28690,7 @@
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>信号周波数偏差,±1.5%,ミニマムポーズ,周期,押しボタンダイヤル</t>
+          <t>信号周波数偏差|信号周波数偏差 ±1.5% ミニマムポーズ 周期 押しボタンダイヤル</t>
         </is>
       </c>
     </row>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="W294" t="inlineStr">
         <is>
-          <t>移動電話端末,漏話減衰量,自動再発信,2回以内,3分</t>
+          <t>移動電話端末自動再発信|移動電話端末 漏話減衰量 自動再発信 2回以内 3分</t>
         </is>
       </c>
     </row>
@@ -28881,7 +28881,7 @@
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>IP電話端末,送出電力,マイナス3dBm,アナログ電話</t>
+          <t>IP電話端末送出電力|IP電話端末 送出電力 マイナス3dBm アナログ電話</t>
         </is>
       </c>
     </row>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="W296" t="inlineStr">
         <is>
-          <t>IP移動電話端末,128秒,通信終了,送信タイミング,総務大臣</t>
+          <t>IP移動電話端末128秒|IP移動電話端末 128秒 送信タイミング 総務大臣告示</t>
         </is>
       </c>
     </row>
@@ -29073,7 +29073,7 @@
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,アクセス制御,変更,デジタルデータ伝送用設備</t>
+          <t>専用通信回線設備等端末変更|専用通信回線設備等端末 アクセス制御 設定変更</t>
         </is>
       </c>
     </row>
@@ -29178,7 +29178,7 @@
       </c>
       <c r="W298" t="inlineStr">
         <is>
-          <t>絶縁電線,保護物,音声周波,高周波,有線電気通信法</t>
+          <t>絶縁電線定義|絶縁電線 絶縁物のみ 保護物含まず 有線電気通信法</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>足場金具,1.8メートル,架空電線,離隔距離,30センチメートル</t>
+          <t>足場金具1.8m|足場金具 地表1.8メートル未満禁止 架空電線 離隔距離30cm</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="W300" t="inlineStr">
         <is>
-          <t>架空電線,道路上,5メートル,有線電気通信設備令</t>
+          <t>架空電線道路上|架空電線 道路上 5メートル以上 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -29461,7 +29461,7 @@
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,電子計算機,犯罪の防止,アクセス制御</t>
+          <t>不正アクセス禁止法電子計算機|不正アクセス禁止法 電子計算機 犯罪防止 アクセス制御</t>
         </is>
       </c>
     </row>
@@ -29553,7 +29553,7 @@
       </c>
       <c r="W302" t="inlineStr">
         <is>
-          <t>特定認証業務,電子署名法,本人,主務省令</t>
+          <t>特定認証業務|特定認証業務 電子署名法 本人のみ 主務省令</t>
         </is>
       </c>
     </row>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>GE-PON,OLT,TDMA,LLID,DBA,P2MPディスカバリ</t>
+          <t>GE-PON|GE-PON OLT TDMA LLID DBA P2MPディスカバリ,DBA|DBA動的帯域割当 GE-PON OLT 上り帯域</t>
         </is>
       </c>
     </row>
@@ -29751,7 +29751,7 @@
       </c>
       <c r="W304" t="inlineStr">
         <is>
-          <t>SIPサーバ,レジストラ,プロキシサーバ,リダイレクトサーバ,UAC</t>
+          <t>SIPサーバ|SIPサーバ レジストラ プロキシ リダイレクト UAC 比較,レジストラ|レジストラ SIPサーバ 登録要求 REGISTER メッセージ</t>
         </is>
       </c>
     </row>
@@ -29844,7 +29844,7 @@
       </c>
       <c r="W305" t="inlineStr">
         <is>
-          <t>IEEE802.11ax,Wi-Fi 6,OFDMA,多元接続,2.4GHz,5GHz</t>
+          <t>OFDMA|OFDMA IEEE802.11ax Wi-Fi6 時分割 サブキャリア</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="W306" t="inlineStr">
         <is>
-          <t>PoE,IEEE802.3at,Type1,Class0,350mA,PSE</t>
+          <t>IEEE802.3at Type1|IEEE802.3at Type1 Class0 350mA 44-57V PSE</t>
         </is>
       </c>
     </row>
@@ -30030,7 +30030,7 @@
       </c>
       <c r="W307" t="inlineStr">
         <is>
-          <t>等電位ボンディング,SPD,雷保護,JIS C 5381</t>
+          <t>等電位ボンディング|等電位ボンディング SPD 雷保護 電位差低減 JIS C 5381</t>
         </is>
       </c>
     </row>
@@ -30123,7 +30123,7 @@
       </c>
       <c r="W308" t="inlineStr">
         <is>
-          <t>10GBASE-LR,64B/66B,8B/10B,符号化,スクランブル</t>
+          <t>10GBASE-LR|10GBASE-LR 64B/66B 符号化方式 スクランブル</t>
         </is>
       </c>
     </row>
@@ -30213,7 +30213,7 @@
       </c>
       <c r="W309" t="inlineStr">
         <is>
-          <t>FTTB,VDSL,PDS方式,PON,集合住宅</t>
+          <t>FTTB|FTTB VDSL 集合住宅 光ファイバ 既設電話線,VDSL|VDSL FTTB 集合住宅 既設電話線 高速伝送</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="W310" t="inlineStr">
         <is>
-          <t>NFV,SDN,仮想化,ルータ,ファイアウォール</t>
+          <t>NFV|NFV SDN 仮想化 ルータ ファイアウォール汎用サーバ</t>
         </is>
       </c>
     </row>
@@ -30399,7 +30399,7 @@
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>ホップリミット,IPv6,TTL,ルータ,パケット破棄</t>
+          <t>ホップリミット|ホップリミット IPv6 TTL IPv4 ルータ パケット破棄</t>
         </is>
       </c>
     </row>
@@ -30489,7 +30489,7 @@
       </c>
       <c r="W312" t="inlineStr">
         <is>
-          <t>MACアドレス,NIC,FCS,MACフレーム,48ビット</t>
+          <t>MACアドレス|MACアドレス NIC 48ビット FCS フレーム誤り検出</t>
         </is>
       </c>
     </row>
@@ -30582,7 +30582,7 @@
       </c>
       <c r="W313" t="inlineStr">
         <is>
-          <t>バッファオーバフロー,スタック,任意コード実行,脆弱性</t>
+          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 スタック 任意コード実行 脆弱性</t>
         </is>
       </c>
     </row>
@@ -30675,7 +30675,7 @@
       </c>
       <c r="W314" t="inlineStr">
         <is>
-          <t>バイオメトリクス,本人拒否率,他人受入率,しきい値,認証</t>
+          <t>バイオメトリクス認証|バイオメトリクス認証 本人拒否率 他人受入率 しきい値</t>
         </is>
       </c>
     </row>
@@ -30775,7 +30775,7 @@
       </c>
       <c r="W315" t="inlineStr">
         <is>
-          <t>UNIX,root権限,アクセス権限,OS,セキュリティ</t>
+          <t>UNIX root権限|UNIX root権限 アクセス権限 OS セキュリティ</t>
         </is>
       </c>
     </row>
@@ -30868,7 +30868,7 @@
       </c>
       <c r="W316" t="inlineStr">
         <is>
-          <t>最小特権の原則,アクセス権限,セキュリティ設計</t>
+          <t>最小特権の原則|最小特権の原則 アクセス権限 セキュリティ設計</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="W317" t="inlineStr">
         <is>
-          <t>リスク特定,リスク分析,リスクレベル,ISMS,JIS Q 27001</t>
+          <t>リスク特定|リスク特定 リスク分析 リスクレベル 違い ISMS</t>
         </is>
       </c>
     </row>
@@ -31064,7 +31064,7 @@
       </c>
       <c r="W318" t="inlineStr">
         <is>
-          <t>光導通試験,SI形,GI形,励振,PINホトダイオード</t>
+          <t>光導通試験|光導通試験 SI形 GI形 コア径 PINホトダイオード</t>
         </is>
       </c>
     </row>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="W319" t="inlineStr">
         <is>
-          <t>JIS C 0303,図記号,情報用アウトレット,電気設備</t>
+          <t>JIS C 0303|JIS C 0303 電気設備図記号 情報用アウトレット</t>
         </is>
       </c>
     </row>
@@ -31233,7 +31233,7 @@
       </c>
       <c r="W320" t="inlineStr">
         <is>
-          <t>光ファイバケーブル,水平ラック,固定間隔,5メートル,OITDA</t>
+          <t>光ファイバ水平ラック固定|光ファイバケーブル 水平ラック 5メートル以下 固定 OITDA</t>
         </is>
       </c>
     </row>
@@ -31326,7 +31326,7 @@
       </c>
       <c r="W321" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,ピン8番,茶色,心線配色</t>
+          <t>T568B|T568B RJ-45 ピン8番 茶色 心線配色</t>
         </is>
       </c>
     </row>
@@ -31424,7 +31424,7 @@
       </c>
       <c r="W322" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスF,水平ケーブル,14m,JIS X 5150</t>
+          <t>JIS X 5150クラスF|JIS X 5150 インタコネクト クラスF 水平ケーブル最大長</t>
         </is>
       </c>
     </row>
@@ -31522,7 +31522,7 @@
       </c>
       <c r="W323" t="inlineStr">
         <is>
-          <t>リバースペア,スプリットペア,クロスペア,配線不良,UTPケーブル</t>
+          <t>リバースペア|リバースペア スプリットペア クロスペア 配線不良 UTPケーブル</t>
         </is>
       </c>
     </row>
@@ -31615,7 +31615,7 @@
       </c>
       <c r="W324" t="inlineStr">
         <is>
-          <t>反射減衰量,挿入損失,3.0dB,JIS X 5150</t>
+          <t>JIS X 5150反射減衰量|JIS X 5150 反射減衰量 3.0dB未満 参考とする</t>
         </is>
       </c>
     </row>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="W325" t="inlineStr">
         <is>
-          <t>光キャビネット,光ローゼット,ドロップ光ファイバ,インドア光ファイバ</t>
+          <t>光キャビネット|光キャビネット 光ローゼット ドロップ光ファイバ 屋外壁面</t>
         </is>
       </c>
     </row>
@@ -31801,7 +31801,7 @@
       </c>
       <c r="W326" t="inlineStr">
         <is>
-          <t>WBGT,暑さ指数,熱中症,湿球黒球温度,熱ストレス</t>
+          <t>WBGT|WBGT 暑さ指数 熱中症 湿球黒球温度 熱ストレス</t>
         </is>
       </c>
     </row>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="W327" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,フリーフロート,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム クリティカルパス トータルフロート フリーフロート PERT</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="W328" t="inlineStr">
         <is>
-          <t>業務改善命令,通信秘密,差別的取扱い,重要通信,電気通信事業法</t>
+          <t>業務改善命令対象|業務改善命令 通信秘密 差別的取扱い 重要通信 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>資格者証,工事担任者,罰金,5年,養成課程,総務大臣</t>
+          <t>資格者証交付要件|資格者証 罰金以上 5年 養成課程 総務大臣 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32196,7 @@
       </c>
       <c r="W330" t="inlineStr">
         <is>
-          <t>技術基準,責任の分界,設置の場所,電気通信事業法</t>
+          <t>技術基準責任分界|技術基準 責任の分界 設置の場所 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -32288,7 +32288,7 @@
       </c>
       <c r="W331" t="inlineStr">
         <is>
-          <t>端末設備,異常,電気通信役務,検査,電気通信事業法</t>
+          <t>端末設備異常検査|端末設備 異常 電気通信役務 検査 利用者</t>
         </is>
       </c>
     </row>
@@ -32380,7 +32380,7 @@
       </c>
       <c r="W332" t="inlineStr">
         <is>
-          <t>重要通信,生活基盤,水道,ガス,緊急通信</t>
+          <t>重要通信生活基盤|重要通信 生活基盤 水道 ガス 緊急通信</t>
         </is>
       </c>
     </row>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="W333" t="inlineStr">
         <is>
-          <t>工事担任者,第二級デジタル通信,1Gbps,64kbps,資格区分</t>
+          <t>第二級デジタル通信|第二級デジタル通信 1Gbps以下 64kbpsではない インターネット接続</t>
         </is>
       </c>
     </row>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="W334" t="inlineStr">
         <is>
-          <t>資格者証,返納,10日以内,知識及び技術,向上</t>
+          <t>資格者証返納10日|資格者証 返納 10日以内 知識及び技術 向上</t>
         </is>
       </c>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="W335" t="inlineStr">
         <is>
-          <t>技術基準適合認定,映像面,電磁的方法,表示方法</t>
+          <t>技術基準適合認定映像面|技術基準適合認定 映像面 電磁的方法 表示方法</t>
         </is>
       </c>
     </row>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="W336" t="inlineStr">
         <is>
-          <t>本邦外,有線電気通信設備,電気通信事業者,有線電気通信法</t>
+          <t>有線電気通信法本邦外|有線電気通信法 本邦外 電気通信事業者 設置</t>
         </is>
       </c>
     </row>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="W337" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保,命令</t>
+          <t>有線電気通信法非常事態|有線電気通信法 非常事態 通信確保 命令</t>
         </is>
       </c>
     </row>
@@ -32961,7 +32961,7 @@
       </c>
       <c r="W338" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,通話チャネル,制御チャネル,端末設備等規則</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 通話チャネル 制御チャネル 定義</t>
         </is>
       </c>
     </row>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="W339" t="inlineStr">
         <is>
-          <t>鳴音,電気的結合,音響的結合,光学的結合,端末設備等規則</t>
+          <t>鳴音電気的音響的結合|鳴音 電気的 音響的結合 光学的ではない 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="W340" t="inlineStr">
         <is>
-          <t>配線設備,事業用電気通信設備,損傷,告示,端末設備等規則</t>
+          <t>配線設備損傷防止|配線設備 事業用電気通信設備 損傷 告示 設置方法</t>
         </is>
       </c>
     </row>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="W341" t="inlineStr">
         <is>
-          <t>絶縁抵抗,0.2MΩ,0.4MΩ,300V,配線設備,1MΩ</t>
+          <t>絶縁抵抗各値|絶縁抵抗 0.2MΩ 0.4MΩ 300V 1MΩ 配線設備</t>
         </is>
       </c>
     </row>
@@ -33347,7 +33347,7 @@
       </c>
       <c r="W342" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,通信路,端末設備等規則</t>
+          <t>識別符号|識別符号 無線設備 通信路設定 照合</t>
         </is>
       </c>
     </row>
@@ -33448,7 +33448,7 @@
       </c>
       <c r="W343" t="inlineStr">
         <is>
-          <t>ミニマムポーズ,低群周波数,高群周波数,2周波電力差,押しボタンダイヤル</t>
+          <t>ミニマムポーズ最小値|ミニマムポーズ 最小値 低群周波数 高群周波数 2周波電力差</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="W344" t="inlineStr">
         <is>
-          <t>移動電話端末,応答を確認する信号,端末設備等規則</t>
+          <t>移動電話端末応答確認信号|移動電話端末 応答を確認する信号 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -33636,7 +33636,7 @@
       </c>
       <c r="W345" t="inlineStr">
         <is>
-          <t>IP電話端末,送出電力,マイナス3dBm,平均レベル</t>
+          <t>IP電話端末送出電力|IP電話端末 送出電力 マイナス3dBm 平均レベル</t>
         </is>
       </c>
     </row>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="W346" t="inlineStr">
         <is>
-          <t>IP移動電話端末,128秒,通信終了メッセージ,応答確認</t>
+          <t>IP移動電話端末128秒|IP移動電話端末 128秒 通信終了メッセージ 応答確認</t>
         </is>
       </c>
     </row>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="W347" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,アクセス制御,初期識別符号,ただし書き</t>
+          <t>専用通信回線設備等端末ただし書き|専用通信回線設備等端末 アクセス制御 初期識別符号 ただし書き</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="W348" t="inlineStr">
         <is>
-          <t>強電流電線,つり線,支線,導体,有線電気通信法</t>
+          <t>強電流電線定義|強電流電線 導体 つり線 支線 含まない 有線電気通信法</t>
         </is>
       </c>
     </row>
@@ -34028,7 +34028,7 @@
       </c>
       <c r="W349" t="inlineStr">
         <is>
-          <t>架空電線,電柱,安全係数,絶縁耐力,有線電気通信設備令</t>
+          <t>電柱安全係数|電柱 安全係数 絶縁耐力ではない 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="W350" t="inlineStr">
         <is>
-          <t>有線電気通信設備,絶縁電線,ケーブル,人体危害,有線電気通信設備令</t>
+          <t>有線電気通信設備設置|有線電気通信設備 絶縁電線 ケーブル 人体危害 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -34209,7 +34209,7 @@
       </c>
       <c r="W351" t="inlineStr">
         <is>
-          <t>アクセス管理者,不正アクセス禁止法,アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 アクセス管理者 アクセス制御機能</t>
         </is>
       </c>
     </row>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="W352" t="inlineStr">
         <is>
-          <t>電子署名,電磁的記録,作成,電子署名法</t>
+          <t>電子署名|電子署名 電磁的記録 作成者 電子署名法</t>
         </is>
       </c>
     </row>
@@ -34389,7 +34389,7 @@
       </c>
       <c r="W353" t="inlineStr">
         <is>
-          <t>10G-EPON,GE-PON,デュアルレートバースト受信器,OLT,ONU</t>
+          <t>デュアルレートバースト受信器|デュアルレートバースト受信器 10G-EPON GE-PON 混在接続</t>
         </is>
       </c>
     </row>
@@ -34482,7 +34482,7 @@
       </c>
       <c r="W354" t="inlineStr">
         <is>
-          <t>VoIPゲートウェイ,デジタル式PBX,IPネットワーク,変換装置</t>
+          <t>VoIPゲートウェイ|VoIPゲートウェイ デジタル式PBX IPネットワーク 変換</t>
         </is>
       </c>
     </row>
@@ -34588,7 +34588,7 @@
       </c>
       <c r="W355" t="inlineStr">
         <is>
-          <t>PoE,Type2,Class4,IEEE802.3at,34.2W,600mA</t>
+          <t>PoE Type2 Class4|PoE Type2 Class4 IEEE802.3at 34.2W 600mA</t>
         </is>
       </c>
     </row>
@@ -34681,7 +34681,7 @@
       </c>
       <c r="W356" t="inlineStr">
         <is>
-          <t>IEEE802.11n,IEEE802.11ax,2.4GHz,5GHz,Wi-Fi 6</t>
+          <t>IEEE802.11n|IEEE802.11n IEEE802.11ax 2.4GHz 5GHz 両対応</t>
         </is>
       </c>
     </row>
@@ -34774,7 +34774,7 @@
       </c>
       <c r="W357" t="inlineStr">
         <is>
-          <t>電圧スイッチング形SPD,SCR,サイリスタ,ガス入り放電管,サージ防護</t>
+          <t>電圧スイッチング形SPD|電圧スイッチング形SPD SCR サイリスタ ガス入り放電管 サージ防護</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="W358" t="inlineStr">
         <is>
-          <t>PCS,1000BASE-T,物理層,LLCサブレイヤ,PMA</t>
+          <t>PCS物理層|PCS 1000BASE-T 物理層 符号化 PMA PMD</t>
         </is>
       </c>
     </row>
@@ -34960,7 +34960,7 @@
       </c>
       <c r="W359" t="inlineStr">
         <is>
-          <t>SS方式,シングルスター,PDS方式,PON,光ファイバ</t>
+          <t>SS方式|SS方式 シングルスター PDS方式 PON 1対1</t>
         </is>
       </c>
     </row>
@@ -35053,7 +35053,7 @@
       </c>
       <c r="W360" t="inlineStr">
         <is>
-          <t>PaaS,SaaS,IaaS,クラウドサービス,ミドルウェア</t>
+          <t>PaaS|PaaS SaaS IaaS クラウドサービス ミドルウェア 比較</t>
         </is>
       </c>
     </row>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="W361" t="inlineStr">
         <is>
-          <t>IPv6,マルチキャスト,ff,リンクローカル,ユニークローカル</t>
+          <t>IPv6マルチキャスト|IPv6 マルチキャスト ff先頭8ビット リンクローカル ユニークローカル</t>
         </is>
       </c>
     </row>
@@ -35244,7 +35244,7 @@
       </c>
       <c r="W362" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,プリアンブル,SFD,FCS</t>
+          <t>EoMPLS|EoMPLS LER MPLS プリアンブル SFD FCS 除去,MPLS|MPLS LER LSR ラベルスイッチング</t>
         </is>
       </c>
     </row>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="W363" t="inlineStr">
         <is>
-          <t>パスワードリスト攻撃,辞書攻撃,不正ログイン,認証情報</t>
+          <t>パスワードリスト攻撃|パスワードリスト攻撃 辞書攻撃 不正ログイン 使い回し</t>
         </is>
       </c>
     </row>
@@ -35430,7 +35430,7 @@
       </c>
       <c r="W364" t="inlineStr">
         <is>
-          <t>シングルサインオン,SSO,リスクベース認証,CHAP,RADIUS</t>
+          <t>シングルサインオン|シングルサインオン SSO リスクベース認証 CHAP RADIUS</t>
         </is>
       </c>
     </row>
@@ -35520,7 +35520,7 @@
       </c>
       <c r="W365" t="inlineStr">
         <is>
-          <t>スニッフィング,TLS,SMTP,FTP,暗号化</t>
+          <t>スニッフィング対策TLS|スニッフィング TLS SMTP FTP 暗号化対策</t>
         </is>
       </c>
     </row>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="W366" t="inlineStr">
         <is>
-          <t>S/MIME,デジタル証明書,電子メール,暗号化,デジタル署名</t>
+          <t>S/MIME|S/MIME デジタル証明書 電子メール暗号化 デジタル署名</t>
         </is>
       </c>
     </row>
@@ -35719,7 +35719,7 @@
       </c>
       <c r="W367" t="inlineStr">
         <is>
-          <t>JIS Q 27001,機密性,完全性,可用性,CIA,情報分類</t>
+          <t>JIS Q 27001情報分類|JIS Q 27001 機密性 完全性 可用性 CIA 情報分類</t>
         </is>
       </c>
     </row>
@@ -35795,7 +35795,7 @@
       </c>
       <c r="W368" t="inlineStr">
         <is>
-          <t>JIS C 0303,複合アウトレット,図記号,電気設備</t>
+          <t>JIS C 0303|JIS C 0303 複合アウトレット 図記号 電気設備</t>
         </is>
       </c>
     </row>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="W369" t="inlineStr">
         <is>
-          <t>融着接続,アーク放電,スクリーニング試験,引張試験,端面切断</t>
+          <t>融着接続アーク放電|融着接続 アーク放電 スクリーニング試験 引張試験 端面切断90度</t>
         </is>
       </c>
     </row>
@@ -35989,7 +35989,7 @@
       </c>
       <c r="W370" t="inlineStr">
         <is>
-          <t>交差接続,クロスコネクト,光配線盤,ジャンパコード</t>
+          <t>交差接続|交差接続 クロスコネクト 光配線盤 ジャンパコード</t>
         </is>
       </c>
     </row>
@@ -36095,7 +36095,7 @@
       </c>
       <c r="W371" t="inlineStr">
         <is>
-          <t>挿入損失,直流ループ抵抗,UTPケーブル,測定,JIS X 5150</t>
+          <t>挿入損失測定方法|挿入損失 直流ループ抵抗 測定方法 違い UTPケーブル</t>
         </is>
       </c>
     </row>
@@ -36193,7 +36193,7 @@
       </c>
       <c r="W372" t="inlineStr">
         <is>
-          <t>クロスコネクト,クラスE,水平ケーブル,80.5m,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 クロスコネクト クラスE 80.5m</t>
         </is>
       </c>
     </row>
@@ -36286,7 +36286,7 @@
       </c>
       <c r="W373" t="inlineStr">
         <is>
-          <t>フラット型インドア光ケーブル,露出配線,固定ピン,カーペット下</t>
+          <t>フラット型インドア光ケーブル|フラット型インドア光ケーブル 露出配線 固定ピン カーペット下</t>
         </is>
       </c>
     </row>
@@ -36387,7 +36387,7 @@
       </c>
       <c r="W374" t="inlineStr">
         <is>
-          <t>反射減衰量,クラスA,クラスB,JIS X 5150</t>
+          <t>JIS X 5150クラスAB|JIS X 5150 反射減衰量 クラスA クラスB 適用外</t>
         </is>
       </c>
     </row>
@@ -36480,7 +36480,7 @@
       </c>
       <c r="W375" t="inlineStr">
         <is>
-          <t>キンク,UTPケーブル,くの字型変形,ケーブル布設</t>
+          <t>キンク|キンク UTPケーブル くの字型変形 ケーブル布設注意</t>
         </is>
       </c>
     </row>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="W376" t="inlineStr">
         <is>
-          <t>シューハート管理図,3シグマ,管理限界線,QC,統計的品質管理</t>
+          <t>シューハート管理図|シューハート管理図 3シグマ 管理限界線 統計的品質管理</t>
         </is>
       </c>
     </row>
@@ -36676,7 +36676,7 @@
       </c>
       <c r="W377" t="inlineStr">
         <is>
-          <t>クリティカルパス,トータルフロート,アローダイアグラム,PERT</t>
+          <t>クリティカルパス|クリティカルパス トータルフロート ゼロ アローダイアグラム PERT</t>
         </is>
       </c>
     </row>
@@ -36781,7 +36781,7 @@
       </c>
       <c r="W378" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,利用者,著しく不適当,電気通信事業法</t>
+          <t>端末設備接続拒否|端末設備 接続請求 利用者 著しく不適当 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -36873,7 +36873,7 @@
       </c>
       <c r="W379" t="inlineStr">
         <is>
-          <t>自営電気通信設備,保持,経営上困難,接続拒否,総務大臣</t>
+          <t>自営電気通信設備保持|自営電気通信設備 保持 経営困難 接続拒否 総務大臣認定</t>
         </is>
       </c>
     </row>
@@ -36965,7 +36965,7 @@
       </c>
       <c r="W380" t="inlineStr">
         <is>
-          <t>技術基準適合認定,表示,電気通信事業法</t>
+          <t>技術基準適合認定取消|技術基準適合認定 不適合 表示なしとみなす 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -37057,7 +37057,7 @@
       </c>
       <c r="W381" t="inlineStr">
         <is>
-          <t>業務改善命令,重要通信,適切に配慮,電気通信事業法</t>
+          <t>業務改善命令重要通信|業務改善命令 重要通信 適切に配慮 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -37156,7 +37156,7 @@
       </c>
       <c r="W382" t="inlineStr">
         <is>
-          <t>重要通信,治安,天災,新聞社,緊急通信</t>
+          <t>重要通信治安天災|重要通信 治安 天災 新聞社 緊急通信</t>
         </is>
       </c>
     </row>
@@ -37246,7 +37246,7 @@
       </c>
       <c r="W383" t="inlineStr">
         <is>
-          <t>工事担任者,第一級アナログ通信,第二級デジタル通信,資格区分</t>
+          <t>工事担任者資格区分|工事担任者 第一級アナログ 第二級デジタル 資格区分 比較</t>
         </is>
       </c>
     </row>
@@ -37340,7 +37340,7 @@
       </c>
       <c r="W384" t="inlineStr">
         <is>
-          <t>資格者証,技術の向上,書換え交付,再交付,住所変更</t>
+          <t>資格者証技術の向上|資格者証 技術の向上 書換え交付 住所変更</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="W385" t="inlineStr">
         <is>
-          <t>技術基準適合認定,映像面,電磁的方法,取扱説明書,表示方法</t>
+          <t>技術基準適合認定表示方法|技術基準適合認定 映像面 取扱説明書 包装 表示方法</t>
         </is>
       </c>
     </row>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="W386" t="inlineStr">
         <is>
-          <t>有線電気通信法,総務大臣,報告,立入検査</t>
+          <t>有線電気通信法報告立入|有線電気通信法 総務大臣 報告 立入検査</t>
         </is>
       </c>
     </row>
@@ -37613,7 +37613,7 @@
       </c>
       <c r="W387" t="inlineStr">
         <is>
-          <t>有線電気通信設備,方式の別,設置の場所,2週間前,届出</t>
+          <t>有線電気通信設備変更届|有線電気通信設備 方式の別 設置の場所 2週間前</t>
         </is>
       </c>
     </row>
@@ -37718,7 +37718,7 @@
       </c>
       <c r="W388" t="inlineStr">
         <is>
-          <t>デジタルデータ伝送用設備,総合デジタル通信用設備,64kbps,端末設備等規則</t>
+          <t>デジタルデータ伝送用設備|デジタルデータ伝送用設備 総合デジタル通信用設備 違い 64kbps</t>
         </is>
       </c>
     </row>
@@ -37810,7 +37810,7 @@
       </c>
       <c r="W389" t="inlineStr">
         <is>
-          <t>端末設備,事業用電気通信設備,識別機能,漏えい</t>
+          <t>端末設備識別禁止|端末設備 事業用電気通信設備 漏えい 意図的識別禁止</t>
         </is>
       </c>
     </row>
@@ -37907,7 +37907,7 @@
       </c>
       <c r="W390" t="inlineStr">
         <is>
-          <t>接地抵抗,100オーム,端末設備等規則</t>
+          <t>接地抵抗100オーム|接地抵抗 100オーム以下 端末設備 金属筐体</t>
         </is>
       </c>
     </row>
@@ -38006,7 +38006,7 @@
       </c>
       <c r="W391" t="inlineStr">
         <is>
-          <t>配線設備,強電流電線,有線電気通信設備令,評価雑音電力,マイナス58dB</t>
+          <t>配線設備有線電気通信設備令|配線設備 強電流電線 有線電気通信設備令 評価雑音電力</t>
         </is>
       </c>
     </row>
@@ -38098,7 +38098,7 @@
       </c>
       <c r="W392" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,空き周波数,通信路</t>
+          <t>識別符号空き周波数|識別符号 無線設備 空き周波数判定 通信路設定</t>
         </is>
       </c>
     </row>
@@ -38203,7 +38203,7 @@
       </c>
       <c r="W393" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,信号送出時間,50ms,30ms,ミニマムポーズ</t>
+          <t>信号送出時間50ms|押しボタンダイヤル 信号送出時間50ms ミニマムポーズ30ms</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="W394" t="inlineStr">
         <is>
-          <t>移動電話端末,自動再発信,2回以内,3分,チャネル切断</t>
+          <t>移動電話端末自動再発信|移動電話端末 自動再発信 2回以内 3分 チャネル切断</t>
         </is>
       </c>
     </row>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="W395" t="inlineStr">
         <is>
-          <t>IP電話端末,直流電圧,緊急通報,電気通信回線</t>
+          <t>IP電話端末緊急通報|IP電話端末 直流電圧 緊急通報 電気通信回線</t>
         </is>
       </c>
     </row>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="W396" t="inlineStr">
         <is>
-          <t>IP移動電話端末,128秒,送信タイミング,総務大臣,告示</t>
+          <t>IP移動電話端末送信タイミング|IP移動電話端末 128秒 送信タイミング 総務大臣告示</t>
         </is>
       </c>
     </row>
@@ -38578,7 +38578,7 @@
       </c>
       <c r="W397" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,漏話減衰量,1500Hz,70dB</t>
+          <t>漏話減衰量1500Hz|専用通信回線設備等端末 漏話減衰量 1500Hz 70dB</t>
         </is>
       </c>
     </row>
@@ -38683,7 +38683,7 @@
       </c>
       <c r="W398" t="inlineStr">
         <is>
-          <t>通信回線,線路の電圧,100ボルト,平衡度,有線電気通信設備令</t>
+          <t>通信回線電圧100V|通信回線 線路の電圧 100ボルト以下 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -38775,7 +38775,7 @@
       </c>
       <c r="W399" t="inlineStr">
         <is>
-          <t>強電流電線,重畳,分離,開閉,有線電気通信設備令</t>
+          <t>強電流電線重畳分離|強電流電線 重畳 分離 開閉 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -38869,7 +38869,7 @@
       </c>
       <c r="W400" t="inlineStr">
         <is>
-          <t>屋内電線,強電流ケーブル,離隔距離,隔壁,有線電気通信設備令</t>
+          <t>屋内電線強電流ケーブル離隔|屋内電線 強電流ケーブル 離隔距離 隔壁 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -38968,7 +38968,7 @@
       </c>
       <c r="W401" t="inlineStr">
         <is>
-          <t>識別符号,不正アクセス禁止法,署名,アクセス管理者</t>
+          <t>識別符号不正アクセス禁止法|識別符号 不正アクセス禁止法 署名 アクセス管理者</t>
         </is>
       </c>
     </row>
@@ -39060,7 +39060,7 @@
       </c>
       <c r="W402" t="inlineStr">
         <is>
-          <t>認証業務,電子署名法,電子署名,自らが行う</t>
+          <t>認証業務電子署名法|認証業務 電子署名法 自らが行う 電磁的記録</t>
         </is>
       </c>
     </row>
@@ -39150,7 +39150,7 @@
       </c>
       <c r="W403" t="inlineStr">
         <is>
-          <t>10G-EPON,GE-PON,TDMA,WDM,OLT,ONU</t>
+          <t>10G-EPON GE-PON混在|10G-EPON GE-PON OLT TDMA WDM 混在接続,WDM|WDM 波長多重 下り信号 10Gbps 1Gbps</t>
         </is>
       </c>
     </row>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="W404" t="inlineStr">
         <is>
-          <t>SIPサーバ,ロケーションサーバ,レジストラ,UAC,位置情報</t>
+          <t>ロケーションサーバ|ロケーションサーバ SIPサーバ UAC 位置情報管理 レジストラ比較</t>
         </is>
       </c>
     </row>
@@ -39331,7 +39331,7 @@
       </c>
       <c r="W405" t="inlineStr">
         <is>
-          <t>PoE,オルタナティブB,ピン4・5・7・8,予備ペア,1000BASE-T</t>
+          <t>PoEオルタナティブB|PoE オルタナティブB ピン4 5 7 8 予備ペア 1000BASE-T</t>
         </is>
       </c>
     </row>
@@ -39424,7 +39424,7 @@
       </c>
       <c r="W406" t="inlineStr">
         <is>
-          <t>IEEE802.11ax,Wi-Fi 6,6GHz,ISMバンド,気象レーダ</t>
+          <t>IEEE802.11ax 6GHz|IEEE802.11ax Wi-Fi6 6GHz ISMバンド 気象レーダ干渉なし</t>
         </is>
       </c>
     </row>
@@ -39524,7 +39524,7 @@
       </c>
       <c r="W407" t="inlineStr">
         <is>
-          <t>コモンモードチョークコイル,フェライトコア,高周波,ノイズ対策,EMC</t>
+          <t>コモンモードチョークコイル|コモンモードチョークコイル フェライトコア 高周波 ノイズ対策 EMC</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="W408" t="inlineStr">
         <is>
-          <t>1000BASE-T,8B1Q4,4D-PAM5,NRZI,8B/10B,符号化</t>
+          <t>8B1Q4|8B1Q4 1000BASE-T 4D-PAM5 NRZI 8B/10B 符号化比較</t>
         </is>
       </c>
     </row>
@@ -39710,7 +39710,7 @@
       </c>
       <c r="W409" t="inlineStr">
         <is>
-          <t>FM一括変換方式,CATV,光強度変調,3GHz,映像信号</t>
+          <t>FM一括変換方式|FM一括変換方式 CATV 3GHz 光強度変調 映像信号</t>
         </is>
       </c>
     </row>
@@ -39803,7 +39803,7 @@
       </c>
       <c r="W410" t="inlineStr">
         <is>
-          <t>ICMPv6,パラメータ問題,時間超過,終点到達不能,IPv6</t>
+          <t>ICMPv6パラメータ問題|ICMPv6 パラメータ問題 時間超過 終点到達不能 IPv6</t>
         </is>
       </c>
     </row>
@@ -39896,7 +39896,7 @@
       </c>
       <c r="W411" t="inlineStr">
         <is>
-          <t>ジッタバッファ,揺らぎ吸収,VoIP,音声品質,パケット損失</t>
+          <t>ジッタバッファ|ジッタバッファ 揺らぎ吸収 VoIP 音声品質 パケット損失</t>
         </is>
       </c>
     </row>
@@ -39986,7 +39986,7 @@
       </c>
       <c r="W412" t="inlineStr">
         <is>
-          <t>広域イーサネット,MPLS,LER,LSR,レイヤ2</t>
+          <t>広域イーサネット|広域イーサネット MPLS LER LSR レイヤ2 ルーティングプロトコル</t>
         </is>
       </c>
     </row>
@@ -40079,7 +40079,7 @@
       </c>
       <c r="W413" t="inlineStr">
         <is>
-          <t>rootkit,ルートキット,バックドア,権限奪取,マルウェア</t>
+          <t>rootkit|rootkit ルートキット バックドア 権限奪取 マルウェア</t>
         </is>
       </c>
     </row>
@@ -40179,7 +40179,7 @@
       </c>
       <c r="W414" t="inlineStr">
         <is>
-          <t>ハイブリッド暗号,PGP,共通鍵暗号,公開鍵暗号,処理速度</t>
+          <t>ハイブリッド暗号|ハイブリッド暗号 PGP 共通鍵 公開鍵 処理速度比較</t>
         </is>
       </c>
     </row>
@@ -40275,7 +40275,7 @@
       </c>
       <c r="W415" t="inlineStr">
         <is>
-          <t>クロスサイトスクリプティング,XSS,SQLインジェクション,サニタイジング</t>
+          <t>クロスサイトスクリプティング|クロスサイトスクリプティング XSS SQLインジェクション サニタイジング比較</t>
         </is>
       </c>
     </row>
@@ -40375,7 +40375,7 @@
       </c>
       <c r="W416" t="inlineStr">
         <is>
-          <t>IPsec,トランスポートモード,トンネルモード,VPN,リモートアクセス</t>
+          <t>IPsec|IPsec トランスポートモード トンネルモード VPN リモートアクセス</t>
         </is>
       </c>
     </row>
@@ -40468,7 +40468,7 @@
       </c>
       <c r="W417" t="inlineStr">
         <is>
-          <t>CSIRT,インシデント対応,セキュリティ,被害拡大防止</t>
+          <t>CSIRT|CSIRT インシデント対応 セキュリティ 被害拡大防止</t>
         </is>
       </c>
     </row>
@@ -40574,7 +40574,7 @@
       </c>
       <c r="W418" t="inlineStr">
         <is>
-          <t>融着接続,アーク放電,スクリーニング試験,引張試験,端面切断</t>
+          <t>融着接続アーク放電|融着接続 アーク放電 スクリーニング試験 引張試験</t>
         </is>
       </c>
     </row>
@@ -40667,7 +40667,7 @@
       </c>
       <c r="W419" t="inlineStr">
         <is>
-          <t>フリーアクセスフロア,OAフロア,不陸調整,支柱ねじ</t>
+          <t>フリーアクセスフロア|フリーアクセスフロア OAフロア 不陸調整 支柱ねじ</t>
         </is>
       </c>
     </row>
@@ -40757,7 +40757,7 @@
       </c>
       <c r="W420" t="inlineStr">
         <is>
-          <t>OTDR法,後方散乱光,光ファイバ損失,両端測定,JIS C 6823</t>
+          <t>OTDR法|OTDR法 後方散乱光 両端測定 平均化 光ファイバ損失</t>
         </is>
       </c>
     </row>
@@ -40850,7 +40850,7 @@
       </c>
       <c r="W421" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,ピン6番,緑色,心線配色</t>
+          <t>T568B|T568B RJ-45 ピン6番 緑色 心線配色</t>
         </is>
       </c>
     </row>
@@ -40948,7 +40948,7 @@
       </c>
       <c r="W422" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスF,水平ケーブル,82.5m,JIS X 5150</t>
+          <t>JIS X 5150クラスF|JIS X 5150 インタコネクト クラスF 82.5m 水平ケーブル</t>
         </is>
       </c>
     </row>
@@ -41041,7 +41041,7 @@
       </c>
       <c r="W423" t="inlineStr">
         <is>
-          <t>IEEE802.3bq,40GBASE-T,カテゴリ8,30メートル,データセンタ</t>
+          <t>IEEE802.3bq|IEEE802.3bq 40GBASE-T カテゴリ8 30メートル データセンタ</t>
         </is>
       </c>
     </row>
@@ -41134,7 +41134,7 @@
       </c>
       <c r="W424" t="inlineStr">
         <is>
-          <t>OTDR,ダイナミックレンジ,後方散乱光,パルスパワー</t>
+          <t>OTDRダイナミックレンジ|OTDR ダイナミックレンジ 後方散乱光 パルスパワー増加</t>
         </is>
       </c>
     </row>
@@ -41227,7 +41227,7 @@
       </c>
       <c r="W425" t="inlineStr">
         <is>
-          <t>融着接続,気泡,光ファイバカッタ,端面切断,やり直し</t>
+          <t>融着接続気泡|融着接続 気泡 光ファイバカッタ 端面切断 やり直し</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="W426" t="inlineStr">
         <is>
-          <t>ヒストグラム,散布図,パレート図,管理図,QC7つ道具</t>
+          <t>QC7つ道具|QC7つ道具 ヒストグラム 散布図 パレート図 管理図 違い</t>
         </is>
       </c>
     </row>
@@ -41421,7 +41421,7 @@
       </c>
       <c r="W427" t="inlineStr">
         <is>
-          <t>KYT,危険予知訓練,4ラウンド法,本質追究,安全管理</t>
+          <t>KYT4ラウンド法|KYT 危険予知訓練 4ラウンド法 本質追究 安全管理</t>
         </is>
       </c>
     </row>
@@ -41521,7 +41521,7 @@
       </c>
       <c r="W428" t="inlineStr">
         <is>
-          <t>資格者証,工事担任者,罰金,5年,養成課程,返納</t>
+          <t>資格者証交付要件|資格者証 罰金以上 5年 養成課程 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41620,7 +41620,7 @@
       </c>
       <c r="W429" t="inlineStr">
         <is>
-          <t>業務改善命令,支障,おそれ,提供条件,電気通信事業法</t>
+          <t>業務改善命令支障おそれ|業務改善命令 支障 おそれ 対象外 提供条件 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -41719,7 +41719,7 @@
       </c>
       <c r="W430" t="inlineStr">
         <is>
-          <t>管理規程,事業開始前,届出,基礎的電気通信役務,電気通信事業法</t>
+          <t>管理規程届出|管理規程 事業開始前 届出 許可ではない 基礎的電気通信役務</t>
         </is>
       </c>
     </row>
@@ -41811,7 +41811,7 @@
       </c>
       <c r="W431" t="inlineStr">
         <is>
-          <t>技術基準適合認定,表示,他の利用者,妨害防止</t>
+          <t>技術基準適合認定他の利用者|技術基準適合認定 他の利用者 妨害防止 表示なしとみなす</t>
         </is>
       </c>
     </row>
@@ -41903,7 +41903,7 @@
       </c>
       <c r="W432" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,利用者,著しく不適当,電気通信事業法</t>
+          <t>端末設備接続拒否著しく不適当|端末設備 接続請求 利用者 著しく不適当 拒否</t>
         </is>
       </c>
     </row>
@@ -42008,7 +42008,7 @@
       </c>
       <c r="W433" t="inlineStr">
         <is>
-          <t>工事担任者,第二級アナログ通信,1以下,50以下,資格区分</t>
+          <t>第二級アナログ通信|第二級アナログ通信 回線数1以下 50以下ではない 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42107,7 +42107,7 @@
       </c>
       <c r="W434" t="inlineStr">
         <is>
-          <t>資格者証,再交付,汚した,返納,10日以内</t>
+          <t>資格者証汚した再交付|資格者証 汚した 再交付 返納10日以内</t>
         </is>
       </c>
     </row>
@@ -42196,7 +42196,7 @@
       </c>
       <c r="W435" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,固定電話端末,G,専用通信回線設備等端末,P</t>
+          <t>技術基準適合認定番号G P|技術基準適合認定番号 固定電話端末G 専用通信回線設備等端末P</t>
         </is>
       </c>
     </row>
@@ -42301,7 +42301,7 @@
       </c>
       <c r="W436" t="inlineStr">
         <is>
-          <t>有線電気通信法,設置及び使用,秩序,公共の福祉</t>
+          <t>有線電気通信法目的|有線電気通信法 設置及び使用 秩序 公共の福祉</t>
         </is>
       </c>
     </row>
@@ -42388,7 +42388,7 @@
       </c>
       <c r="W437" t="inlineStr">
         <is>
-          <t>有線電気通信設備,変更届,2週間前,工事を要しない,2週間以内</t>
+          <t>有線電気通信設備変更届|有線電気通信設備 変更届 2週間前 工事を要しない 2週間以内</t>
         </is>
       </c>
     </row>
@@ -42493,7 +42493,7 @@
       </c>
       <c r="W438" t="inlineStr">
         <is>
-          <t>IP移動電話端末,IP移動電話用設備,デジタルデータ伝送用設備,端末設備等規則</t>
+          <t>IP移動電話端末|IP移動電話端末 IP移動電話用設備のみ デジタルデータ伝送用設備ではない</t>
         </is>
       </c>
     </row>
@@ -42592,7 +42592,7 @@
       </c>
       <c r="W439" t="inlineStr">
         <is>
-          <t>分界点,電気的条件,光学的条件,鳴音,事業用電気通信設備</t>
+          <t>分界点接続方式|分界点 電気的条件 光学的条件 容易に切り離せる 鳴音</t>
         </is>
       </c>
     </row>
@@ -42684,7 +42684,7 @@
       </c>
       <c r="W440" t="inlineStr">
         <is>
-          <t>絶縁耐力試験,250V,2500ボルト,1分間,端末設備等規則</t>
+          <t>絶縁耐力250V 2500V|絶縁耐力試験 250V超 2500ボルト 1分間 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -42776,7 +42776,7 @@
       </c>
       <c r="W441" t="inlineStr">
         <is>
-          <t>配線設備,絶縁抵抗,直流200V,1MΩ,端末設備等規則</t>
+          <t>配線設備絶縁抵抗200V|配線設備 絶縁抵抗 直流200V 1MΩ</t>
         </is>
       </c>
     </row>
@@ -42868,7 +42868,7 @@
       </c>
       <c r="W442" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,通信路,照合,端末設備等規則</t>
+          <t>識別符号|識別符号 無線設備 通信路設定 照合</t>
         </is>
       </c>
     </row>
@@ -42960,7 +42960,7 @@
       </c>
       <c r="W443" t="inlineStr">
         <is>
-          <t>移動電話端末,チャネル切断,通信終了,端末設備等規則</t>
+          <t>移動電話端末チャネル切断|移動電話端末 チャネル切断 通信終了</t>
         </is>
       </c>
     </row>
@@ -43065,7 +43065,7 @@
       </c>
       <c r="W444" t="inlineStr">
         <is>
-          <t>固定電話端末,自動再発信,3分間,2回以内</t>
+          <t>固定電話端末自動再発信|固定電話端末 自動再発信 3分間 2回以内</t>
         </is>
       </c>
     </row>
@@ -43164,7 +43164,7 @@
       </c>
       <c r="W445" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,直流電圧,電気的条件,光学的条件</t>
+          <t>専用通信回線設備等端末直流|専用通信回線設備等端末 直流電圧 電気的条件 光学的条件</t>
         </is>
       </c>
     </row>
@@ -43264,7 +43264,7 @@
       </c>
       <c r="W446" t="inlineStr">
         <is>
-          <t>アクセス制御,初期識別符号,ソフトウェア更新,通信プロトコル,電力停止</t>
+          <t>アクセス制御電力停止|アクセス制御 初期識別符号 ソフトウェア更新 通信プロトコルではない</t>
         </is>
       </c>
     </row>
@@ -43363,7 +43363,7 @@
       </c>
       <c r="W447" t="inlineStr">
         <is>
-          <t>2周波電力差,5dB,ミニマムポーズ,最小値,押しボタンダイヤル</t>
+          <t>2周波電力差5dB|2周波電力差 5dB以内 ミニマムポーズ 最小値 押しボタンダイヤル</t>
         </is>
       </c>
     </row>
@@ -43452,7 +43452,7 @@
       </c>
       <c r="W448" t="inlineStr">
         <is>
-          <t>屋内電線,強電流電線,30センチメートル,保安機能,有線電気通信設備令</t>
+          <t>屋内電線強電流電線30cm|屋内電線 強電流電線 30センチメートル 保安機能 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="W449" t="inlineStr">
         <is>
-          <t>架空電線,建造物,離隔距離,30センチメートル,有線電気通信設備令</t>
+          <t>架空電線建造物30cm|架空電線 建造物 離隔距離 30センチメートル以下禁止</t>
         </is>
       </c>
     </row>
@@ -43649,7 +43649,7 @@
       </c>
       <c r="W450" t="inlineStr">
         <is>
-          <t>架空電線,鉄道横断,軌条面,6メートル,有線電気通信設備令</t>
+          <t>架空電線鉄道6m|架空電線 鉄道軌道横断 軌条面6メートル 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -43741,7 +43741,7 @@
       </c>
       <c r="W451" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,電子計算機,犯罪の防止,アクセス制御</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 電子計算機 犯罪防止 アクセス制御</t>
         </is>
       </c>
     </row>
@@ -43833,7 +43833,7 @@
       </c>
       <c r="W452" t="inlineStr">
         <is>
-          <t>電子署名,電磁的記録,作成,電子署名法</t>
+          <t>電子署名作成者|電子署名 電磁的記録 作成者 電子署名法</t>
         </is>
       </c>
     </row>
@@ -43926,7 +43926,7 @@
       </c>
       <c r="W453" t="inlineStr">
         <is>
-          <t>XGS-PON,ITU-T G.9807.1,GTCフレーム,10Gbps,XG-PON</t>
+          <t>XGS-PON|XGS-PON ITU-T G.9807.1 GTCフレーム 10Gbps対称 XG-PON比較</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
       </c>
       <c r="W454" t="inlineStr">
         <is>
-          <t>汎用サーバIP-PBX,VoIPゲートウェイ,アナログ電話機,SIP,アプリケーション層</t>
+          <t>汎用サーバIP-PBX|汎用サーバIP-PBX VoIPゲートウェイ アナログ電話機 SIPアプリケーション層</t>
         </is>
       </c>
     </row>
@@ -44119,7 +44119,7 @@
       </c>
       <c r="W455" t="inlineStr">
         <is>
-          <t>IEEE802.3bt,Type4,Class8,90W,PoE,4対</t>
+          <t>IEEE802.3bt Type4|IEEE802.3bt Type4 Class8 90W 4対給電</t>
         </is>
       </c>
     </row>
@@ -44212,7 +44212,7 @@
       </c>
       <c r="W456" t="inlineStr">
         <is>
-          <t>IEEE802.11n,ブロックACK,プローブ応答,ビーコン,フレーム</t>
+          <t>ブロックACK|IEEE802.11n ブロックACK プローブ応答 ビーコン 違い</t>
         </is>
       </c>
     </row>
@@ -44305,7 +44305,7 @@
       </c>
       <c r="W457" t="inlineStr">
         <is>
-          <t>等電位ボンディング,SPD,雷保護,直接導体,JIS C 5381</t>
+          <t>等電位ボンディング|等電位ボンディング SPD 雷保護 直接導体 JIS C 5381</t>
         </is>
       </c>
     </row>
@@ -44398,7 +44398,7 @@
       </c>
       <c r="W458" t="inlineStr">
         <is>
-          <t>10GBASE-LR,64B/66B,4B/5B,8B1Q4,8B/6T,符号化</t>
+          <t>10GBASE-LR|10GBASE-LR 64B/66B 4B/5B 8B1Q4 符号化方式比較</t>
         </is>
       </c>
     </row>
@@ -44491,7 +44491,7 @@
       </c>
       <c r="W459" t="inlineStr">
         <is>
-          <t>HFC,Hybrid Fiber Coaxial,光ノード,同軸ケーブル,FTTH</t>
+          <t>HFC|HFC Hybrid Fiber Coaxial 光ノード 同軸ケーブル FTTH比較</t>
         </is>
       </c>
     </row>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="W460" t="inlineStr">
         <is>
-          <t>SaaS,PaaS,IaaS,クラウドサービス,アプリケーション</t>
+          <t>SaaS|SaaS PaaS IaaS クラウドサービス アプリケーション 比較</t>
         </is>
       </c>
     </row>
@@ -44685,7 +44685,7 @@
       </c>
       <c r="W461" t="inlineStr">
         <is>
-          <t>IPv6,リンクローカル,fe80,fec0,マルチキャスト,エニーキャスト</t>
+          <t>IPv6リンクローカル|IPv6 リンクローカル fe80 fec0 マルチキャスト エニーキャスト</t>
         </is>
       </c>
     </row>
@@ -44775,7 +44775,7 @@
       </c>
       <c r="W462" t="inlineStr">
         <is>
-          <t>MACアドレス,NIC,FCS,MACフレーム,48ビット</t>
+          <t>MACアドレス|MACアドレス NIC 48ビット FCS フレーム誤り検出</t>
         </is>
       </c>
     </row>
@@ -44868,7 +44868,7 @@
       </c>
       <c r="W463" t="inlineStr">
         <is>
-          <t>検疫ネットワーク,セキュリティポリシー,隔離,不正PC</t>
+          <t>検疫ネットワーク|検疫ネットワーク セキュリティポリシー 隔離 不正PC</t>
         </is>
       </c>
     </row>
@@ -44961,7 +44961,7 @@
       </c>
       <c r="W464" t="inlineStr">
         <is>
-          <t>DKIM,SPF,デジタル署名,送信元ドメイン認証,迷惑メール</t>
+          <t>DKIM|DKIM SPF デジタル署名 送信元ドメイン認証 迷惑メール対策</t>
         </is>
       </c>
     </row>
@@ -45054,7 +45054,7 @@
       </c>
       <c r="W465" t="inlineStr">
         <is>
-          <t>SSH,Secure Shell,Telnet,暗号化,遠隔操作</t>
+          <t>SSH|SSH Secure Shell Telnet 暗号化 遠隔操作 比較</t>
         </is>
       </c>
     </row>
@@ -45154,7 +45154,7 @@
       </c>
       <c r="W466" t="inlineStr">
         <is>
-          <t>スニッフィング,データマイニング,IPスプーフィング,なりすまし</t>
+          <t>スニッフィング|スニッフィング データマイニング IPスプーフィング 違い なりすまし</t>
         </is>
       </c>
     </row>
@@ -45260,7 +45260,7 @@
       </c>
       <c r="W467" t="inlineStr">
         <is>
-          <t>ISMS,JIS Q 27001,開発環境,テスト環境,本番環境,分離</t>
+          <t>ISMS開発テスト本番分離|ISMS JIS Q 27001 開発環境 テスト環境 本番環境 分離</t>
         </is>
       </c>
     </row>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="W468" t="inlineStr">
         <is>
-          <t>挿入法,カットバック法,挿入損失,融着接続,JIS C 6823</t>
+          <t>挿入法|挿入法 カットバック法 光ファイバ 挿入損失 JIS C 6823</t>
         </is>
       </c>
     </row>
@@ -45429,7 +45429,7 @@
       </c>
       <c r="W469" t="inlineStr">
         <is>
-          <t>JIS C 0303,情報用アウトレット,図記号,電気設備</t>
+          <t>JIS C 0303|JIS C 0303 情報用アウトレット 図記号 電気設備</t>
         </is>
       </c>
     </row>
@@ -45522,7 +45522,7 @@
       </c>
       <c r="W470" t="inlineStr">
         <is>
-          <t>キンク,UTPケーブル,くの字型,ケーブル布設,変形</t>
+          <t>キンク|キンク UTPケーブル くの字型 ケーブル布設 変形</t>
         </is>
       </c>
     </row>
@@ -45612,7 +45612,7 @@
       </c>
       <c r="W471" t="inlineStr">
         <is>
-          <t>光ファイバケーブル,テンションメンバ,8の字,同心円,けん引端</t>
+          <t>8の字巻き|光ファイバケーブル テンションメンバ 8の字 同心円 けん引端</t>
         </is>
       </c>
     </row>
@@ -45713,7 +45713,7 @@
       </c>
       <c r="W472" t="inlineStr">
         <is>
-          <t>分岐点,フロア配線盤,15メートル,JIS X 5150,水平配線</t>
+          <t>分岐点15m|分岐点 フロア配線盤 15メートル以上 JIS X 5150</t>
         </is>
       </c>
     </row>
@@ -45806,7 +45806,7 @@
       </c>
       <c r="W473" t="inlineStr">
         <is>
-          <t>エイリアンクロストーク,異線間漏話,ラック内余長,UTPケーブル</t>
+          <t>エイリアンクロストーク|エイリアンクロストーク 異線間漏話 ラック内余長 UTPケーブル</t>
         </is>
       </c>
     </row>
@@ -45899,7 +45899,7 @@
       </c>
       <c r="W474" t="inlineStr">
         <is>
-          <t>FASコネクタ,単心光コネクタ,架空クロージャ,ドロップ光ファイバ</t>
+          <t>FASコネクタ|FASコネクタ 単心光コネクタ 架空クロージャ ドロップ光ファイバ</t>
         </is>
       </c>
     </row>
@@ -45992,7 +45992,7 @@
       </c>
       <c r="W475" t="inlineStr">
         <is>
-          <t>STP,IEEE802.1D,スパニングツリー,ループ防止,フレーム</t>
+          <t>STP|STP IEEE802.1D スパニングツリー ループ防止 フレーム</t>
         </is>
       </c>
     </row>
@@ -46103,7 +46103,7 @@
       </c>
       <c r="W476" t="inlineStr">
         <is>
-          <t>変動原価率,損益分岐点,採算性,コスト管理,工事</t>
+          <t>変動原価率損益分岐点|変動原価率 損益分岐点 採算性 コスト管理 工事</t>
         </is>
       </c>
     </row>
@@ -46201,7 +46201,7 @@
       </c>
       <c r="W477" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,短縮,所要日数,PERT</t>
+          <t>アローダイアグラム短縮|アローダイアグラム クリティカルパス 短縮 所要日数 PERT</t>
         </is>
       </c>
     </row>
@@ -46306,7 +46306,7 @@
       </c>
       <c r="W478" t="inlineStr">
         <is>
-          <t>業務改善命令,支障,おそれ,不当差別,電気通信事業法</t>
+          <t>業務改善命令支障おそれ|業務改善命令 支障おそれ 対象外 不当差別 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -46398,7 +46398,7 @@
       </c>
       <c r="W479" t="inlineStr">
         <is>
-          <t>端末設備,異常,電気通信役務,検査,電気通信事業法</t>
+          <t>端末設備異常検査|端末設備 異常 電気通信役務 検査 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -46495,7 +46495,7 @@
       </c>
       <c r="W480" t="inlineStr">
         <is>
-          <t>管理規程,確実かつ安定的,適正かつ継続的,電気通信事業法</t>
+          <t>管理規程確実安定的|管理規程 確実かつ安定的 適正かつ継続的 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -46594,7 +46594,7 @@
       </c>
       <c r="W481" t="inlineStr">
         <is>
-          <t>技術基準適合認定,登録認定機関,総務省令,表示,公示</t>
+          <t>技術基準適合認定公示|技術基準適合認定 登録認定機関 総務省令 表示 公示</t>
         </is>
       </c>
     </row>
@@ -46689,7 +46689,7 @@
       </c>
       <c r="W482" t="inlineStr">
         <is>
-          <t>重要通信,気象機関,選挙管理機関,緊急通信,電気通信事業法</t>
+          <t>重要通信気象機関|重要通信 気象機関 選挙管理機関 緊急通信 電気通信事業法</t>
         </is>
       </c>
     </row>
@@ -46779,7 +46779,7 @@
       </c>
       <c r="W483" t="inlineStr">
         <is>
-          <t>工事担任者,第二級アナログ通信,第一級アナログ通信,第二級デジタル通信,資格区分</t>
+          <t>工事担任者資格区分|工事担任者 第二級アナログ 第一級アナログ 第二級デジタル 資格区分</t>
         </is>
       </c>
     </row>
@@ -46878,7 +46878,7 @@
       </c>
       <c r="W484" t="inlineStr">
         <is>
-          <t>資格者証,書換え交付,返納,10日以内,住所変更</t>
+          <t>資格者証書換え返納|資格者証 書換え交付 住所変更 返納10日以内</t>
         </is>
       </c>
     </row>
@@ -46972,7 +46972,7 @@
       </c>
       <c r="W485" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,IP移動電話端末,H,専用通信回線設備等端末,P,Q</t>
+          <t>技術基準適合認定番号H P|技術基準適合認定番号 IP移動電話端末H 専用通信回線設備等端末P Qではない</t>
         </is>
       </c>
     </row>
@@ -47064,7 +47064,7 @@
       </c>
       <c r="W486" t="inlineStr">
         <is>
-          <t>有線電気通信法,設備の概要,変更届,届出</t>
+          <t>有線電気通信法変更届|有線電気通信法 設備の概要 変更届 届出</t>
         </is>
       </c>
     </row>
@@ -47156,7 +47156,7 @@
       </c>
       <c r="W487" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保,使用させ,接続</t>
+          <t>有線電気通信法非常事態|有線電気通信法 非常事態 他の者に使用させ 接続</t>
         </is>
       </c>
     </row>
@@ -47256,7 +47256,7 @@
       </c>
       <c r="W488" t="inlineStr">
         <is>
-          <t>制御チャネル,デジタルデータ伝送用設備,総合デジタル通信用設備,端末設備等規則</t>
+          <t>制御チャネル|制御チャネル デジタルデータ伝送用設備 総合デジタル通信用設備 違い</t>
         </is>
       </c>
     </row>
@@ -47355,7 +47355,7 @@
       </c>
       <c r="W489" t="inlineStr">
         <is>
-          <t>分界点,識別機能,事業用電気通信設備,自営電気通信設備,漏えい</t>
+          <t>分界点識別禁止|分界点 識別機能 事業用電気通信設備 自営電気通信設備 違い</t>
         </is>
       </c>
     </row>
@@ -47452,7 +47452,7 @@
       </c>
       <c r="W490" t="inlineStr">
         <is>
-          <t>絶縁抵抗,250V,2MΩ,0.2MΩ,端末設備等規則</t>
+          <t>絶縁抵抗250V 2MΩ|絶縁抵抗 250V以下 2MΩ以上 0.2MΩとの違い 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -47541,7 +47541,7 @@
       </c>
       <c r="W491" t="inlineStr">
         <is>
-          <t>配線設備,有線電気通信設備令,事業用電気通信設備,損傷,告示</t>
+          <t>配線設備有線電気通信設備令|配線設備 有線電気通信設備令 事業用電気通信設備 損傷 告示</t>
         </is>
       </c>
     </row>
@@ -47633,7 +47633,7 @@
       </c>
       <c r="W492" t="inlineStr">
         <is>
-          <t>識別符号,一の筐体,容易に開けることができない,無線設備,端末設備等規則</t>
+          <t>識別符号一の筐体|識別符号 一の筐体 容易に開けられない 無線設備 端末設備等規則</t>
         </is>
       </c>
     </row>
@@ -47725,7 +47725,7 @@
       </c>
       <c r="W493" t="inlineStr">
         <is>
-          <t>固定電話端末,通信終了メッセージ,2分以内,応答確認</t>
+          <t>固定電話端末通信終了2分|固定電話端末 通信終了メッセージ 2分以内 応答確認</t>
         </is>
       </c>
     </row>
@@ -47825,7 +47825,7 @@
       </c>
       <c r="W494" t="inlineStr">
         <is>
-          <t>登録要求,固定電話端末,固定電話用設備,デジタルデータ伝送用設備</t>
+          <t>登録要求固定電話用設備|登録要求 固定電話端末 固定電話用設備のみ デジタルデータ伝送用設備ではない</t>
         </is>
       </c>
     </row>
@@ -47914,7 +47914,7 @@
       </c>
       <c r="W495" t="inlineStr">
         <is>
-          <t>IP移動電話端末,自動再発信,3回以内,3分,送信タイミング</t>
+          <t>IP移動電話端末自動再発信|IP移動電話端末 自動再発信 3回以内 3分 送信タイミング</t>
         </is>
       </c>
     </row>
@@ -48006,7 +48006,7 @@
       </c>
       <c r="W496" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,アクセス制御,変更,管理,記録</t>
+          <t>専用通信回線設備等端末変更|専用通信回線設備等端末 アクセス制御 変更 管理 記録</t>
         </is>
       </c>
     </row>
@@ -48106,7 +48106,7 @@
       </c>
       <c r="W497" t="inlineStr">
         <is>
-          <t>信号周波数偏差,±1.5%,ミニマムポーズ,信号送出時間,高群周波数,押しボタンダイヤル</t>
+          <t>信号周波数偏差|信号周波数偏差 ±1.5% ミニマムポーズ 信号送出時間 高群周波数</t>
         </is>
       </c>
     </row>
@@ -48206,7 +48206,7 @@
       </c>
       <c r="W498" t="inlineStr">
         <is>
-          <t>絶対レベル,有効電力,1mW,デシベル,有線電気通信法</t>
+          <t>絶対レベル定義|絶対レベル 有効電力 1mW デシベル 有線電気通信法</t>
         </is>
       </c>
     </row>
@@ -48295,7 +48295,7 @@
       </c>
       <c r="W499" t="inlineStr">
         <is>
-          <t>架空電線,強電流電線,支持物,30センチメートル,有線電気通信設備令</t>
+          <t>架空電線強電流電線支持物|架空電線 強電流電線 支持物 30センチメートル 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -48387,7 +48387,7 @@
       </c>
       <c r="W500" t="inlineStr">
         <is>
-          <t>横断歩道橋,架空電線,3メートル,有線電気通信設備令</t>
+          <t>架空電線横断歩道橋3m|架空電線 横断歩道橋 路面3メートル 有線電気通信設備令</t>
         </is>
       </c>
     </row>
@@ -48479,7 +48479,7 @@
       </c>
       <c r="W501" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,アクセス管理者,有効性,高度化</t>
+          <t>アクセス管理者有効性|アクセス管理者 アクセス制御機能 有効性 高度化 不正アクセス禁止法</t>
         </is>
       </c>
     </row>
@@ -48573,7 +48573,7 @@
       </c>
       <c r="W502" t="inlineStr">
         <is>
-          <t>電子署名法,真正に成立,推定,暗号化,電磁的記録</t>
+          <t>電子署名法真正|電子署名法 真正に成立 推定 暗号化ではなく 本人による署名</t>
         </is>
       </c>
     </row>

--- a/工事担任者問題20260523.xlsx
+++ b/工事担任者問題20260523.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON OLT ONU,OLT|OLT GE-PON 光加入者線終端装置,ONU|ONU GE-PON 光網終端装置,TDMA|TDMA GE-PON 上り信号 衝突回避,LLID|LLID GE-PON 論理リンクID</t>
+          <t>GE-PON|GE-PON 工事担任者,OLT|OLT 工事担任者,ONU|ONU 工事担任者,TDMA|TDMA 工事担任者,LLID|LLID 工事担任者</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>IP-PBX|IP-PBX VoIPゲートウェイ アナログ電話,VoIPゲートウェイ|VoIPゲートウェイ IP-PBX アナログ変換,IPセントレックス|IPセントレックス クラウドPBX SIP</t>
+          <t>IP-PBX|IP-PBX 工事担任者,VoIPゲートウェイ|VoIPゲートウェイ 工事担任者,IPセントレックス|IPセントレックス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>IEEE802.3at|IEEE802.3at PoE PSE PD 給電規格,PSE|PSE PoE 給電機器 IEEE802.3at</t>
+          <t>IEEE802.3at|IEEE802.3at 工事担任者,PSE|PSE PoE 工事担任者</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>レイヤ3スイッチ|レイヤ3スイッチ ルーティング RIP OSPF,RIP|RIP OSPF ルーティングプロトコル,OSPF|OSPF RIP ルーティングプロトコル</t>
+          <t>レイヤ3スイッチ|レイヤ3スイッチ 工事担任者,RIP|RIP OSPF ルーティングプロトコル 工事担任者,OSPF|OSPF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SPD|SPD サージ防護デバイス バリスタ,バリスタ|バリスタ SPD 非線形素子 サージ防護</t>
+          <t>SPD|SPD 工事担任者,バリスタ|バリスタ SPD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10GBASE-LR|10GBASE-LR 64B/66B 符号化方式,64B/66B|64B/66B 10GBASE-LR 符号化</t>
+          <t>10GBASE-LR|10GBASE-LR 工事担任者,64B/66B|64B/66B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SS方式|SS方式 シングルスター 光ファイバ 1対1接続,PDS方式|PDS方式 PON 光受動素子 分岐</t>
+          <t>SS方式|SS方式 光ファイバ 工事担任者,PDS方式|PDS方式 PON 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>HFC|HFC Hybrid Fiber Coaxial 光ノード 同軸ケーブル,FTTH|FTTH 光ファイバ 全区間</t>
+          <t>HFC|HFC 工事担任者,FTTH|FTTH 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>IPv6|IPv6 パケット分割 送信元ノード,IPv4|IPv4 DF TTL パケット分割 中継</t>
+          <t>IPv6|IPv6 パケット分割 工事担任者,IPv4|IPv4 DF パケット分割 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS LER MPLS イーサネット転送,LER|LER EoMPLS ラベルエッジルータ,MPLS|MPLS LER LSR ラベルスイッチング</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER MPLS 工事担任者,MPLS|MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 スタック 任意コード実行</t>
+          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>CHAP|CHAP チャレンジ・レスポンス 認証,PAP|PAP 平文認証 パスワード</t>
+          <t>CHAP|CHAP 工事担任者,PAP|PAP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>TLS|TLS HTTPS 暗号化 スニッフィング対策,スニッフィング|スニッフィング 盗聴 TLS 暗号化対策</t>
+          <t>TLS|TLS 工事担任者,スニッフィング|スニッフィング 暗号化対策 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>syslog|syslog UDP ログ管理 リモート転送</t>
+          <t>syslog|syslog 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>JIS Q 27001|JIS Q 27001 ISMS 情報セキュリティ管理</t>
+          <t>JIS Q 27001|JIS Q 27001 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>挿入法|挿入法 光ファイバ損失 挿入損失測定,カットバック法|カットバック法 光ファイバ損失 破壊試験,OTDR|OTDR 光ファイバ 後方散乱光 損失測定</t>
+          <t>挿入法|挿入法 光ファイバ損失 工事担任者,カットバック法|カットバック法 工事担任者,OTDR|OTDR 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>POF|POF プラスチック光ファイバ アクリル フッ素樹脂</t>
+          <t>POF|POF プラスチック光ファイバ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>OTDR法|OTDR法 後方散乱光 光ファイバ損失試験 JIS C 6823,JIS C 6823|JIS C 6823 光ファイバ損失試験 OTDR</t>
+          <t>OTDR法|OTDR法 工事担任者,JIS C 6823|JIS C 6823 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>T568B|T568B RJ-45 心線配色 UTPケーブル配線規格</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 水平配線 チャネル最大長 クラスE</t>
+          <t>JIS X 5150|JIS X 5150 水平ケーブル最大長 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 反射減衰量 挿入損失 測定規定</t>
+          <t>JIS X 5150|JIS X 5150 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>OTDR|OTDR ダイナミックレンジ 後方散乱光 パルスパワー,ダイナミックレンジ|OTDRダイナミックレンジ 測定範囲 後方散乱光</t>
+          <t>OTDR|OTDR ダイナミックレンジ 工事担任者,ダイナミックレンジ|ダイナミックレンジ OTDR 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>CSMA/CD|CSMA/CD 全二重 半二重 衝突 イーサネット,全二重通信|全二重通信 CSMA/CD 衝突なし イーサネット</t>
+          <t>CSMA/CD|CSMA/CD 工事担任者,全二重通信|全二重通信 CSMA/CD 衝突 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>施工計画書|施工計画書 受注者 監督員 工事管理</t>
+          <t>施工計画書|施工計画書 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>アローダイアグラム|アローダイアグラム クリティカルパス PERT 工程管理,クリティカルパス|クリティカルパス トータルフロート アローダイアグラム,トータルフロート|トータルフロート クリティカルパス フリーフロート</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者,クリティカルパス|クリティカルパス 工事担任者,トータルフロート|トータルフロート 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>基礎的電気通信役務|基礎的電気通信役務 電気通信事業法 適切公平安定</t>
+          <t>基礎的電気通信役務|基礎的電気通信役務 電気通信事業法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>管理規程|管理規程 電気通信事業法 確実かつ安定的</t>
+          <t>管理規程|管理規程 電気通信事業法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>技術基準適合認定|技術基準適合認定 登録認定機関 表示 端末機器</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>端末設備|端末設備 技術基準 電気通信事業法 接続検査</t>
+          <t>端末設備|端末設備 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>重要通信|重要通信 緊急通信 電気通信事業法 優先</t>
+          <t>重要通信|重要通信 電気通信事業法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>工事担任者|工事担任者 資格者証 端末設備 知識技術向上</t>
+          <t>工事担任者資格|工事担任者 資格者証 端末設備</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>資格者証|資格者証 再交付 書換え交付 工事担任者</t>
+          <t>資格者証|資格者証 再交付 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号|技術基準適合認定番号 先頭文字 端末機器</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>有線電気通信法|有線電気通信法 総務大臣 立入検査 報告</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>有線電気通信設備令|有線電気通信設備令 技術基準 保安</t>
+          <t>有線電気通信設備令|有線電気通信設備令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>アナログ電話用設備|アナログ電話用設備 端末設備等規則 アナログ信号,専用通信回線設備|専用通信回線設備 端末設備等規則 特定利用者</t>
+          <t>アナログ電話用設備|アナログ電話用設備 端末設備等規則 工事担任者,専用通信回線設備|専用通信回線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>分界点|分界点 端末設備 事業用電気通信設備 切り離し</t>
+          <t>分界点|分界点 端末設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>直流回路|直流回路 アナログ電話用設備 交換設備 動作制御</t>
+          <t>直流回路|直流回路 アナログ電話用設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>評価雑音電力|評価雑音電力 実効的雑音電力 人間聴覚 端末設備等規則</t>
+          <t>評価雑音電力|評価雑音電力 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>識別符号|識別符号 無線設備 通信路設定 照合</t>
+          <t>識別符号|識別符号 無線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル信号|押しボタンダイヤル信号 ダイヤル番号 16種類 ミニマムポーズ</t>
+          <t>押しボタンダイヤル信号|押しボタンダイヤル信号 工事担任者,ミニマムポーズ|ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>絶縁抵抗|絶縁抵抗 配線設備 直流200V 1MΩ 有線電気通信設備令</t>
+          <t>絶縁抵抗|絶縁抵抗 配線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>自動再発信|自動再発信 アナログ電話端末 2回以内 3分間</t>
+          <t>自動再発信|自動再発信 アナログ電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>初期識別符号|初期識別符号 変更を促す機能 アクセス制御 端末設備等規則</t>
+          <t>初期識別符号|初期識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>漏話減衰量|漏話減衰量 専用通信回線設備等端末 1500Hz 70dB</t>
+          <t>漏話減衰量|漏話減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>有線電気通信設備令|有線電気通信設備令 架空電線 電柱 安全係数</t>
+          <t>架空電線|架空電線 電柱 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>有線電気通信法|有線電気通信法 電線 強電流電線 定義</t>
+          <t>有線電気通信法|有線電気通信法 電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>有線電気通信設備令|有線電気通信設備令 屋内電線 強電流電線 離隔距離</t>
+          <t>屋内電線|屋内電線 強電流電線 離隔距離 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法|不正アクセス禁止法 アクセス制御機能 制限を免れる</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>電子署名法|電子署名法 電磁的記録 真正成立 推定</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>10G-EPON|10G-EPON IEEE802.3av FEC 64B/66B,XGS-PON|XGS-PON ITU-T G.9807 10Gbps対称,FEC|FEC 前方誤り訂正 10G-EPON</t>
+          <t>10G-EPON|10G-EPON 工事担任者,XGS-PON|XGS-PON 工事担任者,FEC|FEC 10G-EPON 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>SIPサーバ|SIPサーバ レジストラ プロキシ リダイレクト UAC,レジストラ|レジストラ SIPサーバ 登録要求 REGISTER,UAC|UAC SIPクライアント 発信側</t>
+          <t>SIPサーバ|SIPサーバ 工事担任者,レジストラ|レジストラ SIP 工事担任者,UAC|UAC SIP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>IEEE802.3at|IEEE802.3at PoE Type1 Class0 350mA</t>
+          <t>IEEE802.3at|IEEE802.3at Type1 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>ZigBee|ZigBee IEEE802.15.4 センサネットワーク 250kbps 65535台</t>
+          <t>ZigBee|ZigBee 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>コモンモードチョークコイル|コモンモードチョークコイル EMC ノイズ対策,フェライトコア|フェライトコア 高周波ノイズ インダクタンス EMC</t>
+          <t>コモンモードチョークコイル|コモンモードチョークコイル 工事担任者,フェライトコア|フェライトコア EMC 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>NRZI|NRZI 2値符号 AMI MLT-3 比較,AMI|AMI 3値符号 NRZIとの違い</t>
+          <t>NRZI|NRZI 工事担任者,AMI|AMI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>FTTB|FTTB VDSL 集合住宅 光ファイバ 既設電話線,VDSL|VDSL FTTB 既設電話線 高速伝送</t>
+          <t>FTTB|FTTB 工事担任者,VDSL|VDSL 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>IPv6マルチキャスト|IPv6 マルチキャストアドレス ff 先頭8ビット</t>
+          <t>IPv6|IPv6 マルチキャスト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>PLC|PLC Packet Loss Concealment パケット損失補間 VoIP</t>
+          <t>PLC|PLC パケット損失補間 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>IP-VPN|IP-VPN MPLS レイヤ3 広域イーサネット比較,広域イーサネット|広域イーサネット レイヤ2 IP-VPN比較</t>
+          <t>IP-VPN|IP-VPN 工事担任者,広域イーサネット|広域イーサネット 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>TCPスキャン|TCP SYNスキャン ポートスキャン ステルス</t>
+          <t>TCPスキャン|TCP SYNスキャン 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>RSA暗号|RSA暗号 素因数分解 公開鍵暗号,ブロック暗号|ブロック暗号 ストリーム暗号 違い 暗号方式</t>
+          <t>RSA暗号|RSA暗号 工事担任者,ブロック暗号|ブロック暗号 ストリーム暗号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>パケットフィルタリング|パケットフィルタリング ファイアウォール IPアドレス ポート番号</t>
+          <t>パケットフィルタリング|パケットフィルタリング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>ペネトレーションテスト|ペネトレーションテスト 侵入テスト 脆弱性診断</t>
+          <t>ペネトレーションテスト|ペネトレーションテスト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>JIS Q 27001|JIS Q 27001 ISMS 情報セキュリティ方針</t>
+          <t>JIS Q 27001|JIS Q 27001 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>光導通試験|光導通試験 励振用光ファイバ SI形 GI形,PINホトダイオード|PINホトダイオード 光検出器 受感面</t>
+          <t>光導通試験|光導通試験 工事担任者,PINホトダイオード|PINホトダイオード 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>フリーアクセスフロア|フリーアクセスフロア OAフロア 不陸調整</t>
+          <t>フリーアクセスフロア|フリーアクセスフロア 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>PoEオルタナティブA|PoE オルタナティブA ピン1 2 3 6 データ信号線,PoEオルタナティブB|PoE オルタナティブB ピン4 5 7 8 予備ペア</t>
+          <t>PoEオルタナティブA|PoE オルタナティブA 工事担任者,PoEオルタナティブB|PoE オルタナティブB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>プライベートIPアドレス|プライベートIPアドレス クラスA B C 範囲</t>
+          <t>プライベートIPアドレス|プライベートIPアドレス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 クロスコネクト クラスE 水平ケーブル最大長</t>
+          <t>JIS X 5150|JIS X 5150 クロスコネクト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>MPOコネクタ|MPOコネクタ 多心光コネクタ 12心 24心 プッシュプル</t>
+          <t>MPOコネクタ|MPOコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>挿入損失法|挿入損失法 カットバック法 OTDR 非破壊測定 比較</t>
+          <t>挿入損失法|挿入損失法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>STP|STP IEEE802.1D スパニングツリー ループ防止,IEEE802.1D|IEEE802.1D STP スパニングツリープロトコル</t>
+          <t>STP|STP IEEE802.1D 工事担任者,IEEE802.1D|IEEE802.1D 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>ヒストグラム|ヒストグラム パレート図 管理図 QC7つ道具 違い,パレート図|パレート図 累積度数 QC7つ道具</t>
+          <t>ヒストグラム|ヒストグラム QC 工事担任者,パレート図|パレート図 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>クリティカルパス|クリティカルパス トータルフロート ゼロ アローダイアグラム</t>
+          <t>クリティカルパス|クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>業務改善命令|業務改善命令 電気通信事業法 対象 要件</t>
+          <t>業務改善命令|業務改善命令 電気通信事業法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>重要通信|重要通信 緊急通信 選挙管理機関 天災 電気通信事業法</t>
+          <t>重要通信|重要通信 緊急通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>業務改善命令|業務改善命令 重要通信 適切に配慮 電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 重要通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>管理規程|管理規程 確実かつ安定的 電気通信事業法</t>
+          <t>管理規程|管理規程 確実かつ安定的 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>端末設備接続拒否|端末設備 接続請求 拒否 電波 電気通信事業法</t>
+          <t>端末設備接続拒否|端末設備 接続請求 電波 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>第二級アナログ通信|第二級アナログ通信 工事担任者 回線数1以下 資格区分</t>
+          <t>第二級アナログ通信|第二級アナログ通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>専用設備接続|専用設備 工事担任者 不要 端末設備等規則</t>
+          <t>専用設備|専用設備 工事担任者不要 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号|技術基準適合認定番号 先頭文字 IP電話用設備 E</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 IP電話 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>有線電気通信法|有線電気通信法 本邦外 総務大臣 許可</t>
+          <t>有線電気通信法|有線電気通信法 本邦外 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>有線電気通信法非常事態|有線電気通信法 非常事態 通信確保 命令</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>総合デジタル通信用設備|総合デジタル通信用設備 64kbps 符号音声影像 統合,専用通信回線設備|専用通信回線設備 特定利用者 専用 端末設備等規則</t>
+          <t>総合デジタル通信用設備|総合デジタル通信用設備 工事担任者,専用通信回線設備|専用通信回線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>接地抵抗100オーム|接地抵抗 100オーム以下 端末設備 金属筐体,絶縁耐力試験|絶縁耐力試験 使用電圧 10分間 端末設備</t>
+          <t>接地抵抗|接地抵抗 端末設備 工事担任者,絶縁耐力試験|絶縁耐力試験 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>識別符号|識別符号 無線設備 通信路設定 照合</t>
+          <t>識別符号|識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>端末設備識別機能|端末設備 事業用電気通信設備 漏えい 識別禁止,無線設備筐体|端末設備 無線設備 一の筐体 容易に開けられない</t>
+          <t>識別機能|識別機能 事業用電気通信設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>制御チャネル|制御チャネル 移動電話用設備 制御信号 通信路</t>
+          <t>制御チャネル|制御チャネル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>絶縁抵抗1MΩ|絶縁抵抗 直流200V 1MΩ 配線設備 有線電気通信設備令</t>
+          <t>絶縁抵抗|絶縁抵抗 直流200V 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>ダイヤル番号16種類|押しボタンダイヤル ダイヤル番号 16種類 0-9 記号</t>
+          <t>ダイヤル番号|ダイヤル番号 16種類 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末|専用通信回線設備等端末 直流電圧 電気的条件 光学的条件</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>IPを使用する専用通信回線設備等端末|IPを使用する専用通信回線設備等端末 アクセス制御</t>
+          <t>アクセス制御|アクセス制御 専用通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>IP電話端末発着信|IP電話端末 発信 応答 通信終了 メッセージ送出</t>
+          <t>IP電話端末|IP電話端末 発着信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>絶対レベル|絶対レベル 有効電力 1mW デシベル 端末設備等規則</t>
+          <t>絶対レベル|絶対レベル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>架空電線足場金具|架空電線 足場金具 地表1.8m 有線電気通信設備令</t>
+          <t>足場金具|足場金具 架空電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>架空電線鉄道横断|架空電線 鉄道軌道横断 軌条面6m 有線電気通信設備令</t>
+          <t>架空電線|架空電線 鉄道横断 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法|不正アクセス禁止法 アクセス管理者 アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>電子署名法|電子署名法 認証業務 電磁的記録</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON OLT P2MPディスカバリ マルチポイントMAC,P2MPディスカバリ|P2MPディスカバリ GE-PON ONU自動発見</t>
+          <t>GE-PON|GE-PON 工事担任者,P2MPディスカバリ|P2MPディスカバリ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>IP-PBX|IP-PBX ハードウェアタイプ ソフトウェアタイプ 比較,IPセントレックス|IPセントレックス クラウドPBX 通信事業者</t>
+          <t>IP-PBX|IP-PBX 工事担任者,IPセントレックス|IPセントレックス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>MIMO|MIMO 空間分割多重 複数アンテナ 無線LAN高速化,OFDM|OFDM MIMO 無線LAN 直交周波数分割多重</t>
+          <t>MIMO|MIMO 工事担任者,OFDM|OFDM 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>LPWA|LPWA Low Power Wide Area IoT 省電力 広域通信,LoRaWAN|LoRaWAN LPWA IoT 省電力無線</t>
+          <t>LPWA|LPWA 工事担任者,LoRaWAN|LoRaWAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>電磁エミッション|電磁エミッション EMC 電磁障害 イミュニティ JIS C 60050</t>
+          <t>電磁エミッション|電磁エミッション EMC 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>SS方式|SS方式 シングルスター 光ファイバ 1対1 PDS方式比較</t>
+          <t>SS方式|SS方式 工事担任者,PDS方式|PDS方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>8B1Q4|8B1Q4 1000BASE-T 4D-PAM5 符号化方式</t>
+          <t>8B1Q4|8B1Q4 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>MACアドレス|MACアドレス NIC 48ビット 固有アドレス,FCS|FCS フレームチェックシーケンス 誤り検出</t>
+          <t>MACアドレス|MACアドレス 工事担任者,FCS|FCS MACフレーム 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>トンネリング|トンネリング IPv6 IPv4 カプセル化 移行技術,デュアルスタック|デュアルスタック IPv4 IPv6 両方実装</t>
+          <t>トンネリング|トンネリング IPv6 工事担任者,デュアルスタック|デュアルスタック 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS LER MPLS プリアンブル FCS 除去,LER|LER EoMPLS ラベルエッジルータ,MPLS|MPLS LER LSR ラベルスイッチング</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER MPLS 工事担任者,MPLS|MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>スマーフ攻撃|スマーフ攻撃 DoS ICMP ブロードキャスト IPスプーフィング</t>
+          <t>スマーフ攻撃|スマーフ攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>認証局|認証局 CA デジタル証明書 公開鍵 秘密鍵 署名</t>
+          <t>認証局|認証局 デジタル証明書 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 スタック 入力サイズ 脆弱性</t>
+          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>デフォルトアカウント|デフォルトアカウント 初期設定 無効化 セキュリティ対策</t>
+          <t>デフォルトアカウント|デフォルトアカウント 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>残留リスク|残留リスク リスクマネジメント 許容 ISMS</t>
+          <t>残留リスク|残留リスク ISMS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>挿入法|挿入法 光コネクタ 挿入損失測定 JIS C 6823,カットバック法|カットバック法 破壊試験 光ファイバ損失</t>
+          <t>挿入法|挿入法 工事担任者,カットバック法|カットバック法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>JIS C 0303|JIS C 0303 電気設備図記号 複合アウトレット</t>
+          <t>JIS C 0303|JIS C 0303 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>OTDR法|OTDR法 後方散乱光 光ファイバ損失 JIS C 6823,JIS C 6823|JIS C 6823 光ファイバ損失試験方法</t>
+          <t>OTDR法|OTDR法 工事担任者,JIS C 6823|JIS C 6823 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>T568B|T568B RJ-45 心線配色 UTPケーブル</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 インタコネクト クラスE 水平ケーブル最大長</t>
+          <t>JIS X 5150|JIS X 5150 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>OTDR|OTDR ダミー光ファイバ 測定不能領域 後方散乱光</t>
+          <t>OTDR|OTDR ダミー光ファイバ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>FASコネクタ|FASコネクタ 単心光コネクタ ドロップ光ファイバ 架空クロージャ</t>
+          <t>FASコネクタ|FASコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>細径インドア光ケーブル|細径インドア光ケーブル 低摩擦 集合住宅 押し込み工法</t>
+          <t>細径インドア光ケーブル|細径インドア光ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>工程管理|工程管理 出来形管理 施工管理 違い,出来形管理|出来形管理 工程管理 寸法数量 施工管理</t>
+          <t>工程管理|工程管理 出来形管理 工事担任者,出来形管理|出来形管理 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>アローダイアグラム|アローダイアグラム クリティカルパス トータルフロート PERT</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者,クリティカルパス|クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>資格者証交付要件|資格者証 罰金以上 5年 養成課程 工事担任者法</t>
+          <t>資格者証|資格者証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>自営電気通信設備接続拒否|自営電気通信設備 保持 経営困難 接続拒否 総務大臣</t>
+          <t>自営電気通信設備|自営電気通信設備 接続拒否 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>管理規程届出|管理規程 事業開始前 届出 許可ではない 電気通信事業法</t>
+          <t>管理規程|管理規程 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>技術基準適合認定取消|技術基準適合認定 不適合 表示なしとみなす 電気通信事業法</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>重要通信人命安全|重要通信 人命安全 火災 疫病 交通事故 緊急通信</t>
+          <t>重要通信|重要通信 人命安全 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>第一級デジタル通信|第一級デジタル通信 デジタル伝送路設備 総合デジタル除く,第一級アナログ通信|第一級アナログ通信 アナログ伝送路設備 総合デジタル</t>
+          <t>第一級デジタル通信|第一級デジタル通信 工事担任者,第一級アナログ通信|第一級アナログ通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>資格者証再交付|資格者証 再交付 汚破損 返納 10日以内</t>
+          <t>資格者証|資格者証 再交付 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号先頭文字|技術基準適合認定番号 先頭文字 移動電話A 総合デジタルC IP電話E</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>有線電気通信法立入検査|有線電気通信法 総務大臣 報告 立入検査</t>
+          <t>有線電気通信法|有線電気通信法 立入検査 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>有線電気通信設備変更届|有線電気通信設備 設置の場所 変更届 2週間前</t>
+          <t>有線電気通信設備令|有線電気通信設備令 変更届 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>IP電話端末|IP電話端末 IP電話用設備のみ 接続 端末設備等規則,絶対レベル|絶対レベル 有効電力 1mW デシベル</t>
+          <t>IP電話端末|IP電話端末 工事担任者,絶対レベル|絶対レベル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>音響衝撃防止|通話機能 音響衝撃 過大 防止機能 端末設備等規則</t>
+          <t>音響衝撃|音響衝撃 端末設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13919,7 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>配線設備絶縁抵抗|配線設備 絶縁抵抗 直流200V 1MΩ以上</t>
+          <t>配線設備|配線設備 絶縁抵抗 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>識別符号空き周波数|識別符号 無線設備 空き周波数判定 通信路設定</t>
+          <t>識別符号|識別符号 空き周波数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>絶縁抵抗値|絶縁抵抗 使用電圧300V以下0.2MΩ 300V超0.4MΩ</t>
+          <t>絶縁抵抗|絶縁抵抗 使用電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>移動電話端末発信|移動電話端末 発信要求信号 漏話減衰量 1500Hz</t>
+          <t>移動電話端末|移動電話端末 発信 工事担任者,漏話減衰量|漏話減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>信号送出時間50ms|押しボタンダイヤル 信号送出時間50ms ミニマムポーズ30ms</t>
+          <t>信号送出時間|信号送出時間 ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>分界点接地抵抗|分界点 接地抵抗100オーム 端末設備</t>
+          <t>分界点|分界点 接地抵抗 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>IP電話端末通信終了|IP電話端末 応答確認 2分以内 通信終了メッセージ</t>
+          <t>IP電話端末|IP電話端末 通信終了 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>自動再発信総合デジタル|総合デジタル通信用設備 自動再発信 チャネル切断</t>
+          <t>自動再発信|自動再発信 総合デジタル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>架空電線建造物離隔|架空電線 建造物 離隔距離 30センチメートル以下禁止</t>
+          <t>架空電線|架空電線 建造物 離隔距離 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>強電流電線重畳分離|強電流電線 重畳 分離 開閉 有線電気通信設備令</t>
+          <t>強電流電線|強電流電線 重畳 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>架空電線横断歩道橋|架空電線 横断歩道橋 路面3m以上 有線電気通信設備令</t>
+          <t>架空電線|架空電線 横断歩道橋 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法|不正アクセス禁止法 アクセス制御機能 制限を免れる</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>特定認証業務|特定認証業務 電子署名法 主務省令 本人のみ</t>
+          <t>特定認証業務|特定認証業務 電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15180,7 +15180,7 @@
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>10G-EPON|10G-EPON IEEE802.3av XGS-PON FEC 64B/66B</t>
+          <t>10G-EPON|10G-EPON 工事担任者,XGS-PON|XGS-PON 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>カットアンドスルー|カットアンドスルー ストアアンドフォワード スイッチ転送方式 比較</t>
+          <t>カットアンドスルー|カットアンドスルー 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>IEEE802.3bt|IEEE802.3bt Type4 Class8 90W PoE 4対給電</t>
+          <t>IEEE802.3bt|IEEE802.3bt 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15469,7 +15469,7 @@
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>ブロックACK|IEEE802.11n ブロックACK フレーム集約 スループット向上</t>
+          <t>ブロックACK|ブロックACK IEEE802.11n 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>SPD|SPD サージ防護デバイス バリスタ 非線形素子</t>
+          <t>SPD|SPD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>NRZI|NRZI 2値符号 AMI MLT-3 PAM-5 比較</t>
+          <t>NRZI|NRZI 工事担任者,AMI|AMI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>SS方式|SS方式 HFC PDS方式 光ファイバ 1対1接続</t>
+          <t>SS方式|SS方式 工事担任者,HFC|HFC 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>IaaS|IaaS PaaS SaaS クラウドサービス 比較</t>
+          <t>IaaS|IaaS PaaS SaaS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>ジッタバッファ|ジッタバッファ 揺らぎ吸収 VoIP 音声品質 パケット到着遅延</t>
+          <t>ジッタバッファ|ジッタバッファ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16047,7 +16047,7 @@
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS LER MPLS ラベルスイッチング ルーティング比較,LER|LER EoMPLS ラベルエッジルータ,LSR|LSR MPLS ラベルスイッチングルータ</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER 工事担任者,LSR|LSR MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>SEOポイズニング|SEOポイズニング 不正Webサイト 検索エンジン悪用</t>
+          <t>SEOポイズニング|SEOポイズニング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>チャレンジ・レスポンス|チャレンジ・レスポンス CHAP 認証方式</t>
+          <t>チャレンジ・レスポンス|チャレンジ・レスポンス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16336,7 +16336,7 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>MACアドレスフィルタリング|MACアドレスフィルタリング ANY接続拒否 無線LAN SSID</t>
+          <t>MACアドレスフィルタリング|MACアドレスフィルタリング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>IPsec|IPsec トランスポートモード トンネルモード VPN リモートアクセス</t>
+          <t>IPsec|IPsec 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16529,7 +16529,7 @@
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>アンチパスバック|アンチパスバック 入退室管理 再入室防止</t>
+          <t>アンチパスバック|アンチパスバック 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16624,7 +16624,7 @@
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>光導通試験励振|光導通試験 励振用光ファイバ SI形 GI形 コア径</t>
+          <t>光導通試験|光導通試験 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>POF|POF プラスチック光ファイバ フッ素樹脂 アクリル樹脂 比較</t>
+          <t>POF|POF プラスチック光ファイバ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>1000BASE-T|1000BASE-T UTP 8心全対 カテゴリ5e,1000BASE-TX|1000BASE-TX カテゴリ6 4心 1000BASE-T比較</t>
+          <t>1000BASE-T|1000BASE-T 工事担任者,1000BASE-TX|1000BASE-TX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>反射減衰量測定|反射減衰量 挿入損失 UTPケーブル 測定方法</t>
+          <t>反射減衰量|反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17021,7 +17021,7 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 クロスコネクト クラスE 水平ケーブル最大長</t>
+          <t>JIS X 5150|JIS X 5150 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>FASコネクタ|FASコネクタ ターミネーションコネクタ SC型 光キャビネット</t>
+          <t>FASコネクタ|FASコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>JIS X 5150反射減衰量|JIS X 5150 反射減衰量 クラスC D E 適用</t>
+          <t>JIS X 5150|JIS X 5150 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>融着接続気泡|融着接続 気泡 光ファイバカッタ 端面切断 やり直し</t>
+          <t>融着接続|融着接続 気泡 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>設計図書不整合|設計図書 不整合 発注者 受注者 確認指示</t>
+          <t>設計図書|設計図書 不整合 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17504,7 +17504,7 @@
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>アローダイアグラム|アローダイアグラム クリティカルパス フリーフロート PERT</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者,フリーフロート|フリーフロート 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>重要通信相互接続|重要通信 相互接続 電気通信事業者 連携</t>
+          <t>重要通信|重要通信 相互接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>重要通信緊急通信|重要通信 緊急通信 天災 選挙管理機関 電気通信事業法</t>
+          <t>重要通信|重要通信 緊急通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17785,7 +17785,7 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>業務改善命令重要通信|業務改善命令 重要通信 適切に配慮 電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 重要通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>管理規程確実安定|管理規程 確実かつ安定的 電気通信事業法</t>
+          <t>管理規程|管理規程 確実かつ安定的 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>端末設備接続拒否|端末設備 接続請求 電波 著しく不適当 拒否</t>
+          <t>端末設備|端末設備 接続請求 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>第一級デジタル通信|第一級デジタル通信 総合デジタル除く デジタル伝送路</t>
+          <t>第一級デジタル通信|第一級デジタル通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>資格者証書換え交付|資格者証 書換え交付 住所変更 再交付との違い</t>
+          <t>資格者証|資格者証 書換え交付 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号D|技術基準適合認定番号 デジタルデータ伝送用設備 D</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>有線電気通信法目的|有線電気通信法 設置及び使用 秩序 公共の福祉</t>
+          <t>有線電気通信法|有線電気通信法 目的 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>有線電気通信法非常事態|有線電気通信法 非常事態 通信確保 命令</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末|専用通信回線設備等端末 通話チャネル 制御チャネル 定義</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 工事担任者,通話チャネル|通話チャネル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18663,7 +18663,7 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>分界点鳴音|分界点 鳴音 事業用電気通信設備 告示条件</t>
+          <t>分界点|分界点 鳴音 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>事業用電気通信設備識別禁止|端末設備 事業用電気通信設備 漏えい 識別禁止</t>
+          <t>識別機能|識別機能 事業用電気通信設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>評価雑音電力値|評価雑音電力 実効的雑音電力 マイナス64dB マイナス58dB</t>
+          <t>評価雑音電力|評価雑音電力 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>配線設備強電流電線|配線設備 強電流電線 有線電気通信設備令 告示</t>
+          <t>配線設備|配線設備 強電流電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>ダイヤル番号16種類|押しボタンダイヤル ダイヤル番号 16種類 ミニマムポーズ</t>
+          <t>ダイヤル番号|ダイヤル番号 16種類 工事担任者,ミニマムポーズ|ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>IP移動電話端末128秒|IP移動電話端末 128秒 通信終了メッセージ 応答確認</t>
+          <t>IP移動電話端末|IP移動電話端末 128秒 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>漏話減衰量1500Hz|専用通信回線設備等端末 漏話減衰量 1500Hz 70dB</t>
+          <t>漏話減衰量|漏話減衰量 1500Hz 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末直流|専用通信回線設備等端末 直流電圧 電気的条件 光学的条件</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 直流電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>初期識別符号変更|初期識別符号 変更を促す機能 アクセス制御 端末設備等規則</t>
+          <t>初期識別符号|初期識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>音声周波高周波定義|音声周波 200Hz超3500Hz以下 高周波 3500Hz超 有線電気通信法</t>
+          <t>音声周波|音声周波 高周波 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>足場金具1.8m|足場金具 地表1.8メートル未満禁止 有線電気通信設備令</t>
+          <t>足場金具|足場金具 1.8メートル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>架空電線支持物離隔|架空電線 支持物 強電流電線 1メートル以上 有線電気通信設備令</t>
+          <t>架空電線|架空電線 支持物 離隔距離 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>アクセス管理者動作管理|アクセス管理者 動作を管理する者 不正アクセス禁止法</t>
+          <t>アクセス管理者|アクセス管理者 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>電子署名法流通|電子署名法 流通及び情報処理 公共の福祉</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20019,7 @@
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON OLT TDMA P2MPディスカバリ DBA,DBA|DBA動的帯域割当 GE-PON 上り帯域制御</t>
+          <t>GE-PON|GE-PON 工事担任者,DBA|DBA 動的帯域割当 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>クラウド型PBX|クラウド型PBX SIP IPセントレックス 比較,SIPアプリケーション層|SIP アプリケーション層 インターネット層 違い</t>
+          <t>クラウド型PBX|クラウド型PBX 工事担任者,SIP|SIP アプリケーション層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>IEEE802.3at Type1|IEEE802.3at Type1 Class0 350mA PoE</t>
+          <t>IEEE802.3at|IEEE802.3at Type1 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>IEEE802.11n|IEEE802.11n 2.4GHz 5GHz 両対応 IEEE802.11ax,IEEE802.11ax|IEEE802.11ax Wi-Fi6 2.4GHz 5GHz 6GHz</t>
+          <t>IEEE802.11n|IEEE802.11n 工事担任者,IEEE802.11ax|IEEE802.11ax Wi-Fi6 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>コモンモードノイズ|コモンモードノイズ ノーマルモードノイズ 誘導雑音 違い</t>
+          <t>コモンモードノイズ|コモンモードノイズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>10GBASE-LR|10GBASE-LR 64B/66B 符号化方式,64B/66B|64B/66B 10GBASE-LR スクランブル 符号化</t>
+          <t>10GBASE-LR|10GBASE-LR 工事担任者,64B/66B|64B/66B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>FM一括変換方式|FM一括変換方式 CATV 3GHz 光強度変調 映像伝送</t>
+          <t>FM一括変換方式|FM一括変換方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20687,7 +20687,7 @@
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>10GBASE-SR|10GBASE-SR 850nm マルチモード 10GBASE-LR比較</t>
+          <t>10GBASE-SR|10GBASE-SR 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20787,7 +20787,7 @@
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>ICMPv6|ICMPv6 IPv6 必須 PMTUD パケット分割</t>
+          <t>ICMPv6|ICMPv6 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20880,7 +20880,7 @@
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS LER MPLS L2ヘッダ プリアンブル FCS,MPLS|MPLS LER LSR ラベルスイッチング</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER MPLS 工事担任者,MPLS|MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>バックドア|バックドア マルウェア 再侵入 隠れた経路,フィッシング|フィッシング 偽サイト ID パスワード詐取 スキミング比較</t>
+          <t>バックドア|バックドア 工事担任者,フィッシング|フィッシング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>IPsec|IPsec トンネルモード トランスポートモード VPN</t>
+          <t>IPsec|IPsec 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>パケットフィルタリング|パケットフィルタリング ポートスキャン対策 ファイアウォール</t>
+          <t>パケットフィルタリング|パケットフィルタリング ポートスキャン 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21272,7 +21272,7 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>IPS|IPS IDS 不正アクセス検知 自動遮断 違い</t>
+          <t>IPS|IPS IDS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21372,7 +21372,7 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>アンチパスバック|アンチパスバック 入退室管理 再入室防止,ゾーニング|ゾーニング セキュリティ区画 ハウジングとの違い</t>
+          <t>アンチパスバック|アンチパスバック 工事担任者,ゾーニング|ゾーニング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>融着接続スクリーニング|融着接続 スクリーニング試験 引張試験 曲げ試験ではない</t>
+          <t>融着接続|融着接続 スクリーニング試験 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21573,7 +21573,7 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>1000BASE-TX|1000BASE-TX カテゴリ6 1000BASE-T比較,1000BASE-T|1000BASE-T カテゴリ5e 8心全対</t>
+          <t>1000BASE-TX|1000BASE-TX 工事担任者,1000BASE-T|1000BASE-T 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>交差接続|交差接続 クロスコネクト 光配線盤 ジャンパコード</t>
+          <t>交差接続|交差接続 クロスコネクト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>T568B|T568B RJ-45 ピン2番 橙色 心線配色</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 インタコネクト クラスE 81.5m 15m</t>
+          <t>JIS X 5150|JIS X 5150 インタコネクト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21954,7 +21954,7 @@
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>光キャビネット|光キャビネット 光ローゼット ドロップ光ファイバ インドア光ファイバ 違い</t>
+          <t>光キャビネット|光キャビネット 光ローゼット 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22046,7 +22046,7 @@
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>STP|STP IEEE802.1D スパニングツリー ループ防止</t>
+          <t>STP|STP IEEE802.1D 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>OTDRダイナミックレンジ|OTDR ダイナミックレンジ 後方散乱光 パルスパワー 増加</t>
+          <t>OTDRダイナミックレンジ|OTDR ダイナミックレンジ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>施工計画書|施工計画書 受注者作成 発注者監督員 工事管理</t>
+          <t>施工計画書|施工計画書 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>クリティカルパス|クリティカルパス トータルフロート アローダイアグラム PERT</t>
+          <t>クリティカルパス|クリティカルパス 工事担任者,トータルフロート|トータルフロート 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>資格者証交付要件|資格者証 罰金以上 5年 養成課程 工事担任者</t>
+          <t>資格者証|資格者証 罰金 5年 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>管理規程事業開始前|管理規程 事業開始前 届出 許可ではない 電気通信事業法</t>
+          <t>管理規程|管理規程 事業開始前 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22628,7 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>自営電気通信設備保持|自営電気通信設備 保持 経営困難 接続拒否 総務大臣認定</t>
+          <t>自営電気通信設備|自営電気通信設備 保持 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22718,7 +22718,7 @@
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>技術基準適合認定公示|技術基準適合認定 表示なしとみなす 総務大臣</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22811,7 +22811,7 @@
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>重要通信人命|重要通信 公共の利益 人命安全 火災 疫病</t>
+          <t>重要通信|重要通信 人命安全 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>第一級アナログ通信|第一級アナログ通信 アナログ伝送路設備 総合デジタル通信用設備</t>
+          <t>第一級アナログ通信|第一級アナログ通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23010,7 +23010,7 @@
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>資格者証再交付失った|資格者証 再交付 失った 写真1枚 資格者証添付不要</t>
+          <t>資格者証|資格者証 再交付 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23110,7 +23110,7 @@
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号E|技術基準適合認定番号 IP電話用設備 E</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23202,7 +23202,7 @@
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>有線電気通信法目的|有線電気通信法 設置及び使用 秩序 公共の福祉</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23294,7 +23294,7 @@
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>有線電気通信法非常事態|有線電気通信法 非常事態 他の者に使用させ 接続</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23399,7 +23399,7 @@
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末|専用通信回線設備等端末 デジタルデータ伝送用設備 接続</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>直流回路|直流回路 アナログ電話用設備 交換設備 動作制御</t>
+          <t>直流回路|直流回路 アナログ電話用設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>分界点事業用|分界点 事業用電気通信設備 端末設備 接続方式</t>
+          <t>分界点|分界点 事業用電気通信設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>絶縁抵抗300V以下|絶縁抵抗 300V以下 0.2MΩ 端末設備等規則</t>
+          <t>絶縁抵抗|絶縁抵抗 300V以下 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23786,7 +23786,7 @@
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>配線設備絶縁抵抗200V|配線設備 絶縁抵抗 直流200V 1MΩ 告示</t>
+          <t>配線設備|配線設備 絶縁抵抗 直流200V 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23891,7 +23891,7 @@
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>ミニマムポーズ最小値|ミニマムポーズ 最小値 押しボタンダイヤル 高群周波数</t>
+          <t>ミニマムポーズ|ミニマムポーズ 工事担任者,押しボタンダイヤル信号|押しボタンダイヤル信号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>アナログ電話端末緊急通報|アナログ電話端末 緊急通報 警察 海上保安 消防</t>
+          <t>緊急通報|緊急通報 アナログ電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24088,7 +24088,7 @@
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>IP電話端末自動再発信|IP電話端末 自動再発信 3分間 2回以内</t>
+          <t>自動再発信|自動再発信 IP電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>移動電話端末漏話|移動電話端末 漏話減衰量 1500Hz 70dB</t>
+          <t>漏話減衰量|漏話減衰量 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末ソフト|専用通信回線設備等端末 ソフトウェア更新 アクセス制御 電力停止</t>
+          <t>アクセス制御|アクセス制御 ソフトウェア更新 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24363,7 +24363,7 @@
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>有線電気通信設備保安|有線電気通信設備 絶縁機能 避雷機能 保安機能</t>
+          <t>保安機能|保安機能 有線電気通信設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24468,7 +24468,7 @@
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>電線定義|電線 強電流電線 重畳 除く 有線電気通信法</t>
+          <t>電線|電線 強電流電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>屋内電線強電流ケーブル|屋内電線 強電流ケーブル 離隔距離 隔壁 有線電気通信設備令</t>
+          <t>屋内電線|屋内電線 強電流ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>アクセス制御機能有効性|アクセス管理者 アクセス制御機能 有効性検証 高度化 不正アクセス禁止法</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>電子署名真正成立|電子署名法 本人による署名 真正に成立 推定</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24829,7 +24829,7 @@
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>デュアルレートバースト受信器|デュアルレートバースト受信器 10G-EPON GE-PON 混在</t>
+          <t>デュアルレートバースト受信器|デュアルレートバースト受信器 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>IPセントレックス|IPセントレックス IP-PBX ハードウェアタイプ ソフトウェアタイプ</t>
+          <t>IPセントレックス|IPセントレックス 工事担任者,IP-PBX|IP-PBX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25022,7 +25022,7 @@
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>IEEE802.11ax 6GHz|IEEE802.11ax Wi-Fi6 6GHz ISMバンド 気象レーダ</t>
+          <t>IEEE802.11ax|IEEE802.11ax 6GHz 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25115,7 +25115,7 @@
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>IEEE802.3bt Type4|IEEE802.3bt Type4 Class8 90W 4対給電</t>
+          <t>IEEE802.3bt|IEEE802.3bt Type4 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25208,7 +25208,7 @@
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>誘導雷サージ|誘導雷サージ 電磁誘導 静電誘導 過電圧 雷保護</t>
+          <t>誘導雷サージ|誘導雷サージ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25301,7 +25301,7 @@
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>4D-PAM5|4D-PAM5 1000BASE-T 5値 4次元 符号化</t>
+          <t>4D-PAM5|4D-PAM5 1000BASE-T 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>CWDM|CWDM DWDM 波長多重 隣接波長間隔20nm アクセス系</t>
+          <t>CWDM|CWDM 工事担任者,DWDM|DWDM 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="W260" t="inlineStr">
         <is>
-          <t>SDN|SDN NFV データプレーン コントロールプレーン 分離</t>
+          <t>SDN|SDN 工事担任者,NFV|NFV 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>トンネリング|トンネリング デュアルスタック IPv4 IPv6 移行技術</t>
+          <t>トンネリング|トンネリング IPv6 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25685,7 +25685,7 @@
       </c>
       <c r="W262" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS LER LSR MPLS ラベルスイッチング ルーティング比較</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER 工事担任者,LSR|LSR MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25778,7 +25778,7 @@
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>OP25B|OP25B 迷惑メール対策 25番ポート SPF DKIM</t>
+          <t>OP25B|OP25B 工事担任者,DKIM|DKIM 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="W264" t="inlineStr">
         <is>
-          <t>デジタル署名送信否認|デジタル署名 公開鍵暗号 送信否認防止 共通鍵との違い</t>
+          <t>デジタル署名|デジタル署名 否認防止 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25978,7 +25978,7 @@
       </c>
       <c r="W265" t="inlineStr">
         <is>
-          <t>チェックサム|チェックサム ウイルス 改変検出 名前特定不可</t>
+          <t>チェックサム|チェックサム ウイルス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26069,7 @@
       </c>
       <c r="W266" t="inlineStr">
         <is>
-          <t>サニタイジング|サニタイジング XSS HTMLタグ JavaScript 無効化</t>
+          <t>サニタイジング|サニタイジング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26162,7 +26162,7 @@
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>ベースラインアプローチ|ベースラインアプローチ 詳細リスク分析 ISMS リスク分析手法比較</t>
+          <t>ベースラインアプローチ|ベースラインアプローチ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="W268" t="inlineStr">
         <is>
-          <t>光導通試験|光導通試験 励振用光ファイバ SI形 GI形 コア径,PINホトダイオード|PINホトダイオード 光検出器 受感面 大きくする</t>
+          <t>光導通試験|光導通試験 SI形 GI形 工事担任者,PINホトダイオード|PINホトダイオード 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26355,7 +26355,7 @@
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>PoEオルタナティブB|PoE オルタナティブB ピン4 5 7 8 予備ペア</t>
+          <t>PoEオルタナティブB|PoE オルタナティブB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26448,7 +26448,7 @@
       </c>
       <c r="W270" t="inlineStr">
         <is>
-          <t>光ファイバけん引速度|光ファイバケーブル けん引速度 20メートル以下 OITDA</t>
+          <t>けん引速度|光ファイバ けん引速度 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="W271" t="inlineStr">
         <is>
-          <t>プライベートIPアドレス|プライベートIPアドレス クラスB 172.16 範囲</t>
+          <t>プライベートIPアドレス|プライベートIPアドレス クラスB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="W272" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 クロスコネクト クラスF 水平ケーブル最大長</t>
+          <t>JIS X 5150|JIS X 5150 クラスF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26732,7 +26732,7 @@
       </c>
       <c r="W273" t="inlineStr">
         <is>
-          <t>CSMA/CD全二重|CSMA/CD 全二重 半二重 衝突 オートネゴシエーション,全二重通信|全二重通信 CSMA/CD 衝突なし 送受信独立チャネル</t>
+          <t>CSMA/CD|CSMA/CD 工事担任者,全二重通信|全二重通信 CSMA/CD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26825,7 +26825,7 @@
       </c>
       <c r="W274" t="inlineStr">
         <is>
-          <t>MPOコネクタ|MPOコネクタ 多心光コネクタ 12心 24心 プッシュプル</t>
+          <t>MPOコネクタ|MPOコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>細径インドア光ケーブル|細径インドア光ケーブル 低摩擦 集合住宅 押し込み工法</t>
+          <t>細径インドア光ケーブル|細径インドア光ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27024,7 +27024,7 @@
       </c>
       <c r="W276" t="inlineStr">
         <is>
-          <t>KY活動|KY活動 危険予知 ほう・れん・そう 安全管理 違い</t>
+          <t>KY活動|KY活動 危険予知 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27125,7 +27125,7 @@
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>アローダイアグラム|アローダイアグラム クリティカルパス トータルフロート PERT</t>
+          <t>クリティカルパス|クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27226,7 +27226,7 @@
       </c>
       <c r="W278" t="inlineStr">
         <is>
-          <t>技術基準責任分界|技術基準 責任の分界 設置の場所 電気通信事業法</t>
+          <t>技術基準|技術基準 責任の分界 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="W279" t="inlineStr">
         <is>
-          <t>業務改善命令修理|業務改善命令 修理 支障 電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27407,7 +27407,7 @@
       </c>
       <c r="W280" t="inlineStr">
         <is>
-          <t>技術基準修理改造|技術基準 修理 改造 使用制限 総務大臣</t>
+          <t>技術基準|技術基準 修理 改造 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27500,7 +27500,7 @@
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>端末設備接続拒否電波|端末設備 接続請求 電波 著しく不適当</t>
+          <t>端末設備|端末設備 接続請求 電波 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27595,7 +27595,7 @@
       </c>
       <c r="W282" t="inlineStr">
         <is>
-          <t>重要通信生活基盤|重要通信 気象 水象 生活基盤 緊急通信</t>
+          <t>重要通信|重要通信 生活基盤 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27685,7 +27685,7 @@
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>第二級デジタル通信|第二級デジタル通信 1Gbps以下 インターネット接続</t>
+          <t>第二級デジタル通信|第二級デジタル通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="W284" t="inlineStr">
         <is>
-          <t>資格者証書換え交付|資格者証 書換え交付 住所変更 返納10日以内</t>
+          <t>資格者証|資格者証 書換え交付 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27889,7 +27889,7 @@
       </c>
       <c r="W285" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号C|技術基準適合認定番号 総合デジタル通信用設備 C</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27994,7 +27994,7 @@
       </c>
       <c r="W286" t="inlineStr">
         <is>
-          <t>有線電気通信法|有線電気通信法 設置及び使用 秩序 公共の福祉</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28086,7 +28086,7 @@
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>有線電気通信設備本邦外|有線電気通信設備 本邦外 総務大臣 許可</t>
+          <t>有線電気通信設備令|有線電気通信設備令 本邦外 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28192,7 +28192,7 @@
       </c>
       <c r="W288" t="inlineStr">
         <is>
-          <t>IP電話端末接続|IP電話端末 IP電話用設備のみ デジタルデータ伝送用設備ではない</t>
+          <t>IP電話端末|IP電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>端末設備識別鳴音|端末設備 事業用電気通信設備 漏えい 識別禁止 鳴音</t>
+          <t>識別機能|識別機能 鳴音 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28392,7 +28392,7 @@
       </c>
       <c r="W290" t="inlineStr">
         <is>
-          <t>接地抵抗100オーム|接地抵抗 100オーム以下 端末設備 金属筐体</t>
+          <t>接地抵抗|接地抵抗 100オーム 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>評価雑音電力マイナス58dB|評価雑音電力 マイナス64dB マイナス58dB 端末設備等規則</t>
+          <t>評価雑音電力|評価雑音電力 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28591,7 +28591,7 @@
       </c>
       <c r="W292" t="inlineStr">
         <is>
-          <t>識別符号無線設備|識別符号 無線設備 交換設備ではない 端末設備等規則</t>
+          <t>識別符号|識別符号 無線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28690,7 +28690,7 @@
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>信号周波数偏差|信号周波数偏差 ±1.5% ミニマムポーズ 周期 押しボタンダイヤル</t>
+          <t>信号周波数偏差|信号周波数偏差 工事担任者,ミニマムポーズ|ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="W294" t="inlineStr">
         <is>
-          <t>移動電話端末自動再発信|移動電話端末 漏話減衰量 自動再発信 2回以内 3分</t>
+          <t>漏話減衰量|漏話減衰量 工事担任者,自動再発信|自動再発信 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28881,7 +28881,7 @@
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>IP電話端末送出電力|IP電話端末 送出電力 マイナス3dBm アナログ電話</t>
+          <t>送出電力|送出電力 IP電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="W296" t="inlineStr">
         <is>
-          <t>IP移動電話端末128秒|IP移動電話端末 128秒 送信タイミング 総務大臣告示</t>
+          <t>IP移動電話端末|IP移動電話端末 128秒 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29073,7 +29073,7 @@
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末変更|専用通信回線設備等端末 アクセス制御 設定変更</t>
+          <t>アクセス制御|アクセス制御 専用通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29178,7 +29178,7 @@
       </c>
       <c r="W298" t="inlineStr">
         <is>
-          <t>絶縁電線定義|絶縁電線 絶縁物のみ 保護物含まず 有線電気通信法</t>
+          <t>絶縁電線|絶縁電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>足場金具1.8m|足場金具 地表1.8メートル未満禁止 架空電線 離隔距離30cm</t>
+          <t>足場金具|足場金具 1.8メートル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="W300" t="inlineStr">
         <is>
-          <t>架空電線道路上|架空電線 道路上 5メートル以上 有線電気通信設備令</t>
+          <t>架空電線|架空電線 道路上 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29461,7 +29461,7 @@
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法電子計算機|不正アクセス禁止法 電子計算機 犯罪防止 アクセス制御</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29553,7 +29553,7 @@
       </c>
       <c r="W302" t="inlineStr">
         <is>
-          <t>特定認証業務|特定認証業務 電子署名法 本人のみ 主務省令</t>
+          <t>特定認証業務|特定認証業務 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON OLT TDMA LLID DBA P2MPディスカバリ,DBA|DBA動的帯域割当 GE-PON OLT 上り帯域</t>
+          <t>GE-PON|GE-PON 工事担任者,DBA|DBA 動的帯域割当 工事担任者,LLID|LLID 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29751,7 +29751,7 @@
       </c>
       <c r="W304" t="inlineStr">
         <is>
-          <t>SIPサーバ|SIPサーバ レジストラ プロキシ リダイレクト UAC 比較,レジストラ|レジストラ SIPサーバ 登録要求 REGISTER メッセージ</t>
+          <t>SIPサーバ|SIPサーバ 工事担任者,レジストラ|レジストラ SIP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29844,7 +29844,7 @@
       </c>
       <c r="W305" t="inlineStr">
         <is>
-          <t>OFDMA|OFDMA IEEE802.11ax Wi-Fi6 時分割 サブキャリア</t>
+          <t>OFDMA|OFDMA IEEE802.11ax 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="W306" t="inlineStr">
         <is>
-          <t>IEEE802.3at Type1|IEEE802.3at Type1 Class0 350mA 44-57V PSE</t>
+          <t>IEEE802.3at|IEEE802.3at 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30030,7 +30030,7 @@
       </c>
       <c r="W307" t="inlineStr">
         <is>
-          <t>等電位ボンディング|等電位ボンディング SPD 雷保護 電位差低減 JIS C 5381</t>
+          <t>等電位ボンディング|等電位ボンディング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30123,7 +30123,7 @@
       </c>
       <c r="W308" t="inlineStr">
         <is>
-          <t>10GBASE-LR|10GBASE-LR 64B/66B 符号化方式 スクランブル</t>
+          <t>10GBASE-LR|10GBASE-LR 工事担任者,64B/66B|64B/66B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30213,7 +30213,7 @@
       </c>
       <c r="W309" t="inlineStr">
         <is>
-          <t>FTTB|FTTB VDSL 集合住宅 光ファイバ 既設電話線,VDSL|VDSL FTTB 集合住宅 既設電話線 高速伝送</t>
+          <t>FTTB|FTTB 工事担任者,VDSL|VDSL 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="W310" t="inlineStr">
         <is>
-          <t>NFV|NFV SDN 仮想化 ルータ ファイアウォール汎用サーバ</t>
+          <t>NFV|NFV 工事担任者,SDN|SDN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30399,7 +30399,7 @@
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>ホップリミット|ホップリミット IPv6 TTL IPv4 ルータ パケット破棄</t>
+          <t>ホップリミット|ホップリミット IPv6 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30489,7 +30489,7 @@
       </c>
       <c r="W312" t="inlineStr">
         <is>
-          <t>MACアドレス|MACアドレス NIC 48ビット FCS フレーム誤り検出</t>
+          <t>MACアドレス|MACアドレス 工事担任者,FCS|FCS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30582,7 +30582,7 @@
       </c>
       <c r="W313" t="inlineStr">
         <is>
-          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 スタック 任意コード実行 脆弱性</t>
+          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30675,7 +30675,7 @@
       </c>
       <c r="W314" t="inlineStr">
         <is>
-          <t>バイオメトリクス認証|バイオメトリクス認証 本人拒否率 他人受入率 しきい値</t>
+          <t>バイオメトリクス認証|バイオメトリクス認証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30775,7 +30775,7 @@
       </c>
       <c r="W315" t="inlineStr">
         <is>
-          <t>UNIX root権限|UNIX root権限 アクセス権限 OS セキュリティ</t>
+          <t>UNIX|UNIX root権限 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30868,7 +30868,7 @@
       </c>
       <c r="W316" t="inlineStr">
         <is>
-          <t>最小特権の原則|最小特権の原則 アクセス権限 セキュリティ設計</t>
+          <t>最小特権の原則|最小特権の原則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="W317" t="inlineStr">
         <is>
-          <t>リスク特定|リスク特定 リスク分析 リスクレベル 違い ISMS</t>
+          <t>リスク特定|リスク特定 リスク分析 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31064,7 +31064,7 @@
       </c>
       <c r="W318" t="inlineStr">
         <is>
-          <t>光導通試験|光導通試験 SI形 GI形 コア径 PINホトダイオード</t>
+          <t>光導通試験|光導通試験 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="W319" t="inlineStr">
         <is>
-          <t>JIS C 0303|JIS C 0303 電気設備図記号 情報用アウトレット</t>
+          <t>JIS C 0303|JIS C 0303 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31233,7 +31233,7 @@
       </c>
       <c r="W320" t="inlineStr">
         <is>
-          <t>光ファイバ水平ラック固定|光ファイバケーブル 水平ラック 5メートル以下 固定 OITDA</t>
+          <t>けん引|光ファイバ 水平ラック固定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31326,7 +31326,7 @@
       </c>
       <c r="W321" t="inlineStr">
         <is>
-          <t>T568B|T568B RJ-45 ピン8番 茶色 心線配色</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31424,7 +31424,7 @@
       </c>
       <c r="W322" t="inlineStr">
         <is>
-          <t>JIS X 5150クラスF|JIS X 5150 インタコネクト クラスF 水平ケーブル最大長</t>
+          <t>JIS X 5150|JIS X 5150 クラスF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31522,7 +31522,7 @@
       </c>
       <c r="W323" t="inlineStr">
         <is>
-          <t>リバースペア|リバースペア スプリットペア クロスペア 配線不良 UTPケーブル</t>
+          <t>リバースペア|リバースペア 配線不良 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31615,7 +31615,7 @@
       </c>
       <c r="W324" t="inlineStr">
         <is>
-          <t>JIS X 5150反射減衰量|JIS X 5150 反射減衰量 3.0dB未満 参考とする</t>
+          <t>JIS X 5150|JIS X 5150 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="W325" t="inlineStr">
         <is>
-          <t>光キャビネット|光キャビネット 光ローゼット ドロップ光ファイバ 屋外壁面</t>
+          <t>光キャビネット|光キャビネット 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31801,7 +31801,7 @@
       </c>
       <c r="W326" t="inlineStr">
         <is>
-          <t>WBGT|WBGT 暑さ指数 熱中症 湿球黒球温度 熱ストレス</t>
+          <t>WBGT|WBGT 暑さ指数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="W327" t="inlineStr">
         <is>
-          <t>アローダイアグラム|アローダイアグラム クリティカルパス トータルフロート フリーフロート PERT</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者,トータルフロート|トータルフロート 工事担任者,フリーフロート|フリーフロート 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="W328" t="inlineStr">
         <is>
-          <t>業務改善命令対象|業務改善命令 通信秘密 差別的取扱い 重要通信 電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>資格者証交付要件|資格者証 罰金以上 5年 養成課程 総務大臣 工事担任者</t>
+          <t>資格者証|資格者証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32196,7 @@
       </c>
       <c r="W330" t="inlineStr">
         <is>
-          <t>技術基準責任分界|技術基準 責任の分界 設置の場所 電気通信事業法</t>
+          <t>技術基準|技術基準 責任の分界 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32288,7 +32288,7 @@
       </c>
       <c r="W331" t="inlineStr">
         <is>
-          <t>端末設備異常検査|端末設備 異常 電気通信役務 検査 利用者</t>
+          <t>端末設備|端末設備 異常 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32380,7 +32380,7 @@
       </c>
       <c r="W332" t="inlineStr">
         <is>
-          <t>重要通信生活基盤|重要通信 生活基盤 水道 ガス 緊急通信</t>
+          <t>重要通信|重要通信 生活基盤 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="W333" t="inlineStr">
         <is>
-          <t>第二級デジタル通信|第二級デジタル通信 1Gbps以下 64kbpsではない インターネット接続</t>
+          <t>第二級デジタル通信|第二級デジタル通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="W334" t="inlineStr">
         <is>
-          <t>資格者証返納10日|資格者証 返納 10日以内 知識及び技術 向上</t>
+          <t>資格者証|資格者証 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="W335" t="inlineStr">
         <is>
-          <t>技術基準適合認定映像面|技術基準適合認定 映像面 電磁的方法 表示方法</t>
+          <t>技術基準適合認定|技術基準適合認定 映像面 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="W336" t="inlineStr">
         <is>
-          <t>有線電気通信法本邦外|有線電気通信法 本邦外 電気通信事業者 設置</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="W337" t="inlineStr">
         <is>
-          <t>有線電気通信法非常事態|有線電気通信法 非常事態 通信確保 命令</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32961,7 +32961,7 @@
       </c>
       <c r="W338" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末|専用通信回線設備等端末 通話チャネル 制御チャネル 定義</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 工事担任者,通話チャネル|通話チャネル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="W339" t="inlineStr">
         <is>
-          <t>鳴音電気的音響的結合|鳴音 電気的 音響的結合 光学的ではない 端末設備等規則</t>
+          <t>鳴音|鳴音 電気的 音響的結合 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="W340" t="inlineStr">
         <is>
-          <t>配線設備損傷防止|配線設備 事業用電気通信設備 損傷 告示 設置方法</t>
+          <t>配線設備|配線設備 損傷防止 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="W341" t="inlineStr">
         <is>
-          <t>絶縁抵抗各値|絶縁抵抗 0.2MΩ 0.4MΩ 300V 1MΩ 配線設備</t>
+          <t>絶縁抵抗|絶縁抵抗 0.2MΩ 0.4MΩ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33347,7 +33347,7 @@
       </c>
       <c r="W342" t="inlineStr">
         <is>
-          <t>識別符号|識別符号 無線設備 通信路設定 照合</t>
+          <t>識別符号|識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33448,7 +33448,7 @@
       </c>
       <c r="W343" t="inlineStr">
         <is>
-          <t>ミニマムポーズ最小値|ミニマムポーズ 最小値 低群周波数 高群周波数 2周波電力差</t>
+          <t>ミニマムポーズ|ミニマムポーズ 工事担任者,低群周波数|低群周波数 高群周波数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="W344" t="inlineStr">
         <is>
-          <t>移動電話端末応答確認信号|移動電話端末 応答を確認する信号 端末設備等規則</t>
+          <t>応答を確認する信号|応答を確認する信号 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33636,7 +33636,7 @@
       </c>
       <c r="W345" t="inlineStr">
         <is>
-          <t>IP電話端末送出電力|IP電話端末 送出電力 マイナス3dBm 平均レベル</t>
+          <t>送出電力|送出電力 IP電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="W346" t="inlineStr">
         <is>
-          <t>IP移動電話端末128秒|IP移動電話端末 128秒 通信終了メッセージ 応答確認</t>
+          <t>IP移動電話端末|IP移動電話端末 128秒 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="W347" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末ただし書き|専用通信回線設備等端末 アクセス制御 初期識別符号 ただし書き</t>
+          <t>アクセス制御|アクセス制御 初期識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="W348" t="inlineStr">
         <is>
-          <t>強電流電線定義|強電流電線 導体 つり線 支線 含まない 有線電気通信法</t>
+          <t>強電流電線|強電流電線 定義 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34028,7 +34028,7 @@
       </c>
       <c r="W349" t="inlineStr">
         <is>
-          <t>電柱安全係数|電柱 安全係数 絶縁耐力ではない 有線電気通信設備令</t>
+          <t>電柱|電柱 安全係数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="W350" t="inlineStr">
         <is>
-          <t>有線電気通信設備設置|有線電気通信設備 絶縁電線 ケーブル 人体危害 有線電気通信設備令</t>
+          <t>有線電気通信設備令|有線電気通信設備令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34209,7 +34209,7 @@
       </c>
       <c r="W351" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法|不正アクセス禁止法 アクセス管理者 アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="W352" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 電磁的記録 作成者 電子署名法</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34389,7 +34389,7 @@
       </c>
       <c r="W353" t="inlineStr">
         <is>
-          <t>デュアルレートバースト受信器|デュアルレートバースト受信器 10G-EPON GE-PON 混在接続</t>
+          <t>デュアルレートバースト受信器|デュアルレートバースト受信器 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34482,7 +34482,7 @@
       </c>
       <c r="W354" t="inlineStr">
         <is>
-          <t>VoIPゲートウェイ|VoIPゲートウェイ デジタル式PBX IPネットワーク 変換</t>
+          <t>VoIPゲートウェイ|VoIPゲートウェイ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34588,7 +34588,7 @@
       </c>
       <c r="W355" t="inlineStr">
         <is>
-          <t>PoE Type2 Class4|PoE Type2 Class4 IEEE802.3at 34.2W 600mA</t>
+          <t>IEEE802.3at|IEEE802.3at Type2 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34681,7 +34681,7 @@
       </c>
       <c r="W356" t="inlineStr">
         <is>
-          <t>IEEE802.11n|IEEE802.11n IEEE802.11ax 2.4GHz 5GHz 両対応</t>
+          <t>IEEE802.11n|IEEE802.11n 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34774,7 +34774,7 @@
       </c>
       <c r="W357" t="inlineStr">
         <is>
-          <t>電圧スイッチング形SPD|電圧スイッチング形SPD SCR サイリスタ ガス入り放電管 サージ防護</t>
+          <t>電圧スイッチング形SPD|電圧スイッチング形SPD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="W358" t="inlineStr">
         <is>
-          <t>PCS物理層|PCS 1000BASE-T 物理層 符号化 PMA PMD</t>
+          <t>PCS|PCS 物理層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34960,7 +34960,7 @@
       </c>
       <c r="W359" t="inlineStr">
         <is>
-          <t>SS方式|SS方式 シングルスター PDS方式 PON 1対1</t>
+          <t>SS方式|SS方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35053,7 +35053,7 @@
       </c>
       <c r="W360" t="inlineStr">
         <is>
-          <t>PaaS|PaaS SaaS IaaS クラウドサービス ミドルウェア 比較</t>
+          <t>PaaS|PaaS SaaS IaaS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="W361" t="inlineStr">
         <is>
-          <t>IPv6マルチキャスト|IPv6 マルチキャスト ff先頭8ビット リンクローカル ユニークローカル</t>
+          <t>IPv6|IPv6 マルチキャスト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35244,7 +35244,7 @@
       </c>
       <c r="W362" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS LER MPLS プリアンブル SFD FCS 除去,MPLS|MPLS LER LSR ラベルスイッチング</t>
+          <t>EoMPLS|EoMPLS 工事担任者,MPLS|MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="W363" t="inlineStr">
         <is>
-          <t>パスワードリスト攻撃|パスワードリスト攻撃 辞書攻撃 不正ログイン 使い回し</t>
+          <t>パスワードリスト攻撃|パスワードリスト攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35430,7 +35430,7 @@
       </c>
       <c r="W364" t="inlineStr">
         <is>
-          <t>シングルサインオン|シングルサインオン SSO リスクベース認証 CHAP RADIUS</t>
+          <t>シングルサインオン|シングルサインオン 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35520,7 +35520,7 @@
       </c>
       <c r="W365" t="inlineStr">
         <is>
-          <t>スニッフィング対策TLS|スニッフィング TLS SMTP FTP 暗号化対策</t>
+          <t>スニッフィング|スニッフィング TLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="W366" t="inlineStr">
         <is>
-          <t>S/MIME|S/MIME デジタル証明書 電子メール暗号化 デジタル署名</t>
+          <t>S/MIME|S/MIME 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35719,7 +35719,7 @@
       </c>
       <c r="W367" t="inlineStr">
         <is>
-          <t>JIS Q 27001情報分類|JIS Q 27001 機密性 完全性 可用性 CIA 情報分類</t>
+          <t>JIS Q 27001|JIS Q 27001 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35795,7 +35795,7 @@
       </c>
       <c r="W368" t="inlineStr">
         <is>
-          <t>JIS C 0303|JIS C 0303 複合アウトレット 図記号 電気設備</t>
+          <t>JIS C 0303|JIS C 0303 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="W369" t="inlineStr">
         <is>
-          <t>融着接続アーク放電|融着接続 アーク放電 スクリーニング試験 引張試験 端面切断90度</t>
+          <t>融着接続|融着接続 アーク放電 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35989,7 +35989,7 @@
       </c>
       <c r="W370" t="inlineStr">
         <is>
-          <t>交差接続|交差接続 クロスコネクト 光配線盤 ジャンパコード</t>
+          <t>交差接続|交差接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36095,7 +36095,7 @@
       </c>
       <c r="W371" t="inlineStr">
         <is>
-          <t>挿入損失測定方法|挿入損失 直流ループ抵抗 測定方法 違い UTPケーブル</t>
+          <t>挿入損失|挿入損失 測定方法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36193,7 +36193,7 @@
       </c>
       <c r="W372" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 クロスコネクト クラスE 80.5m</t>
+          <t>JIS X 5150|JIS X 5150 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36286,7 +36286,7 @@
       </c>
       <c r="W373" t="inlineStr">
         <is>
-          <t>フラット型インドア光ケーブル|フラット型インドア光ケーブル 露出配線 固定ピン カーペット下</t>
+          <t>フラット型インドア光ケーブル|フラット型インドア光ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36387,7 +36387,7 @@
       </c>
       <c r="W374" t="inlineStr">
         <is>
-          <t>JIS X 5150クラスAB|JIS X 5150 反射減衰量 クラスA クラスB 適用外</t>
+          <t>JIS X 5150|JIS X 5150 クラスA クラスB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36480,7 +36480,7 @@
       </c>
       <c r="W375" t="inlineStr">
         <is>
-          <t>キンク|キンク UTPケーブル くの字型変形 ケーブル布設注意</t>
+          <t>キンク|キンク UTPケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="W376" t="inlineStr">
         <is>
-          <t>シューハート管理図|シューハート管理図 3シグマ 管理限界線 統計的品質管理</t>
+          <t>シューハート管理図|シューハート管理図 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36676,7 +36676,7 @@
       </c>
       <c r="W377" t="inlineStr">
         <is>
-          <t>クリティカルパス|クリティカルパス トータルフロート ゼロ アローダイアグラム PERT</t>
+          <t>クリティカルパス|クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36781,7 +36781,7 @@
       </c>
       <c r="W378" t="inlineStr">
         <is>
-          <t>端末設備接続拒否|端末設備 接続請求 利用者 著しく不適当 電気通信事業法</t>
+          <t>端末設備|端末設備 接続請求 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36873,7 +36873,7 @@
       </c>
       <c r="W379" t="inlineStr">
         <is>
-          <t>自営電気通信設備保持|自営電気通信設備 保持 経営困難 接続拒否 総務大臣認定</t>
+          <t>自営電気通信設備|自営電気通信設備 保持 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36965,7 +36965,7 @@
       </c>
       <c r="W380" t="inlineStr">
         <is>
-          <t>技術基準適合認定取消|技術基準適合認定 不適合 表示なしとみなす 電気通信事業法</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37057,7 +37057,7 @@
       </c>
       <c r="W381" t="inlineStr">
         <is>
-          <t>業務改善命令重要通信|業務改善命令 重要通信 適切に配慮 電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 重要通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37156,7 +37156,7 @@
       </c>
       <c r="W382" t="inlineStr">
         <is>
-          <t>重要通信治安天災|重要通信 治安 天災 新聞社 緊急通信</t>
+          <t>重要通信|重要通信 治安 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37246,7 +37246,7 @@
       </c>
       <c r="W383" t="inlineStr">
         <is>
-          <t>工事担任者資格区分|工事担任者 第一級アナログ 第二級デジタル 資格区分 比較</t>
+          <t>工事担任者資格区分|工事担任者 資格区分 比較</t>
         </is>
       </c>
     </row>
@@ -37340,7 +37340,7 @@
       </c>
       <c r="W384" t="inlineStr">
         <is>
-          <t>資格者証技術の向上|資格者証 技術の向上 書換え交付 住所変更</t>
+          <t>資格者証|資格者証 書換え交付 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="W385" t="inlineStr">
         <is>
-          <t>技術基準適合認定表示方法|技術基準適合認定 映像面 取扱説明書 包装 表示方法</t>
+          <t>技術基準適合認定|技術基準適合認定 表示方法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="W386" t="inlineStr">
         <is>
-          <t>有線電気通信法報告立入|有線電気通信法 総務大臣 報告 立入検査</t>
+          <t>有線電気通信法|有線電気通信法 立入検査 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37613,7 +37613,7 @@
       </c>
       <c r="W387" t="inlineStr">
         <is>
-          <t>有線電気通信設備変更届|有線電気通信設備 方式の別 設置の場所 2週間前</t>
+          <t>有線電気通信設備令|有線電気通信設備令 変更届 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37718,7 +37718,7 @@
       </c>
       <c r="W388" t="inlineStr">
         <is>
-          <t>デジタルデータ伝送用設備|デジタルデータ伝送用設備 総合デジタル通信用設備 違い 64kbps</t>
+          <t>デジタルデータ伝送用設備|デジタルデータ伝送用設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37810,7 +37810,7 @@
       </c>
       <c r="W389" t="inlineStr">
         <is>
-          <t>端末設備識別禁止|端末設備 事業用電気通信設備 漏えい 意図的識別禁止</t>
+          <t>識別機能|識別機能 漏えい 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37907,7 +37907,7 @@
       </c>
       <c r="W390" t="inlineStr">
         <is>
-          <t>接地抵抗100オーム|接地抵抗 100オーム以下 端末設備 金属筐体</t>
+          <t>接地抵抗|接地抵抗 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38006,7 +38006,7 @@
       </c>
       <c r="W391" t="inlineStr">
         <is>
-          <t>配線設備有線電気通信設備令|配線設備 強電流電線 有線電気通信設備令 評価雑音電力</t>
+          <t>有線電気通信設備令|有線電気通信設備令 評価雑音電力 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38098,7 +38098,7 @@
       </c>
       <c r="W392" t="inlineStr">
         <is>
-          <t>識別符号空き周波数|識別符号 無線設備 空き周波数判定 通信路設定</t>
+          <t>識別符号|識別符号 空き周波数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38203,7 +38203,7 @@
       </c>
       <c r="W393" t="inlineStr">
         <is>
-          <t>信号送出時間50ms|押しボタンダイヤル 信号送出時間50ms ミニマムポーズ30ms</t>
+          <t>信号送出時間|信号送出時間 50ms 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="W394" t="inlineStr">
         <is>
-          <t>移動電話端末自動再発信|移動電話端末 自動再発信 2回以内 3分 チャネル切断</t>
+          <t>自動再発信|自動再発信 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="W395" t="inlineStr">
         <is>
-          <t>IP電話端末緊急通報|IP電話端末 直流電圧 緊急通報 電気通信回線</t>
+          <t>IP電話端末|IP電話端末 緊急通報 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="W396" t="inlineStr">
         <is>
-          <t>IP移動電話端末送信タイミング|IP移動電話端末 128秒 送信タイミング 総務大臣告示</t>
+          <t>IP移動電話端末|IP移動電話端末 送信タイミング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38578,7 +38578,7 @@
       </c>
       <c r="W397" t="inlineStr">
         <is>
-          <t>漏話減衰量1500Hz|専用通信回線設備等端末 漏話減衰量 1500Hz 70dB</t>
+          <t>漏話減衰量|漏話減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38683,7 +38683,7 @@
       </c>
       <c r="W398" t="inlineStr">
         <is>
-          <t>通信回線電圧100V|通信回線 線路の電圧 100ボルト以下 有線電気通信設備令</t>
+          <t>通信回線|通信回線 線路の電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38775,7 +38775,7 @@
       </c>
       <c r="W399" t="inlineStr">
         <is>
-          <t>強電流電線重畳分離|強電流電線 重畳 分離 開閉 有線電気通信設備令</t>
+          <t>強電流電線|強電流電線 重畳 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38869,7 +38869,7 @@
       </c>
       <c r="W400" t="inlineStr">
         <is>
-          <t>屋内電線強電流ケーブル離隔|屋内電線 強電流ケーブル 離隔距離 隔壁 有線電気通信設備令</t>
+          <t>屋内電線|屋内電線 強電流ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38968,7 +38968,7 @@
       </c>
       <c r="W401" t="inlineStr">
         <is>
-          <t>識別符号不正アクセス禁止法|識別符号 不正アクセス禁止法 署名 アクセス管理者</t>
+          <t>識別符号|識別符号 不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39060,7 +39060,7 @@
       </c>
       <c r="W402" t="inlineStr">
         <is>
-          <t>認証業務電子署名法|認証業務 電子署名法 自らが行う 電磁的記録</t>
+          <t>認証業務|認証業務 電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39150,7 +39150,7 @@
       </c>
       <c r="W403" t="inlineStr">
         <is>
-          <t>10G-EPON GE-PON混在|10G-EPON GE-PON OLT TDMA WDM 混在接続,WDM|WDM 波長多重 下り信号 10Gbps 1Gbps</t>
+          <t>10G-EPON|10G-EPON GE-PON 工事担任者,WDM|WDM 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="W404" t="inlineStr">
         <is>
-          <t>ロケーションサーバ|ロケーションサーバ SIPサーバ UAC 位置情報管理 レジストラ比較</t>
+          <t>ロケーションサーバ|ロケーションサーバ SIP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39331,7 +39331,7 @@
       </c>
       <c r="W405" t="inlineStr">
         <is>
-          <t>PoEオルタナティブB|PoE オルタナティブB ピン4 5 7 8 予備ペア 1000BASE-T</t>
+          <t>PoEオルタナティブB|PoE オルタナティブB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39424,7 +39424,7 @@
       </c>
       <c r="W406" t="inlineStr">
         <is>
-          <t>IEEE802.11ax 6GHz|IEEE802.11ax Wi-Fi6 6GHz ISMバンド 気象レーダ干渉なし</t>
+          <t>IEEE802.11ax|IEEE802.11ax 6GHz 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39524,7 +39524,7 @@
       </c>
       <c r="W407" t="inlineStr">
         <is>
-          <t>コモンモードチョークコイル|コモンモードチョークコイル フェライトコア 高周波 ノイズ対策 EMC</t>
+          <t>コモンモードチョークコイル|コモンモードチョークコイル 工事担任者,フェライトコア|フェライトコア 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="W408" t="inlineStr">
         <is>
-          <t>8B1Q4|8B1Q4 1000BASE-T 4D-PAM5 NRZI 8B/10B 符号化比較</t>
+          <t>8B1Q4|8B1Q4 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39710,7 +39710,7 @@
       </c>
       <c r="W409" t="inlineStr">
         <is>
-          <t>FM一括変換方式|FM一括変換方式 CATV 3GHz 光強度変調 映像信号</t>
+          <t>FM一括変換方式|FM一括変換方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39803,7 +39803,7 @@
       </c>
       <c r="W410" t="inlineStr">
         <is>
-          <t>ICMPv6パラメータ問題|ICMPv6 パラメータ問題 時間超過 終点到達不能 IPv6</t>
+          <t>ICMPv6|ICMPv6 パラメータ問題 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39896,7 +39896,7 @@
       </c>
       <c r="W411" t="inlineStr">
         <is>
-          <t>ジッタバッファ|ジッタバッファ 揺らぎ吸収 VoIP 音声品質 パケット損失</t>
+          <t>ジッタバッファ|ジッタバッファ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39986,7 +39986,7 @@
       </c>
       <c r="W412" t="inlineStr">
         <is>
-          <t>広域イーサネット|広域イーサネット MPLS LER LSR レイヤ2 ルーティングプロトコル</t>
+          <t>広域イーサネット|広域イーサネット 工事担任者,MPLS|MPLS LER LSR 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40079,7 +40079,7 @@
       </c>
       <c r="W413" t="inlineStr">
         <is>
-          <t>rootkit|rootkit ルートキット バックドア 権限奪取 マルウェア</t>
+          <t>rootkit|rootkit 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40179,7 +40179,7 @@
       </c>
       <c r="W414" t="inlineStr">
         <is>
-          <t>ハイブリッド暗号|ハイブリッド暗号 PGP 共通鍵 公開鍵 処理速度比較</t>
+          <t>ハイブリッド暗号|ハイブリッド暗号 PGP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40275,7 +40275,7 @@
       </c>
       <c r="W415" t="inlineStr">
         <is>
-          <t>クロスサイトスクリプティング|クロスサイトスクリプティング XSS SQLインジェクション サニタイジング比較</t>
+          <t>クロスサイトスクリプティング|クロスサイトスクリプティング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40375,7 +40375,7 @@
       </c>
       <c r="W416" t="inlineStr">
         <is>
-          <t>IPsec|IPsec トランスポートモード トンネルモード VPN リモートアクセス</t>
+          <t>IPsec|IPsec 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40468,7 +40468,7 @@
       </c>
       <c r="W417" t="inlineStr">
         <is>
-          <t>CSIRT|CSIRT インシデント対応 セキュリティ 被害拡大防止</t>
+          <t>CSIRT|CSIRT 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40574,7 +40574,7 @@
       </c>
       <c r="W418" t="inlineStr">
         <is>
-          <t>融着接続アーク放電|融着接続 アーク放電 スクリーニング試験 引張試験</t>
+          <t>融着接続|融着接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40667,7 +40667,7 @@
       </c>
       <c r="W419" t="inlineStr">
         <is>
-          <t>フリーアクセスフロア|フリーアクセスフロア OAフロア 不陸調整 支柱ねじ</t>
+          <t>フリーアクセスフロア|フリーアクセスフロア 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40757,7 +40757,7 @@
       </c>
       <c r="W420" t="inlineStr">
         <is>
-          <t>OTDR法|OTDR法 後方散乱光 両端測定 平均化 光ファイバ損失</t>
+          <t>OTDR法|OTDR法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40850,7 +40850,7 @@
       </c>
       <c r="W421" t="inlineStr">
         <is>
-          <t>T568B|T568B RJ-45 ピン6番 緑色 心線配色</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40948,7 +40948,7 @@
       </c>
       <c r="W422" t="inlineStr">
         <is>
-          <t>JIS X 5150クラスF|JIS X 5150 インタコネクト クラスF 82.5m 水平ケーブル</t>
+          <t>JIS X 5150|JIS X 5150 クラスF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41041,7 +41041,7 @@
       </c>
       <c r="W423" t="inlineStr">
         <is>
-          <t>IEEE802.3bq|IEEE802.3bq 40GBASE-T カテゴリ8 30メートル データセンタ</t>
+          <t>IEEE802.3bq|IEEE802.3bq 40GBASE-T 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41134,7 +41134,7 @@
       </c>
       <c r="W424" t="inlineStr">
         <is>
-          <t>OTDRダイナミックレンジ|OTDR ダイナミックレンジ 後方散乱光 パルスパワー増加</t>
+          <t>OTDRダイナミックレンジ|OTDR ダイナミックレンジ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41227,7 +41227,7 @@
       </c>
       <c r="W425" t="inlineStr">
         <is>
-          <t>融着接続気泡|融着接続 気泡 光ファイバカッタ 端面切断 やり直し</t>
+          <t>融着接続|融着接続 気泡 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="W426" t="inlineStr">
         <is>
-          <t>QC7つ道具|QC7つ道具 ヒストグラム 散布図 パレート図 管理図 違い</t>
+          <t>QC7つ道具|QC7つ道具 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41421,7 +41421,7 @@
       </c>
       <c r="W427" t="inlineStr">
         <is>
-          <t>KYT4ラウンド法|KYT 危険予知訓練 4ラウンド法 本質追究 安全管理</t>
+          <t>KYT|KYT 4ラウンド法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41521,7 +41521,7 @@
       </c>
       <c r="W428" t="inlineStr">
         <is>
-          <t>資格者証交付要件|資格者証 罰金以上 5年 養成課程 返納 工事担任者</t>
+          <t>資格者証|資格者証 罰金 5年 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41620,7 +41620,7 @@
       </c>
       <c r="W429" t="inlineStr">
         <is>
-          <t>業務改善命令支障おそれ|業務改善命令 支障 おそれ 対象外 提供条件 電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 支障 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41719,7 +41719,7 @@
       </c>
       <c r="W430" t="inlineStr">
         <is>
-          <t>管理規程届出|管理規程 事業開始前 届出 許可ではない 基礎的電気通信役務</t>
+          <t>管理規程|管理規程 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41811,7 +41811,7 @@
       </c>
       <c r="W431" t="inlineStr">
         <is>
-          <t>技術基準適合認定他の利用者|技術基準適合認定 他の利用者 妨害防止 表示なしとみなす</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41903,7 +41903,7 @@
       </c>
       <c r="W432" t="inlineStr">
         <is>
-          <t>端末設備接続拒否著しく不適当|端末設備 接続請求 利用者 著しく不適当 拒否</t>
+          <t>端末設備|端末設備 接続請求 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42008,7 +42008,7 @@
       </c>
       <c r="W433" t="inlineStr">
         <is>
-          <t>第二級アナログ通信|第二級アナログ通信 回線数1以下 50以下ではない 工事担任者</t>
+          <t>第二級アナログ通信|第二級アナログ通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42107,7 +42107,7 @@
       </c>
       <c r="W434" t="inlineStr">
         <is>
-          <t>資格者証汚した再交付|資格者証 汚した 再交付 返納10日以内</t>
+          <t>資格者証|資格者証 再交付 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42196,7 +42196,7 @@
       </c>
       <c r="W435" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号G P|技術基準適合認定番号 固定電話端末G 専用通信回線設備等端末P</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42301,7 +42301,7 @@
       </c>
       <c r="W436" t="inlineStr">
         <is>
-          <t>有線電気通信法目的|有線電気通信法 設置及び使用 秩序 公共の福祉</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42388,7 +42388,7 @@
       </c>
       <c r="W437" t="inlineStr">
         <is>
-          <t>有線電気通信設備変更届|有線電気通信設備 変更届 2週間前 工事を要しない 2週間以内</t>
+          <t>有線電気通信設備令|有線電気通信設備令 変更届 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42493,7 +42493,7 @@
       </c>
       <c r="W438" t="inlineStr">
         <is>
-          <t>IP移動電話端末|IP移動電話端末 IP移動電話用設備のみ デジタルデータ伝送用設備ではない</t>
+          <t>IP移動電話端末|IP移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42592,7 +42592,7 @@
       </c>
       <c r="W439" t="inlineStr">
         <is>
-          <t>分界点接続方式|分界点 電気的条件 光学的条件 容易に切り離せる 鳴音</t>
+          <t>分界点|分界点 接続方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42684,7 +42684,7 @@
       </c>
       <c r="W440" t="inlineStr">
         <is>
-          <t>絶縁耐力250V 2500V|絶縁耐力試験 250V超 2500ボルト 1分間 端末設備等規則</t>
+          <t>絶縁耐力試験|絶縁耐力試験 2500V 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42776,7 +42776,7 @@
       </c>
       <c r="W441" t="inlineStr">
         <is>
-          <t>配線設備絶縁抵抗200V|配線設備 絶縁抵抗 直流200V 1MΩ</t>
+          <t>配線設備|配線設備 直流200V 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42868,7 +42868,7 @@
       </c>
       <c r="W442" t="inlineStr">
         <is>
-          <t>識別符号|識別符号 無線設備 通信路設定 照合</t>
+          <t>識別符号|識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42960,7 +42960,7 @@
       </c>
       <c r="W443" t="inlineStr">
         <is>
-          <t>移動電話端末チャネル切断|移動電話端末 チャネル切断 通信終了</t>
+          <t>チャネル切断|チャネル切断 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43065,7 +43065,7 @@
       </c>
       <c r="W444" t="inlineStr">
         <is>
-          <t>固定電話端末自動再発信|固定電話端末 自動再発信 3分間 2回以内</t>
+          <t>自動再発信|自動再発信 固定電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43164,7 +43164,7 @@
       </c>
       <c r="W445" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末直流|専用通信回線設備等端末 直流電圧 電気的条件 光学的条件</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 直流電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43264,7 +43264,7 @@
       </c>
       <c r="W446" t="inlineStr">
         <is>
-          <t>アクセス制御電力停止|アクセス制御 初期識別符号 ソフトウェア更新 通信プロトコルではない</t>
+          <t>アクセス制御|アクセス制御 ソフトウェア更新 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43363,7 +43363,7 @@
       </c>
       <c r="W447" t="inlineStr">
         <is>
-          <t>2周波電力差5dB|2周波電力差 5dB以内 ミニマムポーズ 最小値 押しボタンダイヤル</t>
+          <t>2周波電力差|2周波電力差 ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43452,7 +43452,7 @@
       </c>
       <c r="W448" t="inlineStr">
         <is>
-          <t>屋内電線強電流電線30cm|屋内電線 強電流電線 30センチメートル 保安機能 有線電気通信設備令</t>
+          <t>屋内電線|屋内電線 強電流電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="W449" t="inlineStr">
         <is>
-          <t>架空電線建造物30cm|架空電線 建造物 離隔距離 30センチメートル以下禁止</t>
+          <t>架空電線|架空電線 建造物 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43649,7 +43649,7 @@
       </c>
       <c r="W450" t="inlineStr">
         <is>
-          <t>架空電線鉄道6m|架空電線 鉄道軌道横断 軌条面6メートル 有線電気通信設備令</t>
+          <t>架空電線|架空電線 鉄道横断 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43741,7 +43741,7 @@
       </c>
       <c r="W451" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法|不正アクセス禁止法 電子計算機 犯罪防止 アクセス制御</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43833,7 +43833,7 @@
       </c>
       <c r="W452" t="inlineStr">
         <is>
-          <t>電子署名作成者|電子署名 電磁的記録 作成者 電子署名法</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43926,7 +43926,7 @@
       </c>
       <c r="W453" t="inlineStr">
         <is>
-          <t>XGS-PON|XGS-PON ITU-T G.9807.1 GTCフレーム 10Gbps対称 XG-PON比較</t>
+          <t>XGS-PON|XGS-PON 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
       </c>
       <c r="W454" t="inlineStr">
         <is>
-          <t>汎用サーバIP-PBX|汎用サーバIP-PBX VoIPゲートウェイ アナログ電話機 SIPアプリケーション層</t>
+          <t>IP-PBX|IP-PBX VoIPゲートウェイ 工事担任者,SIP|SIP アプリケーション層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44119,7 +44119,7 @@
       </c>
       <c r="W455" t="inlineStr">
         <is>
-          <t>IEEE802.3bt Type4|IEEE802.3bt Type4 Class8 90W 4対給電</t>
+          <t>IEEE802.3bt|IEEE802.3bt 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44212,7 +44212,7 @@
       </c>
       <c r="W456" t="inlineStr">
         <is>
-          <t>ブロックACK|IEEE802.11n ブロックACK プローブ応答 ビーコン 違い</t>
+          <t>ブロックACK|ブロックACK IEEE802.11n 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44305,7 +44305,7 @@
       </c>
       <c r="W457" t="inlineStr">
         <is>
-          <t>等電位ボンディング|等電位ボンディング SPD 雷保護 直接導体 JIS C 5381</t>
+          <t>等電位ボンディング|等電位ボンディング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44398,7 +44398,7 @@
       </c>
       <c r="W458" t="inlineStr">
         <is>
-          <t>10GBASE-LR|10GBASE-LR 64B/66B 4B/5B 8B1Q4 符号化方式比較</t>
+          <t>10GBASE-LR|10GBASE-LR 工事担任者,64B/66B|64B/66B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44491,7 +44491,7 @@
       </c>
       <c r="W459" t="inlineStr">
         <is>
-          <t>HFC|HFC Hybrid Fiber Coaxial 光ノード 同軸ケーブル FTTH比較</t>
+          <t>HFC|HFC 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="W460" t="inlineStr">
         <is>
-          <t>SaaS|SaaS PaaS IaaS クラウドサービス アプリケーション 比較</t>
+          <t>SaaS|SaaS PaaS IaaS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44685,7 +44685,7 @@
       </c>
       <c r="W461" t="inlineStr">
         <is>
-          <t>IPv6リンクローカル|IPv6 リンクローカル fe80 fec0 マルチキャスト エニーキャスト</t>
+          <t>IPv6|IPv6 リンクローカル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44775,7 +44775,7 @@
       </c>
       <c r="W462" t="inlineStr">
         <is>
-          <t>MACアドレス|MACアドレス NIC 48ビット FCS フレーム誤り検出</t>
+          <t>MACアドレス|MACアドレス 工事担任者,FCS|FCS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44868,7 +44868,7 @@
       </c>
       <c r="W463" t="inlineStr">
         <is>
-          <t>検疫ネットワーク|検疫ネットワーク セキュリティポリシー 隔離 不正PC</t>
+          <t>検疫ネットワーク|検疫ネットワーク 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44961,7 +44961,7 @@
       </c>
       <c r="W464" t="inlineStr">
         <is>
-          <t>DKIM|DKIM SPF デジタル署名 送信元ドメイン認証 迷惑メール対策</t>
+          <t>DKIM|DKIM SPF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45054,7 +45054,7 @@
       </c>
       <c r="W465" t="inlineStr">
         <is>
-          <t>SSH|SSH Secure Shell Telnet 暗号化 遠隔操作 比較</t>
+          <t>SSH|SSH Telnet 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45154,7 +45154,7 @@
       </c>
       <c r="W466" t="inlineStr">
         <is>
-          <t>スニッフィング|スニッフィング データマイニング IPスプーフィング 違い なりすまし</t>
+          <t>スニッフィング|スニッフィング IPスプーフィング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45260,7 +45260,7 @@
       </c>
       <c r="W467" t="inlineStr">
         <is>
-          <t>ISMS開発テスト本番分離|ISMS JIS Q 27001 開発環境 テスト環境 本番環境 分離</t>
+          <t>JIS Q 27001|JIS Q 27001 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="W468" t="inlineStr">
         <is>
-          <t>挿入法|挿入法 カットバック法 光ファイバ 挿入損失 JIS C 6823</t>
+          <t>挿入法|挿入法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45429,7 +45429,7 @@
       </c>
       <c r="W469" t="inlineStr">
         <is>
-          <t>JIS C 0303|JIS C 0303 情報用アウトレット 図記号 電気設備</t>
+          <t>JIS C 0303|JIS C 0303 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45522,7 +45522,7 @@
       </c>
       <c r="W470" t="inlineStr">
         <is>
-          <t>キンク|キンク UTPケーブル くの字型 ケーブル布設 変形</t>
+          <t>キンク|キンク UTPケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45612,7 +45612,7 @@
       </c>
       <c r="W471" t="inlineStr">
         <is>
-          <t>8の字巻き|光ファイバケーブル テンションメンバ 8の字 同心円 けん引端</t>
+          <t>8の字巻き|光ファイバ 8の字巻き 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45713,7 +45713,7 @@
       </c>
       <c r="W472" t="inlineStr">
         <is>
-          <t>分岐点15m|分岐点 フロア配線盤 15メートル以上 JIS X 5150</t>
+          <t>分岐点|分岐点 フロア配線盤 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45806,7 +45806,7 @@
       </c>
       <c r="W473" t="inlineStr">
         <is>
-          <t>エイリアンクロストーク|エイリアンクロストーク 異線間漏話 ラック内余長 UTPケーブル</t>
+          <t>エイリアンクロストーク|エイリアンクロストーク 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45899,7 +45899,7 @@
       </c>
       <c r="W474" t="inlineStr">
         <is>
-          <t>FASコネクタ|FASコネクタ 単心光コネクタ 架空クロージャ ドロップ光ファイバ</t>
+          <t>FASコネクタ|FASコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45992,7 +45992,7 @@
       </c>
       <c r="W475" t="inlineStr">
         <is>
-          <t>STP|STP IEEE802.1D スパニングツリー ループ防止 フレーム</t>
+          <t>STP|STP IEEE802.1D 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46103,7 +46103,7 @@
       </c>
       <c r="W476" t="inlineStr">
         <is>
-          <t>変動原価率損益分岐点|変動原価率 損益分岐点 採算性 コスト管理 工事</t>
+          <t>損益分岐点|損益分岐点 変動原価率 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46201,7 +46201,7 @@
       </c>
       <c r="W477" t="inlineStr">
         <is>
-          <t>アローダイアグラム短縮|アローダイアグラム クリティカルパス 短縮 所要日数 PERT</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46306,7 +46306,7 @@
       </c>
       <c r="W478" t="inlineStr">
         <is>
-          <t>業務改善命令支障おそれ|業務改善命令 支障おそれ 対象外 不当差別 電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46398,7 +46398,7 @@
       </c>
       <c r="W479" t="inlineStr">
         <is>
-          <t>端末設備異常検査|端末設備 異常 電気通信役務 検査 電気通信事業法</t>
+          <t>端末設備|端末設備 異常 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46495,7 +46495,7 @@
       </c>
       <c r="W480" t="inlineStr">
         <is>
-          <t>管理規程確実安定的|管理規程 確実かつ安定的 適正かつ継続的 電気通信事業法</t>
+          <t>管理規程|管理規程 確実かつ安定的 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46594,7 +46594,7 @@
       </c>
       <c r="W481" t="inlineStr">
         <is>
-          <t>技術基準適合認定公示|技術基準適合認定 登録認定機関 総務省令 表示 公示</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46689,7 +46689,7 @@
       </c>
       <c r="W482" t="inlineStr">
         <is>
-          <t>重要通信気象機関|重要通信 気象機関 選挙管理機関 緊急通信 電気通信事業法</t>
+          <t>重要通信|重要通信 気象機関 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46779,7 +46779,7 @@
       </c>
       <c r="W483" t="inlineStr">
         <is>
-          <t>工事担任者資格区分|工事担任者 第二級アナログ 第一級アナログ 第二級デジタル 資格区分</t>
+          <t>工事担任者資格区分|工事担任者 資格区分 比較</t>
         </is>
       </c>
     </row>
@@ -46878,7 +46878,7 @@
       </c>
       <c r="W484" t="inlineStr">
         <is>
-          <t>資格者証書換え返納|資格者証 書換え交付 住所変更 返納10日以内</t>
+          <t>資格者証|資格者証 書換え交付 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46972,7 +46972,7 @@
       </c>
       <c r="W485" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号H P|技術基準適合認定番号 IP移動電話端末H 専用通信回線設備等端末P Qではない</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47064,7 +47064,7 @@
       </c>
       <c r="W486" t="inlineStr">
         <is>
-          <t>有線電気通信法変更届|有線電気通信法 設備の概要 変更届 届出</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47156,7 +47156,7 @@
       </c>
       <c r="W487" t="inlineStr">
         <is>
-          <t>有線電気通信法非常事態|有線電気通信法 非常事態 他の者に使用させ 接続</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47256,7 +47256,7 @@
       </c>
       <c r="W488" t="inlineStr">
         <is>
-          <t>制御チャネル|制御チャネル デジタルデータ伝送用設備 総合デジタル通信用設備 違い</t>
+          <t>制御チャネル|制御チャネル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47355,7 +47355,7 @@
       </c>
       <c r="W489" t="inlineStr">
         <is>
-          <t>分界点識別禁止|分界点 識別機能 事業用電気通信設備 自営電気通信設備 違い</t>
+          <t>分界点|分界点 識別機能 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47452,7 +47452,7 @@
       </c>
       <c r="W490" t="inlineStr">
         <is>
-          <t>絶縁抵抗250V 2MΩ|絶縁抵抗 250V以下 2MΩ以上 0.2MΩとの違い 端末設備等規則</t>
+          <t>絶縁抵抗|絶縁抵抗 250V 2MΩ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47541,7 +47541,7 @@
       </c>
       <c r="W491" t="inlineStr">
         <is>
-          <t>配線設備有線電気通信設備令|配線設備 有線電気通信設備令 事業用電気通信設備 損傷 告示</t>
+          <t>有線電気通信設備令|有線電気通信設備令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47633,7 +47633,7 @@
       </c>
       <c r="W492" t="inlineStr">
         <is>
-          <t>識別符号一の筐体|識別符号 一の筐体 容易に開けられない 無線設備 端末設備等規則</t>
+          <t>識別符号|識別符号 一の筐体 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47725,7 +47725,7 @@
       </c>
       <c r="W493" t="inlineStr">
         <is>
-          <t>固定電話端末通信終了2分|固定電話端末 通信終了メッセージ 2分以内 応答確認</t>
+          <t>固定電話端末|固定電話端末 通信終了 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47825,7 +47825,7 @@
       </c>
       <c r="W494" t="inlineStr">
         <is>
-          <t>登録要求固定電話用設備|登録要求 固定電話端末 固定電話用設備のみ デジタルデータ伝送用設備ではない</t>
+          <t>登録要求|登録要求 固定電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47914,7 +47914,7 @@
       </c>
       <c r="W495" t="inlineStr">
         <is>
-          <t>IP移動電話端末自動再発信|IP移動電話端末 自動再発信 3回以内 3分 送信タイミング</t>
+          <t>IP移動電話端末|IP移動電話端末 自動再発信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48006,7 +48006,7 @@
       </c>
       <c r="W496" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末変更|専用通信回線設備等端末 アクセス制御 変更 管理 記録</t>
+          <t>アクセス制御|アクセス制御 変更 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48106,7 +48106,7 @@
       </c>
       <c r="W497" t="inlineStr">
         <is>
-          <t>信号周波数偏差|信号周波数偏差 ±1.5% ミニマムポーズ 信号送出時間 高群周波数</t>
+          <t>信号周波数偏差|信号周波数偏差 工事担任者,ミニマムポーズ|ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48206,7 +48206,7 @@
       </c>
       <c r="W498" t="inlineStr">
         <is>
-          <t>絶対レベル定義|絶対レベル 有効電力 1mW デシベル 有線電気通信法</t>
+          <t>絶対レベル|絶対レベル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48295,7 +48295,7 @@
       </c>
       <c r="W499" t="inlineStr">
         <is>
-          <t>架空電線強電流電線支持物|架空電線 強電流電線 支持物 30センチメートル 有線電気通信設備令</t>
+          <t>架空電線|架空電線 強電流電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48387,7 +48387,7 @@
       </c>
       <c r="W500" t="inlineStr">
         <is>
-          <t>架空電線横断歩道橋3m|架空電線 横断歩道橋 路面3メートル 有線電気通信設備令</t>
+          <t>架空電線|架空電線 横断歩道橋 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48479,7 +48479,7 @@
       </c>
       <c r="W501" t="inlineStr">
         <is>
-          <t>アクセス管理者有効性|アクセス管理者 アクセス制御機能 有効性 高度化 不正アクセス禁止法</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48573,7 +48573,7 @@
       </c>
       <c r="W502" t="inlineStr">
         <is>
-          <t>電子署名法真正|電子署名法 真正に成立 推定 暗号化ではなく 本人による署名</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
